--- a/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
+++ b/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>113</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.375</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(7170, 2)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7170, 2)</t>
         </is>
@@ -551,13 +566,19 @@
           <t>words are very</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(530, 4, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(530, 4, 50, getRandomCRGB())</t>
         </is>
@@ -572,13 +593,19 @@
           <t>synth</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(8495, 970, 6, 5, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8495, 970, 6, 5, 26, 5, true, 3)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>synth</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 8, 10)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 10)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(16990, 3, 15)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(16990, 3, 15)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>all i ever wanted</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8495, 20, 1060)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 20, 1060)</t>
         </is>
@@ -656,13 +701,19 @@
           <t>words are very</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(7965, 25, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progStrobo(7965, 25, 50, getRandomCRGB())</t>
         </is>
@@ -677,13 +728,19 @@
           <t>STOP</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(520, 30)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progBlack(520, 30)</t>
         </is>
@@ -698,13 +755,19 @@
           <t>drumloop</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progMovingLines(1590, 32)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progMovingLines(1590, 32)</t>
         </is>
@@ -719,13 +782,19 @@
           <t>snarewirbel</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(540, 35, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progStrobo(540, 35, 50, getRandomCRGB())</t>
         </is>
@@ -740,13 +809,19 @@
           <t>synth</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(17000, 970, 40, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(17000, 970, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -761,13 +836,19 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(8495, 2, 45)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 2, 45)</t>
         </is>
@@ -782,13 +863,19 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(8495, 3, 50)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 3, 50)</t>
         </is>
@@ -803,13 +890,19 @@
           <t>all i ever wanted</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8495, 55, 1060)</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 55, 1060)</t>
         </is>
@@ -824,13 +917,19 @@
           <t>words are very</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(8495, 60, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 60, 50, getRandomCRGB())</t>
         </is>
@@ -845,13 +944,19 @@
           <t>2  3  4</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(2125, 65, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 65))</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 65, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 65))</t>
         </is>
@@ -866,13 +971,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 2, 70)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 70)</t>
         </is>
@@ -887,13 +998,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 4, 75)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 75)</t>
         </is>
@@ -908,13 +1025,20 @@
           <t>bass slap part</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(16990, 80, 50, true, true)
+! der alte Code setzt hier Marker: markerLED5 = ESaite_F_hoch</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16990, 80, 50, true, true)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_F_hoch</t>
@@ -930,13 +1054,20 @@
           <t>all i ever wanted</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8495, 85, 1060)
+! der alte Code setzt hier Marker: markerLED5 = 0</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 85, 1060)
 ! der alte Code setzt hier Marker: markerLED5 = 0</t>
@@ -952,13 +1083,19 @@
           <t>words are very</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(8495, 90, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 90, 50, getRandomCRGB())</t>
         </is>
@@ -973,13 +1110,19 @@
           <t>all i ever wanted</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(8500, 95, 1060)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8500, 95, 1060)</t>
         </is>
@@ -994,13 +1137,19 @@
           <t>words are very</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(8495, 100, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 100, 50, getRandomCRGB())</t>
         </is>
@@ -1015,13 +1164,19 @@
           <t>2  3  4</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(2125, 105, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 105))</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 105, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 105))</t>
         </is>
@@ -1036,13 +1191,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 2, 110)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 110)</t>
         </is>
@@ -1057,13 +1218,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 4, 115)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 115)</t>
         </is>
@@ -1078,13 +1245,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 6, 120)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 6, 120)</t>
         </is>
@@ -1099,13 +1272,19 @@
           <t>enjoy the silence</t>
         </is>
       </c>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(8495, 8, 135)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 135)</t>
         </is>
@@ -1125,10 +1304,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="E34">
+      <c r="F34">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
+++ b/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>27.75</v>
+        <v>28.75</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>28.75</v>
+        <v>29.75</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="34">
       <c r="A34" s="7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>

--- a/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
+++ b/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>113</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.375</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(7170, 2)</t>
         </is>
@@ -573,12 +583,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(530, 4, 50, getRandomCRGB())</t>
         </is>
@@ -600,12 +611,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in festen Farben (ROYAL) und mit weichen Farbwechseln (soft 60) - passt besser zum getragenen Riff.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8495, 970, 6, 5, 26, 5, true, 3)</t>
         </is>
@@ -627,12 +643,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 10)</t>
         </is>
@@ -654,12 +671,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Rain, ICE, Farbwanderung (triad, 2 Takte): ruhige Leuchtspuren, Eisblau wandert nach Pink und zurück.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(16990, 3, 15)</t>
         </is>
@@ -681,12 +703,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, SUNSET, soft 100: die ganze Bühne fließt von Farbe zu Farbe (alle 2 Beats) statt zu springen. Fester Look für alle vier "all i ever wanted".</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 20, 1060)</t>
         </is>
@@ -708,12 +735,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Statt 4 Takten Flimmern: Szene Wave Out, WHITE - ein Blitz läuft pro Beat von der Mitte nach außen. Fester Look für alle "words are very".</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progStrobo(7965, 25, 50, getRandomCRGB())</t>
         </is>
@@ -735,12 +767,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progBlack(520, 30)</t>
         </is>
@@ -762,12 +795,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Buildup (3 Beats), ROYAL statt wandernder Linien: lädt sich auf, Explosion auf den Snarewirbel.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progMovingLines(1590, 32)</t>
         </is>
@@ -789,12 +827,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo; starker Blinder auf den Einsatz von "synth (3)" (Takt 30).</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progStrobo(540, 35, 50, getRandomCRGB())</t>
         </is>
@@ -816,12 +859,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Stern wie am Anfang (ROYAL, soft 60), Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(17000, 970, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -843,12 +891,17 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Szene DNA Flip, ROYAL: stehende Helix auf der Matrix, alle anderen pulsieren einmal je Takt.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 2, 45)</t>
         </is>
@@ -870,12 +923,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Szene Verse, ICE: dezenter Puls im Beat - kleine Steigerung zum Part davor.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 3, 50)</t>
         </is>
@@ -897,12 +955,17 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Colors, SUNSET, soft 100).</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 55, 1060)</t>
         </is>
@@ -924,12 +987,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>wie oben (Wave Out, WHITE).</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 60, 50, getRandomCRGB())</t>
         </is>
@@ -951,12 +1019,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Text "2 3 4" auf der Matrix, eine Zahl pro Beat; dazu kurzer weißer Blinder nur auf den Lampen auf jeden Beat.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 65, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 65))</t>
         </is>
@@ -978,12 +1051,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Einzelblitze bleiben (wachsen von Mal zu Mal). Blinder auf den Einsatz (2 Beats).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 70)</t>
         </is>
@@ -1005,12 +1083,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 75)</t>
         </is>
@@ -1033,12 +1112,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Szene Solo Bass, ROYAL: zwei Kometen laufen um den Bass, alle anderen atmen dunkel (Marker bleibt).</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16990, 80, 50, true, true)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_F_hoch</t>
@@ -1062,12 +1146,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>wie vorher (Colors, SUNSET, soft 100).</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 85, 1060)
 ! der alte Code setzt hier Marker: markerLED5 = 0</t>
@@ -1090,12 +1179,17 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>wie oben (Wave Out, WHITE).</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 90, 50, getRandomCRGB())</t>
         </is>
@@ -1117,12 +1211,17 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Colors, jetzt in FIRE - eine Stufe wärmer zum Schluss.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8500, 95, 1060)</t>
         </is>
@@ -1144,12 +1243,17 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Wave Out, WHITE, dazu Glitzern als Ebene (Sparkle 40).</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 100, 50, getRandomCRGB())</t>
         </is>
@@ -1171,12 +1275,17 @@
         </is>
       </c>
       <c r="D29" s="6" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>wie beim ersten Mal (Text 2 3 4, Lampen-Blinder im Beat).</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 105, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 105))</t>
         </is>
@@ -1198,12 +1307,17 @@
         </is>
       </c>
       <c r="D30" s="6" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Blinder auf den Einsatz (2 Beats), Einzelblitze wachsen wie bisher.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 110)</t>
         </is>
@@ -1225,12 +1339,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 115)</t>
         </is>
@@ -1252,12 +1367,13 @@
         </is>
       </c>
       <c r="D32" s="6" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 6, 120)</t>
         </is>
@@ -1279,12 +1395,17 @@
         </is>
       </c>
       <c r="D33" s="6" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Dichteste Einzelblitze in FIRE; starker Blinder auf der letzten Viertel (Takt 103,75), der 5 Sekunden ins Schluss-Schwarz ausklingt (wie APT.).</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 135)</t>
         </is>
@@ -1304,10 +1425,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="G34">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
+++ b/songs/EnjoyTheSilence_v1/quelle/struktur.xlsx
@@ -30,7 +30,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,7 +61,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -72,6 +78,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -437,17 +446,18 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H470"/>
+  <dimension ref="A1:I470"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" outlineLevelRow="2"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -473,6 +483,7 @@
       </c>
       <c r="D2" s="2" t="n"/>
       <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -485,6 +496,7 @@
       </c>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -497,6 +509,7 @@
       </c>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,25 +529,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Alter Effekt (temporär)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Änderungswunsch</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Neuer Vorschlag (KI)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -557,12 +575,13 @@
       </c>
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5">
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
     </row>
     <row r="7" outlineLevel="2">
       <c r="A7" s="4" t="n">
@@ -572,9 +591,10 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="F7" s="6" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="6" t="n"/>
     </row>
     <row r="8" outlineLevel="2">
       <c r="A8" s="4" t="n">
@@ -584,9 +604,10 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="F8" s="6" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="6" t="n"/>
     </row>
     <row r="9" outlineLevel="2">
       <c r="A9" s="4" t="n">
@@ -596,9 +617,10 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="F9" s="6" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="6" t="n"/>
     </row>
     <row r="10" ht="57.6" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -618,9 +640,10 @@
       </c>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="6" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="6" t="n"/>
     </row>
     <row r="11" outlineLevel="2">
       <c r="A11" s="4" t="n">
@@ -630,9 +653,10 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="F11" s="6" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="6" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="6" t="n"/>
     </row>
     <row r="12" outlineLevel="2">
       <c r="A12" s="4" t="n">
@@ -642,9 +666,10 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="6" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="6" t="n"/>
     </row>
     <row r="13" outlineLevel="2">
       <c r="A13" s="4" t="n">
@@ -654,9 +679,10 @@
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="F13" s="6" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="6" t="n"/>
     </row>
     <row r="14" outlineLevel="1">
       <c r="A14" s="4" t="n">
@@ -666,9 +692,10 @@
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="6" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="6" t="n"/>
     </row>
     <row r="15" outlineLevel="2">
       <c r="A15" s="4" t="n">
@@ -678,9 +705,10 @@
       <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="5" t="n"/>
+      <c r="F15" s="6" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="6" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="6" t="n"/>
     </row>
     <row r="16" outlineLevel="2">
       <c r="A16" s="4" t="n">
@@ -690,9 +718,10 @@
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="n"/>
       <c r="G16" s="5" t="n"/>
-      <c r="H16" s="6" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="n"/>
     </row>
     <row r="17" outlineLevel="2">
       <c r="A17" s="4" t="n">
@@ -702,9 +731,10 @@
       <c r="C17" s="6" t="n"/>
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="6" t="n"/>
-      <c r="F17" s="5" t="n"/>
+      <c r="F17" s="6" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="6" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="n"/>
     </row>
     <row r="18" outlineLevel="1">
       <c r="A18" s="4" t="n">
@@ -714,9 +744,10 @@
       <c r="C18" s="6" t="n"/>
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="6" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="F18" s="6" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="6" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="n"/>
     </row>
     <row r="19" outlineLevel="2">
       <c r="A19" s="4" t="n">
@@ -726,9 +757,10 @@
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
       <c r="E19" s="6" t="n"/>
-      <c r="F19" s="5" t="n"/>
+      <c r="F19" s="6" t="n"/>
       <c r="G19" s="5" t="n"/>
-      <c r="H19" s="6" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="n"/>
     </row>
     <row r="20" outlineLevel="2">
       <c r="A20" s="4" t="n">
@@ -738,9 +770,10 @@
       <c r="C20" s="6" t="n"/>
       <c r="D20" s="6" t="n"/>
       <c r="E20" s="6" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="6" t="n"/>
       <c r="G20" s="5" t="n"/>
-      <c r="H20" s="6" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="6" t="n"/>
     </row>
     <row r="21" outlineLevel="2">
       <c r="A21" s="4" t="n">
@@ -750,9 +783,10 @@
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
-      <c r="F21" s="5" t="n"/>
+      <c r="F21" s="6" t="n"/>
       <c r="G21" s="5" t="n"/>
-      <c r="H21" s="6" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="6" t="n"/>
     </row>
     <row r="22" outlineLevel="1">
       <c r="A22" s="4" t="n">
@@ -762,9 +796,10 @@
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
       <c r="E22" s="6" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="F22" s="6" t="n"/>
       <c r="G22" s="5" t="n"/>
-      <c r="H22" s="6" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="6" t="n"/>
     </row>
     <row r="23" outlineLevel="2">
       <c r="A23" s="4" t="n">
@@ -774,9 +809,10 @@
       <c r="C23" s="6" t="n"/>
       <c r="D23" s="6" t="n"/>
       <c r="E23" s="6" t="n"/>
-      <c r="F23" s="5" t="n"/>
+      <c r="F23" s="6" t="n"/>
       <c r="G23" s="5" t="n"/>
-      <c r="H23" s="6" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="6" t="n"/>
     </row>
     <row r="24" outlineLevel="2">
       <c r="A24" s="4" t="n">
@@ -786,9 +822,10 @@
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
       <c r="E24" s="6" t="n"/>
-      <c r="F24" s="5" t="n"/>
+      <c r="F24" s="6" t="n"/>
       <c r="G24" s="5" t="n"/>
-      <c r="H24" s="6" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="6" t="n"/>
     </row>
     <row r="25" outlineLevel="2">
       <c r="A25" s="4" t="n">
@@ -798,9 +835,10 @@
       <c r="C25" s="6" t="n"/>
       <c r="D25" s="6" t="n"/>
       <c r="E25" s="6" t="n"/>
-      <c r="F25" s="5" t="n"/>
+      <c r="F25" s="6" t="n"/>
       <c r="G25" s="5" t="n"/>
-      <c r="H25" s="6" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="6" t="n"/>
     </row>
     <row r="26" outlineLevel="1">
       <c r="A26" s="4" t="n">
@@ -810,9 +848,10 @@
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="F26" s="6" t="n"/>
       <c r="G26" s="5" t="n"/>
-      <c r="H26" s="6" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="6" t="n"/>
     </row>
     <row r="27" outlineLevel="2">
       <c r="A27" s="4" t="n">
@@ -822,9 +861,10 @@
       <c r="C27" s="6" t="n"/>
       <c r="D27" s="6" t="n"/>
       <c r="E27" s="6" t="n"/>
-      <c r="F27" s="5" t="n"/>
+      <c r="F27" s="6" t="n"/>
       <c r="G27" s="5" t="n"/>
-      <c r="H27" s="6" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="6" t="n"/>
     </row>
     <row r="28" outlineLevel="2">
       <c r="A28" s="4" t="n">
@@ -834,9 +874,10 @@
       <c r="C28" s="6" t="n"/>
       <c r="D28" s="6" t="n"/>
       <c r="E28" s="6" t="n"/>
-      <c r="F28" s="5" t="n"/>
+      <c r="F28" s="6" t="n"/>
       <c r="G28" s="5" t="n"/>
-      <c r="H28" s="6" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="6" t="n"/>
     </row>
     <row r="29" outlineLevel="2">
       <c r="A29" s="4" t="n">
@@ -846,9 +887,10 @@
       <c r="C29" s="6" t="n"/>
       <c r="D29" s="6" t="n"/>
       <c r="E29" s="6" t="n"/>
-      <c r="F29" s="5" t="n"/>
+      <c r="F29" s="6" t="n"/>
       <c r="G29" s="5" t="n"/>
-      <c r="H29" s="6" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="6" t="n"/>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="4" t="n">
@@ -858,9 +900,10 @@
       <c r="C30" s="6" t="n"/>
       <c r="D30" s="6" t="n"/>
       <c r="E30" s="6" t="n"/>
-      <c r="F30" s="5" t="n"/>
+      <c r="F30" s="6" t="n"/>
       <c r="G30" s="5" t="n"/>
-      <c r="H30" s="6" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="6" t="n"/>
     </row>
     <row r="31" outlineLevel="2">
       <c r="A31" s="4" t="n">
@@ -870,9 +913,10 @@
       <c r="C31" s="6" t="n"/>
       <c r="D31" s="6" t="n"/>
       <c r="E31" s="6" t="n"/>
-      <c r="F31" s="5" t="n"/>
+      <c r="F31" s="6" t="n"/>
       <c r="G31" s="5" t="n"/>
-      <c r="H31" s="6" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="6" t="n"/>
     </row>
     <row r="32" outlineLevel="2">
       <c r="A32" s="4" t="n">
@@ -882,9 +926,10 @@
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
-      <c r="F32" s="5" t="n"/>
+      <c r="F32" s="6" t="n"/>
       <c r="G32" s="5" t="n"/>
-      <c r="H32" s="6" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="6" t="n"/>
     </row>
     <row r="33" outlineLevel="2">
       <c r="A33" s="4" t="n">
@@ -894,9 +939,10 @@
       <c r="C33" s="6" t="n"/>
       <c r="D33" s="6" t="n"/>
       <c r="E33" s="6" t="n"/>
-      <c r="F33" s="5" t="n"/>
+      <c r="F33" s="6" t="n"/>
       <c r="G33" s="5" t="n"/>
-      <c r="H33" s="6" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="6" t="n"/>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="4" t="n">
@@ -906,9 +952,10 @@
       <c r="C34" s="6" t="n"/>
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n"/>
-      <c r="F34" s="5" t="n"/>
+      <c r="F34" s="6" t="n"/>
       <c r="G34" s="5" t="n"/>
-      <c r="H34" s="6" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="6" t="n"/>
     </row>
     <row r="35" outlineLevel="2">
       <c r="A35" s="4" t="n">
@@ -918,9 +965,10 @@
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
       <c r="E35" s="6" t="n"/>
-      <c r="F35" s="5" t="n"/>
+      <c r="F35" s="6" t="n"/>
       <c r="G35" s="5" t="n"/>
-      <c r="H35" s="6" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="6" t="n"/>
     </row>
     <row r="36" outlineLevel="2">
       <c r="A36" s="4" t="n">
@@ -930,9 +978,10 @@
       <c r="C36" s="6" t="n"/>
       <c r="D36" s="6" t="n"/>
       <c r="E36" s="6" t="n"/>
-      <c r="F36" s="5" t="n"/>
+      <c r="F36" s="6" t="n"/>
       <c r="G36" s="5" t="n"/>
-      <c r="H36" s="6" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="6" t="n"/>
     </row>
     <row r="37" outlineLevel="2">
       <c r="A37" s="4" t="n">
@@ -942,9 +991,10 @@
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
       <c r="E37" s="6" t="n"/>
-      <c r="F37" s="5" t="n"/>
+      <c r="F37" s="6" t="n"/>
       <c r="G37" s="5" t="n"/>
-      <c r="H37" s="6" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="6" t="n"/>
     </row>
     <row r="38" outlineLevel="1">
       <c r="A38" s="4" t="n">
@@ -954,9 +1004,10 @@
       <c r="C38" s="6" t="n"/>
       <c r="D38" s="6" t="n"/>
       <c r="E38" s="6" t="n"/>
-      <c r="F38" s="5" t="n"/>
+      <c r="F38" s="6" t="n"/>
       <c r="G38" s="5" t="n"/>
-      <c r="H38" s="6" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="6" t="n"/>
     </row>
     <row r="39" outlineLevel="2">
       <c r="A39" s="4" t="n">
@@ -966,9 +1017,10 @@
       <c r="C39" s="6" t="n"/>
       <c r="D39" s="6" t="n"/>
       <c r="E39" s="6" t="n"/>
-      <c r="F39" s="5" t="n"/>
+      <c r="F39" s="6" t="n"/>
       <c r="G39" s="5" t="n"/>
-      <c r="H39" s="6" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="6" t="n"/>
     </row>
     <row r="40" outlineLevel="2">
       <c r="A40" s="4" t="n">
@@ -978,9 +1030,10 @@
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
-      <c r="F40" s="5" t="n"/>
+      <c r="F40" s="6" t="n"/>
       <c r="G40" s="5" t="n"/>
-      <c r="H40" s="6" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="6" t="n"/>
     </row>
     <row r="41" outlineLevel="2">
       <c r="A41" s="4" t="n">
@@ -990,9 +1043,10 @@
       <c r="C41" s="6" t="n"/>
       <c r="D41" s="6" t="n"/>
       <c r="E41" s="6" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="F41" s="6" t="n"/>
       <c r="G41" s="5" t="n"/>
-      <c r="H41" s="6" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="6" t="n"/>
     </row>
     <row r="42" outlineLevel="1">
       <c r="A42" s="4" t="n">
@@ -1002,9 +1056,10 @@
       <c r="C42" s="6" t="n"/>
       <c r="D42" s="6" t="n"/>
       <c r="E42" s="6" t="n"/>
-      <c r="F42" s="5" t="n"/>
+      <c r="F42" s="6" t="n"/>
       <c r="G42" s="5" t="n"/>
-      <c r="H42" s="6" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="6" t="n"/>
     </row>
     <row r="43" outlineLevel="2">
       <c r="A43" s="4" t="n">
@@ -1014,9 +1069,10 @@
       <c r="C43" s="6" t="n"/>
       <c r="D43" s="6" t="n"/>
       <c r="E43" s="6" t="n"/>
-      <c r="F43" s="5" t="n"/>
+      <c r="F43" s="6" t="n"/>
       <c r="G43" s="5" t="n"/>
-      <c r="H43" s="6" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="6" t="n"/>
     </row>
     <row r="44" outlineLevel="2">
       <c r="A44" s="4" t="n">
@@ -1026,9 +1082,10 @@
       <c r="C44" s="6" t="n"/>
       <c r="D44" s="6" t="n"/>
       <c r="E44" s="6" t="n"/>
-      <c r="F44" s="5" t="n"/>
+      <c r="F44" s="6" t="n"/>
       <c r="G44" s="5" t="n"/>
-      <c r="H44" s="6" t="n"/>
+      <c r="H44" s="5" t="n"/>
+      <c r="I44" s="6" t="n"/>
     </row>
     <row r="45" outlineLevel="2">
       <c r="A45" s="4" t="n">
@@ -1038,9 +1095,10 @@
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
-      <c r="F45" s="5" t="n"/>
+      <c r="F45" s="6" t="n"/>
       <c r="G45" s="5" t="n"/>
-      <c r="H45" s="6" t="n"/>
+      <c r="H45" s="5" t="n"/>
+      <c r="I45" s="6" t="n"/>
     </row>
     <row r="46" outlineLevel="1">
       <c r="A46" s="4" t="n">
@@ -1050,9 +1108,10 @@
       <c r="C46" s="6" t="n"/>
       <c r="D46" s="6" t="n"/>
       <c r="E46" s="6" t="n"/>
-      <c r="F46" s="5" t="n"/>
+      <c r="F46" s="6" t="n"/>
       <c r="G46" s="5" t="n"/>
-      <c r="H46" s="6" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="6" t="n"/>
     </row>
     <row r="47" outlineLevel="2">
       <c r="A47" s="4" t="n">
@@ -1062,9 +1121,10 @@
       <c r="C47" s="6" t="n"/>
       <c r="D47" s="6" t="n"/>
       <c r="E47" s="6" t="n"/>
-      <c r="F47" s="5" t="n"/>
+      <c r="F47" s="6" t="n"/>
       <c r="G47" s="5" t="n"/>
-      <c r="H47" s="6" t="n"/>
+      <c r="H47" s="5" t="n"/>
+      <c r="I47" s="6" t="n"/>
     </row>
     <row r="48" outlineLevel="2">
       <c r="A48" s="4" t="n">
@@ -1074,9 +1134,10 @@
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6" t="n"/>
       <c r="E48" s="6" t="n"/>
-      <c r="F48" s="5" t="n"/>
+      <c r="F48" s="6" t="n"/>
       <c r="G48" s="5" t="n"/>
-      <c r="H48" s="6" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="6" t="n"/>
     </row>
     <row r="49" outlineLevel="2">
       <c r="A49" s="4" t="n">
@@ -1086,9 +1147,10 @@
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="6" t="n"/>
       <c r="E49" s="6" t="n"/>
-      <c r="F49" s="5" t="n"/>
+      <c r="F49" s="6" t="n"/>
       <c r="G49" s="5" t="n"/>
-      <c r="H49" s="6" t="n"/>
+      <c r="H49" s="5" t="n"/>
+      <c r="I49" s="6" t="n"/>
     </row>
     <row r="50" outlineLevel="1">
       <c r="A50" s="4" t="n">
@@ -1098,9 +1160,10 @@
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="6" t="n"/>
       <c r="E50" s="6" t="n"/>
-      <c r="F50" s="5" t="n"/>
+      <c r="F50" s="6" t="n"/>
       <c r="G50" s="5" t="n"/>
-      <c r="H50" s="6" t="n"/>
+      <c r="H50" s="5" t="n"/>
+      <c r="I50" s="6" t="n"/>
     </row>
     <row r="51" outlineLevel="2">
       <c r="A51" s="4" t="n">
@@ -1110,9 +1173,10 @@
       <c r="C51" s="6" t="n"/>
       <c r="D51" s="6" t="n"/>
       <c r="E51" s="6" t="n"/>
-      <c r="F51" s="5" t="n"/>
+      <c r="F51" s="6" t="n"/>
       <c r="G51" s="5" t="n"/>
-      <c r="H51" s="6" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="6" t="n"/>
     </row>
     <row r="52" outlineLevel="2">
       <c r="A52" s="4" t="n">
@@ -1122,9 +1186,10 @@
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="6" t="n"/>
-      <c r="F52" s="5" t="n"/>
+      <c r="F52" s="6" t="n"/>
       <c r="G52" s="5" t="n"/>
-      <c r="H52" s="6" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="6" t="n"/>
     </row>
     <row r="53" outlineLevel="2">
       <c r="A53" s="4" t="n">
@@ -1134,9 +1199,10 @@
       <c r="C53" s="6" t="n"/>
       <c r="D53" s="6" t="n"/>
       <c r="E53" s="6" t="n"/>
-      <c r="F53" s="5" t="n"/>
+      <c r="F53" s="6" t="n"/>
       <c r="G53" s="5" t="n"/>
-      <c r="H53" s="6" t="n"/>
+      <c r="H53" s="5" t="n"/>
+      <c r="I53" s="6" t="n"/>
     </row>
     <row r="54" outlineLevel="1">
       <c r="A54" s="4" t="n">
@@ -1146,9 +1212,10 @@
       <c r="C54" s="6" t="n"/>
       <c r="D54" s="6" t="n"/>
       <c r="E54" s="6" t="n"/>
-      <c r="F54" s="5" t="n"/>
+      <c r="F54" s="6" t="n"/>
       <c r="G54" s="5" t="n"/>
-      <c r="H54" s="6" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="6" t="n"/>
     </row>
     <row r="55" outlineLevel="2">
       <c r="A55" s="4" t="n">
@@ -1158,9 +1225,10 @@
       <c r="C55" s="6" t="n"/>
       <c r="D55" s="6" t="n"/>
       <c r="E55" s="6" t="n"/>
-      <c r="F55" s="5" t="n"/>
+      <c r="F55" s="6" t="n"/>
       <c r="G55" s="5" t="n"/>
-      <c r="H55" s="6" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="6" t="n"/>
     </row>
     <row r="56" outlineLevel="2">
       <c r="A56" s="4" t="n">
@@ -1170,9 +1238,10 @@
       <c r="C56" s="6" t="n"/>
       <c r="D56" s="6" t="n"/>
       <c r="E56" s="6" t="n"/>
-      <c r="F56" s="5" t="n"/>
+      <c r="F56" s="6" t="n"/>
       <c r="G56" s="5" t="n"/>
-      <c r="H56" s="6" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="6" t="n"/>
     </row>
     <row r="57" outlineLevel="2">
       <c r="A57" s="4" t="n">
@@ -1182,9 +1251,10 @@
       <c r="C57" s="6" t="n"/>
       <c r="D57" s="6" t="n"/>
       <c r="E57" s="6" t="n"/>
-      <c r="F57" s="5" t="n"/>
+      <c r="F57" s="6" t="n"/>
       <c r="G57" s="5" t="n"/>
-      <c r="H57" s="6" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="6" t="n"/>
     </row>
     <row r="58" outlineLevel="1" ht="28.8" customHeight="1">
       <c r="A58" s="4" t="n">
@@ -1198,9 +1268,10 @@
       </c>
       <c r="D58" s="6" t="n"/>
       <c r="E58" s="6" t="n"/>
-      <c r="F58" s="5" t="n"/>
+      <c r="F58" s="6" t="n"/>
       <c r="G58" s="5" t="n"/>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>progBlack(7170, 2)</t>
         </is>
@@ -1214,9 +1285,10 @@
       <c r="C59" s="6" t="n"/>
       <c r="D59" s="6" t="n"/>
       <c r="E59" s="6" t="n"/>
-      <c r="F59" s="5" t="n"/>
+      <c r="F59" s="6" t="n"/>
       <c r="G59" s="5" t="n"/>
-      <c r="H59" s="6" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="6" t="n"/>
     </row>
     <row r="60" outlineLevel="2">
       <c r="A60" s="4" t="n">
@@ -1226,9 +1298,10 @@
       <c r="C60" s="6" t="n"/>
       <c r="D60" s="6" t="n"/>
       <c r="E60" s="6" t="n"/>
-      <c r="F60" s="5" t="n"/>
+      <c r="F60" s="6" t="n"/>
       <c r="G60" s="5" t="n"/>
-      <c r="H60" s="6" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="6" t="n"/>
     </row>
     <row r="61" outlineLevel="2">
       <c r="A61" s="4" t="n">
@@ -1238,9 +1311,10 @@
       <c r="C61" s="6" t="n"/>
       <c r="D61" s="6" t="n"/>
       <c r="E61" s="6" t="n"/>
-      <c r="F61" s="5" t="n"/>
+      <c r="F61" s="6" t="n"/>
       <c r="G61" s="5" t="n"/>
-      <c r="H61" s="6" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="6" t="n"/>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="4" t="n">
@@ -1250,9 +1324,10 @@
       <c r="C62" s="6" t="n"/>
       <c r="D62" s="6" t="n"/>
       <c r="E62" s="6" t="n"/>
-      <c r="F62" s="5" t="n"/>
+      <c r="F62" s="6" t="n"/>
       <c r="G62" s="5" t="n"/>
-      <c r="H62" s="6" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="6" t="n"/>
     </row>
     <row r="63" outlineLevel="2">
       <c r="A63" s="4" t="n">
@@ -1262,9 +1337,10 @@
       <c r="C63" s="6" t="n"/>
       <c r="D63" s="6" t="n"/>
       <c r="E63" s="6" t="n"/>
-      <c r="F63" s="5" t="n"/>
+      <c r="F63" s="6" t="n"/>
       <c r="G63" s="5" t="n"/>
-      <c r="H63" s="6" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="6" t="n"/>
     </row>
     <row r="64" outlineLevel="2">
       <c r="A64" s="4" t="n">
@@ -1274,9 +1350,10 @@
       <c r="C64" s="6" t="n"/>
       <c r="D64" s="6" t="n"/>
       <c r="E64" s="6" t="n"/>
-      <c r="F64" s="5" t="n"/>
+      <c r="F64" s="6" t="n"/>
       <c r="G64" s="5" t="n"/>
-      <c r="H64" s="6" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="6" t="n"/>
     </row>
     <row r="65" outlineLevel="2">
       <c r="A65" s="4" t="n">
@@ -1286,9 +1363,10 @@
       <c r="C65" s="6" t="n"/>
       <c r="D65" s="6" t="n"/>
       <c r="E65" s="6" t="n"/>
-      <c r="F65" s="5" t="n"/>
+      <c r="F65" s="6" t="n"/>
       <c r="G65" s="5" t="n"/>
-      <c r="H65" s="6" t="n"/>
+      <c r="H65" s="5" t="n"/>
+      <c r="I65" s="6" t="n"/>
     </row>
     <row r="66" outlineLevel="1">
       <c r="A66" s="4" t="n">
@@ -1298,9 +1376,10 @@
       <c r="C66" s="6" t="n"/>
       <c r="D66" s="6" t="n"/>
       <c r="E66" s="6" t="n"/>
-      <c r="F66" s="5" t="n"/>
+      <c r="F66" s="6" t="n"/>
       <c r="G66" s="5" t="n"/>
-      <c r="H66" s="6" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="6" t="n"/>
     </row>
     <row r="67" outlineLevel="2">
       <c r="A67" s="4" t="n">
@@ -1310,9 +1389,10 @@
       <c r="C67" s="6" t="n"/>
       <c r="D67" s="6" t="n"/>
       <c r="E67" s="6" t="n"/>
-      <c r="F67" s="5" t="n"/>
+      <c r="F67" s="6" t="n"/>
       <c r="G67" s="5" t="n"/>
-      <c r="H67" s="6" t="n"/>
+      <c r="H67" s="5" t="n"/>
+      <c r="I67" s="6" t="n"/>
     </row>
     <row r="68" outlineLevel="2">
       <c r="A68" s="4" t="n">
@@ -1322,9 +1402,10 @@
       <c r="C68" s="6" t="n"/>
       <c r="D68" s="6" t="n"/>
       <c r="E68" s="6" t="n"/>
-      <c r="F68" s="5" t="n"/>
+      <c r="F68" s="6" t="n"/>
       <c r="G68" s="5" t="n"/>
-      <c r="H68" s="6" t="n"/>
+      <c r="H68" s="5" t="n"/>
+      <c r="I68" s="6" t="n"/>
     </row>
     <row r="69" outlineLevel="2">
       <c r="A69" s="4" t="n">
@@ -1334,9 +1415,10 @@
       <c r="C69" s="6" t="n"/>
       <c r="D69" s="6" t="n"/>
       <c r="E69" s="6" t="n"/>
-      <c r="F69" s="5" t="n"/>
+      <c r="F69" s="6" t="n"/>
       <c r="G69" s="5" t="n"/>
-      <c r="H69" s="6" t="n"/>
+      <c r="H69" s="5" t="n"/>
+      <c r="I69" s="6" t="n"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="4" t="n">
@@ -1346,9 +1428,10 @@
       <c r="C70" s="6" t="n"/>
       <c r="D70" s="6" t="n"/>
       <c r="E70" s="6" t="n"/>
-      <c r="F70" s="5" t="n"/>
+      <c r="F70" s="6" t="n"/>
       <c r="G70" s="5" t="n"/>
-      <c r="H70" s="6" t="n"/>
+      <c r="H70" s="5" t="n"/>
+      <c r="I70" s="6" t="n"/>
     </row>
     <row r="71" outlineLevel="2">
       <c r="A71" s="4" t="n">
@@ -1358,9 +1441,10 @@
       <c r="C71" s="6" t="n"/>
       <c r="D71" s="6" t="n"/>
       <c r="E71" s="6" t="n"/>
-      <c r="F71" s="5" t="n"/>
+      <c r="F71" s="6" t="n"/>
       <c r="G71" s="5" t="n"/>
-      <c r="H71" s="6" t="n"/>
+      <c r="H71" s="5" t="n"/>
+      <c r="I71" s="6" t="n"/>
     </row>
     <row r="72" outlineLevel="2">
       <c r="A72" s="4" t="n">
@@ -1370,9 +1454,10 @@
       <c r="C72" s="6" t="n"/>
       <c r="D72" s="6" t="n"/>
       <c r="E72" s="6" t="n"/>
-      <c r="F72" s="5" t="n"/>
+      <c r="F72" s="6" t="n"/>
       <c r="G72" s="5" t="n"/>
-      <c r="H72" s="6" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="6" t="n"/>
     </row>
     <row r="73" ht="43.2" customHeight="1">
       <c r="A73" s="4" t="n">
@@ -1392,12 +1477,13 @@
       </c>
       <c r="D73" s="6" t="n"/>
       <c r="E73" s="6" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5">
+      <c r="F73" s="6" t="n"/>
+      <c r="G73" s="5" t="n"/>
+      <c r="H73" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>progStrobo(530, 4, 50, getRandomCRGB())</t>
         </is>
@@ -1421,12 +1507,13 @@
       </c>
       <c r="D74" s="6" t="n"/>
       <c r="E74" s="6" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5">
+      <c r="F74" s="6" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H74" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(8495, 970, 6, 5, 26, 5, true, 3)</t>
         </is>
@@ -1440,9 +1527,10 @@
       <c r="C75" s="6" t="n"/>
       <c r="D75" s="6" t="n"/>
       <c r="E75" s="6" t="n"/>
-      <c r="F75" s="5" t="n"/>
+      <c r="F75" s="6" t="n"/>
       <c r="G75" s="5" t="n"/>
-      <c r="H75" s="6" t="n"/>
+      <c r="H75" s="5" t="n"/>
+      <c r="I75" s="6" t="n"/>
     </row>
     <row r="76" outlineLevel="2">
       <c r="A76" s="4" t="n">
@@ -1452,9 +1540,10 @@
       <c r="C76" s="6" t="n"/>
       <c r="D76" s="6" t="n"/>
       <c r="E76" s="6" t="n"/>
-      <c r="F76" s="5" t="n"/>
+      <c r="F76" s="6" t="n"/>
       <c r="G76" s="5" t="n"/>
-      <c r="H76" s="6" t="n"/>
+      <c r="H76" s="5" t="n"/>
+      <c r="I76" s="6" t="n"/>
     </row>
     <row r="77" outlineLevel="2">
       <c r="A77" s="4" t="n">
@@ -1464,9 +1553,10 @@
       <c r="C77" s="6" t="n"/>
       <c r="D77" s="6" t="n"/>
       <c r="E77" s="6" t="n"/>
-      <c r="F77" s="5" t="n"/>
+      <c r="F77" s="6" t="n"/>
       <c r="G77" s="5" t="n"/>
-      <c r="H77" s="6" t="n"/>
+      <c r="H77" s="5" t="n"/>
+      <c r="I77" s="6" t="n"/>
     </row>
     <row r="78" outlineLevel="1">
       <c r="A78" s="4" t="n">
@@ -1476,9 +1566,10 @@
       <c r="C78" s="6" t="n"/>
       <c r="D78" s="6" t="n"/>
       <c r="E78" s="6" t="n"/>
-      <c r="F78" s="5" t="n"/>
+      <c r="F78" s="6" t="n"/>
       <c r="G78" s="5" t="n"/>
-      <c r="H78" s="6" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="6" t="n"/>
     </row>
     <row r="79" outlineLevel="2">
       <c r="A79" s="4" t="n">
@@ -1488,9 +1579,10 @@
       <c r="C79" s="6" t="n"/>
       <c r="D79" s="6" t="n"/>
       <c r="E79" s="6" t="n"/>
-      <c r="F79" s="5" t="n"/>
+      <c r="F79" s="6" t="n"/>
       <c r="G79" s="5" t="n"/>
-      <c r="H79" s="6" t="n"/>
+      <c r="H79" s="5" t="n"/>
+      <c r="I79" s="6" t="n"/>
     </row>
     <row r="80" outlineLevel="2">
       <c r="A80" s="4" t="n">
@@ -1500,9 +1592,10 @@
       <c r="C80" s="6" t="n"/>
       <c r="D80" s="6" t="n"/>
       <c r="E80" s="6" t="n"/>
-      <c r="F80" s="5" t="n"/>
+      <c r="F80" s="6" t="n"/>
       <c r="G80" s="5" t="n"/>
-      <c r="H80" s="6" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="6" t="n"/>
     </row>
     <row r="81" outlineLevel="2">
       <c r="A81" s="4" t="n">
@@ -1512,9 +1605,10 @@
       <c r="C81" s="6" t="n"/>
       <c r="D81" s="6" t="n"/>
       <c r="E81" s="6" t="n"/>
-      <c r="F81" s="5" t="n"/>
+      <c r="F81" s="6" t="n"/>
       <c r="G81" s="5" t="n"/>
-      <c r="H81" s="6" t="n"/>
+      <c r="H81" s="5" t="n"/>
+      <c r="I81" s="6" t="n"/>
     </row>
     <row r="82" outlineLevel="1">
       <c r="A82" s="4" t="n">
@@ -1524,9 +1618,10 @@
       <c r="C82" s="6" t="n"/>
       <c r="D82" s="6" t="n"/>
       <c r="E82" s="6" t="n"/>
-      <c r="F82" s="5" t="n"/>
+      <c r="F82" s="6" t="n"/>
       <c r="G82" s="5" t="n"/>
-      <c r="H82" s="6" t="n"/>
+      <c r="H82" s="5" t="n"/>
+      <c r="I82" s="6" t="n"/>
     </row>
     <row r="83" outlineLevel="2">
       <c r="A83" s="4" t="n">
@@ -1536,9 +1631,10 @@
       <c r="C83" s="6" t="n"/>
       <c r="D83" s="6" t="n"/>
       <c r="E83" s="6" t="n"/>
-      <c r="F83" s="5" t="n"/>
+      <c r="F83" s="6" t="n"/>
       <c r="G83" s="5" t="n"/>
-      <c r="H83" s="6" t="n"/>
+      <c r="H83" s="5" t="n"/>
+      <c r="I83" s="6" t="n"/>
     </row>
     <row r="84" outlineLevel="2">
       <c r="A84" s="4" t="n">
@@ -1548,9 +1644,10 @@
       <c r="C84" s="6" t="n"/>
       <c r="D84" s="6" t="n"/>
       <c r="E84" s="6" t="n"/>
-      <c r="F84" s="5" t="n"/>
+      <c r="F84" s="6" t="n"/>
       <c r="G84" s="5" t="n"/>
-      <c r="H84" s="6" t="n"/>
+      <c r="H84" s="5" t="n"/>
+      <c r="I84" s="6" t="n"/>
     </row>
     <row r="85" outlineLevel="2">
       <c r="A85" s="4" t="n">
@@ -1560,9 +1657,10 @@
       <c r="C85" s="6" t="n"/>
       <c r="D85" s="6" t="n"/>
       <c r="E85" s="6" t="n"/>
-      <c r="F85" s="5" t="n"/>
+      <c r="F85" s="6" t="n"/>
       <c r="G85" s="5" t="n"/>
-      <c r="H85" s="6" t="n"/>
+      <c r="H85" s="5" t="n"/>
+      <c r="I85" s="6" t="n"/>
     </row>
     <row r="86" outlineLevel="1">
       <c r="A86" s="4" t="n">
@@ -1572,9 +1670,10 @@
       <c r="C86" s="6" t="n"/>
       <c r="D86" s="6" t="n"/>
       <c r="E86" s="6" t="n"/>
-      <c r="F86" s="5" t="n"/>
+      <c r="F86" s="6" t="n"/>
       <c r="G86" s="5" t="n"/>
-      <c r="H86" s="6" t="n"/>
+      <c r="H86" s="5" t="n"/>
+      <c r="I86" s="6" t="n"/>
     </row>
     <row r="87" outlineLevel="2">
       <c r="A87" s="4" t="n">
@@ -1584,9 +1683,10 @@
       <c r="C87" s="6" t="n"/>
       <c r="D87" s="6" t="n"/>
       <c r="E87" s="6" t="n"/>
-      <c r="F87" s="5" t="n"/>
+      <c r="F87" s="6" t="n"/>
       <c r="G87" s="5" t="n"/>
-      <c r="H87" s="6" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="6" t="n"/>
     </row>
     <row r="88" outlineLevel="2">
       <c r="A88" s="4" t="n">
@@ -1596,9 +1696,10 @@
       <c r="C88" s="6" t="n"/>
       <c r="D88" s="6" t="n"/>
       <c r="E88" s="6" t="n"/>
-      <c r="F88" s="5" t="n"/>
+      <c r="F88" s="6" t="n"/>
       <c r="G88" s="5" t="n"/>
-      <c r="H88" s="6" t="n"/>
+      <c r="H88" s="5" t="n"/>
+      <c r="I88" s="6" t="n"/>
     </row>
     <row r="89" outlineLevel="2">
       <c r="A89" s="4" t="n">
@@ -1608,9 +1709,10 @@
       <c r="C89" s="6" t="n"/>
       <c r="D89" s="6" t="n"/>
       <c r="E89" s="6" t="n"/>
-      <c r="F89" s="5" t="n"/>
+      <c r="F89" s="6" t="n"/>
       <c r="G89" s="5" t="n"/>
-      <c r="H89" s="6" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="6" t="n"/>
     </row>
     <row r="90" ht="28.8" customHeight="1">
       <c r="A90" s="4" t="n">
@@ -1629,12 +1731,13 @@
       </c>
       <c r="D90" s="6" t="n"/>
       <c r="E90" s="6" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5">
+      <c r="F90" s="6" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 10)</t>
         </is>
@@ -1648,9 +1751,10 @@
       <c r="C91" s="6" t="n"/>
       <c r="D91" s="6" t="n"/>
       <c r="E91" s="6" t="n"/>
-      <c r="F91" s="5" t="n"/>
+      <c r="F91" s="6" t="n"/>
       <c r="G91" s="5" t="n"/>
-      <c r="H91" s="6" t="n"/>
+      <c r="H91" s="5" t="n"/>
+      <c r="I91" s="6" t="n"/>
     </row>
     <row r="92" outlineLevel="2">
       <c r="A92" s="4" t="n">
@@ -1660,9 +1764,10 @@
       <c r="C92" s="6" t="n"/>
       <c r="D92" s="6" t="n"/>
       <c r="E92" s="6" t="n"/>
-      <c r="F92" s="5" t="n"/>
+      <c r="F92" s="6" t="n"/>
       <c r="G92" s="5" t="n"/>
-      <c r="H92" s="6" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="6" t="n"/>
     </row>
     <row r="93" outlineLevel="2">
       <c r="A93" s="4" t="n">
@@ -1672,9 +1777,10 @@
       <c r="C93" s="6" t="n"/>
       <c r="D93" s="6" t="n"/>
       <c r="E93" s="6" t="n"/>
-      <c r="F93" s="5" t="n"/>
+      <c r="F93" s="6" t="n"/>
       <c r="G93" s="5" t="n"/>
-      <c r="H93" s="6" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="6" t="n"/>
     </row>
     <row r="94" outlineLevel="1">
       <c r="A94" s="4" t="n">
@@ -1684,9 +1790,10 @@
       <c r="C94" s="6" t="n"/>
       <c r="D94" s="6" t="n"/>
       <c r="E94" s="6" t="n"/>
-      <c r="F94" s="5" t="n"/>
+      <c r="F94" s="6" t="n"/>
       <c r="G94" s="5" t="n"/>
-      <c r="H94" s="6" t="n"/>
+      <c r="H94" s="5" t="n"/>
+      <c r="I94" s="6" t="n"/>
     </row>
     <row r="95" outlineLevel="2">
       <c r="A95" s="4" t="n">
@@ -1696,9 +1803,10 @@
       <c r="C95" s="6" t="n"/>
       <c r="D95" s="6" t="n"/>
       <c r="E95" s="6" t="n"/>
-      <c r="F95" s="5" t="n"/>
+      <c r="F95" s="6" t="n"/>
       <c r="G95" s="5" t="n"/>
-      <c r="H95" s="6" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="6" t="n"/>
     </row>
     <row r="96" outlineLevel="2">
       <c r="A96" s="4" t="n">
@@ -1708,9 +1816,10 @@
       <c r="C96" s="6" t="n"/>
       <c r="D96" s="6" t="n"/>
       <c r="E96" s="6" t="n"/>
-      <c r="F96" s="5" t="n"/>
+      <c r="F96" s="6" t="n"/>
       <c r="G96" s="5" t="n"/>
-      <c r="H96" s="6" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="6" t="n"/>
     </row>
     <row r="97" outlineLevel="2">
       <c r="A97" s="4" t="n">
@@ -1720,9 +1829,10 @@
       <c r="C97" s="6" t="n"/>
       <c r="D97" s="6" t="n"/>
       <c r="E97" s="6" t="n"/>
-      <c r="F97" s="5" t="n"/>
+      <c r="F97" s="6" t="n"/>
       <c r="G97" s="5" t="n"/>
-      <c r="H97" s="6" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="6" t="n"/>
     </row>
     <row r="98" outlineLevel="1">
       <c r="A98" s="4" t="n">
@@ -1732,9 +1842,10 @@
       <c r="C98" s="6" t="n"/>
       <c r="D98" s="6" t="n"/>
       <c r="E98" s="6" t="n"/>
-      <c r="F98" s="5" t="n"/>
+      <c r="F98" s="6" t="n"/>
       <c r="G98" s="5" t="n"/>
-      <c r="H98" s="6" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="6" t="n"/>
     </row>
     <row r="99" outlineLevel="2">
       <c r="A99" s="4" t="n">
@@ -1744,9 +1855,10 @@
       <c r="C99" s="6" t="n"/>
       <c r="D99" s="6" t="n"/>
       <c r="E99" s="6" t="n"/>
-      <c r="F99" s="5" t="n"/>
+      <c r="F99" s="6" t="n"/>
       <c r="G99" s="5" t="n"/>
-      <c r="H99" s="6" t="n"/>
+      <c r="H99" s="5" t="n"/>
+      <c r="I99" s="6" t="n"/>
     </row>
     <row r="100" outlineLevel="2">
       <c r="A100" s="4" t="n">
@@ -1756,9 +1868,10 @@
       <c r="C100" s="6" t="n"/>
       <c r="D100" s="6" t="n"/>
       <c r="E100" s="6" t="n"/>
-      <c r="F100" s="5" t="n"/>
+      <c r="F100" s="6" t="n"/>
       <c r="G100" s="5" t="n"/>
-      <c r="H100" s="6" t="n"/>
+      <c r="H100" s="5" t="n"/>
+      <c r="I100" s="6" t="n"/>
     </row>
     <row r="101" outlineLevel="2">
       <c r="A101" s="4" t="n">
@@ -1768,9 +1881,10 @@
       <c r="C101" s="6" t="n"/>
       <c r="D101" s="6" t="n"/>
       <c r="E101" s="6" t="n"/>
-      <c r="F101" s="5" t="n"/>
+      <c r="F101" s="6" t="n"/>
       <c r="G101" s="5" t="n"/>
-      <c r="H101" s="6" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="6" t="n"/>
     </row>
     <row r="102" outlineLevel="1">
       <c r="A102" s="4" t="n">
@@ -1780,9 +1894,10 @@
       <c r="C102" s="6" t="n"/>
       <c r="D102" s="6" t="n"/>
       <c r="E102" s="6" t="n"/>
-      <c r="F102" s="5" t="n"/>
+      <c r="F102" s="6" t="n"/>
       <c r="G102" s="5" t="n"/>
-      <c r="H102" s="6" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="6" t="n"/>
     </row>
     <row r="103" outlineLevel="2">
       <c r="A103" s="4" t="n">
@@ -1792,9 +1907,10 @@
       <c r="C103" s="6" t="n"/>
       <c r="D103" s="6" t="n"/>
       <c r="E103" s="6" t="n"/>
-      <c r="F103" s="5" t="n"/>
+      <c r="F103" s="6" t="n"/>
       <c r="G103" s="5" t="n"/>
-      <c r="H103" s="6" t="n"/>
+      <c r="H103" s="5" t="n"/>
+      <c r="I103" s="6" t="n"/>
     </row>
     <row r="104" outlineLevel="2">
       <c r="A104" s="4" t="n">
@@ -1804,9 +1920,10 @@
       <c r="C104" s="6" t="n"/>
       <c r="D104" s="6" t="n"/>
       <c r="E104" s="6" t="n"/>
-      <c r="F104" s="5" t="n"/>
+      <c r="F104" s="6" t="n"/>
       <c r="G104" s="5" t="n"/>
-      <c r="H104" s="6" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="6" t="n"/>
     </row>
     <row r="105" outlineLevel="2">
       <c r="A105" s="4" t="n">
@@ -1816,9 +1933,10 @@
       <c r="C105" s="6" t="n"/>
       <c r="D105" s="6" t="n"/>
       <c r="E105" s="6" t="n"/>
-      <c r="F105" s="5" t="n"/>
+      <c r="F105" s="6" t="n"/>
       <c r="G105" s="5" t="n"/>
-      <c r="H105" s="6" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="6" t="n"/>
     </row>
     <row r="106" ht="43.2" customHeight="1">
       <c r="A106" s="4" t="n">
@@ -1837,12 +1955,13 @@
       </c>
       <c r="D106" s="6" t="n"/>
       <c r="E106" s="6" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5">
+      <c r="F106" s="6" t="n"/>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>progPalette(16990, 3, 15)</t>
         </is>
@@ -1856,9 +1975,10 @@
       <c r="C107" s="6" t="n"/>
       <c r="D107" s="6" t="n"/>
       <c r="E107" s="6" t="n"/>
-      <c r="F107" s="5" t="n"/>
+      <c r="F107" s="6" t="n"/>
       <c r="G107" s="5" t="n"/>
-      <c r="H107" s="6" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="6" t="n"/>
     </row>
     <row r="108" outlineLevel="2">
       <c r="A108" s="4" t="n">
@@ -1868,9 +1988,10 @@
       <c r="C108" s="6" t="n"/>
       <c r="D108" s="6" t="n"/>
       <c r="E108" s="6" t="n"/>
-      <c r="F108" s="5" t="n"/>
+      <c r="F108" s="6" t="n"/>
       <c r="G108" s="5" t="n"/>
-      <c r="H108" s="6" t="n"/>
+      <c r="H108" s="5" t="n"/>
+      <c r="I108" s="6" t="n"/>
     </row>
     <row r="109" outlineLevel="2">
       <c r="A109" s="4" t="n">
@@ -1880,9 +2001,10 @@
       <c r="C109" s="6" t="n"/>
       <c r="D109" s="6" t="n"/>
       <c r="E109" s="6" t="n"/>
-      <c r="F109" s="5" t="n"/>
+      <c r="F109" s="6" t="n"/>
       <c r="G109" s="5" t="n"/>
-      <c r="H109" s="6" t="n"/>
+      <c r="H109" s="5" t="n"/>
+      <c r="I109" s="6" t="n"/>
     </row>
     <row r="110" outlineLevel="1">
       <c r="A110" s="4" t="n">
@@ -1892,9 +2014,10 @@
       <c r="C110" s="6" t="n"/>
       <c r="D110" s="6" t="n"/>
       <c r="E110" s="6" t="n"/>
-      <c r="F110" s="5" t="n"/>
+      <c r="F110" s="6" t="n"/>
       <c r="G110" s="5" t="n"/>
-      <c r="H110" s="6" t="n"/>
+      <c r="H110" s="5" t="n"/>
+      <c r="I110" s="6" t="n"/>
     </row>
     <row r="111" outlineLevel="2">
       <c r="A111" s="4" t="n">
@@ -1904,9 +2027,10 @@
       <c r="C111" s="6" t="n"/>
       <c r="D111" s="6" t="n"/>
       <c r="E111" s="6" t="n"/>
-      <c r="F111" s="5" t="n"/>
+      <c r="F111" s="6" t="n"/>
       <c r="G111" s="5" t="n"/>
-      <c r="H111" s="6" t="n"/>
+      <c r="H111" s="5" t="n"/>
+      <c r="I111" s="6" t="n"/>
     </row>
     <row r="112" outlineLevel="2">
       <c r="A112" s="4" t="n">
@@ -1916,9 +2040,10 @@
       <c r="C112" s="6" t="n"/>
       <c r="D112" s="6" t="n"/>
       <c r="E112" s="6" t="n"/>
-      <c r="F112" s="5" t="n"/>
+      <c r="F112" s="6" t="n"/>
       <c r="G112" s="5" t="n"/>
-      <c r="H112" s="6" t="n"/>
+      <c r="H112" s="5" t="n"/>
+      <c r="I112" s="6" t="n"/>
     </row>
     <row r="113" outlineLevel="2">
       <c r="A113" s="4" t="n">
@@ -1928,9 +2053,10 @@
       <c r="C113" s="6" t="n"/>
       <c r="D113" s="6" t="n"/>
       <c r="E113" s="6" t="n"/>
-      <c r="F113" s="5" t="n"/>
+      <c r="F113" s="6" t="n"/>
       <c r="G113" s="5" t="n"/>
-      <c r="H113" s="6" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="6" t="n"/>
     </row>
     <row r="114" outlineLevel="1">
       <c r="A114" s="4" t="n">
@@ -1940,9 +2066,10 @@
       <c r="C114" s="6" t="n"/>
       <c r="D114" s="6" t="n"/>
       <c r="E114" s="6" t="n"/>
-      <c r="F114" s="5" t="n"/>
+      <c r="F114" s="6" t="n"/>
       <c r="G114" s="5" t="n"/>
-      <c r="H114" s="6" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="6" t="n"/>
     </row>
     <row r="115" outlineLevel="2">
       <c r="A115" s="4" t="n">
@@ -1952,9 +2079,10 @@
       <c r="C115" s="6" t="n"/>
       <c r="D115" s="6" t="n"/>
       <c r="E115" s="6" t="n"/>
-      <c r="F115" s="5" t="n"/>
+      <c r="F115" s="6" t="n"/>
       <c r="G115" s="5" t="n"/>
-      <c r="H115" s="6" t="n"/>
+      <c r="H115" s="5" t="n"/>
+      <c r="I115" s="6" t="n"/>
     </row>
     <row r="116" outlineLevel="2">
       <c r="A116" s="4" t="n">
@@ -1964,9 +2092,10 @@
       <c r="C116" s="6" t="n"/>
       <c r="D116" s="6" t="n"/>
       <c r="E116" s="6" t="n"/>
-      <c r="F116" s="5" t="n"/>
+      <c r="F116" s="6" t="n"/>
       <c r="G116" s="5" t="n"/>
-      <c r="H116" s="6" t="n"/>
+      <c r="H116" s="5" t="n"/>
+      <c r="I116" s="6" t="n"/>
     </row>
     <row r="117" outlineLevel="2">
       <c r="A117" s="4" t="n">
@@ -1976,9 +2105,10 @@
       <c r="C117" s="6" t="n"/>
       <c r="D117" s="6" t="n"/>
       <c r="E117" s="6" t="n"/>
-      <c r="F117" s="5" t="n"/>
+      <c r="F117" s="6" t="n"/>
       <c r="G117" s="5" t="n"/>
-      <c r="H117" s="6" t="n"/>
+      <c r="H117" s="5" t="n"/>
+      <c r="I117" s="6" t="n"/>
     </row>
     <row r="118" outlineLevel="1">
       <c r="A118" s="4" t="n">
@@ -1988,9 +2118,10 @@
       <c r="C118" s="6" t="n"/>
       <c r="D118" s="6" t="n"/>
       <c r="E118" s="6" t="n"/>
-      <c r="F118" s="5" t="n"/>
+      <c r="F118" s="6" t="n"/>
       <c r="G118" s="5" t="n"/>
-      <c r="H118" s="6" t="n"/>
+      <c r="H118" s="5" t="n"/>
+      <c r="I118" s="6" t="n"/>
     </row>
     <row r="119" outlineLevel="2">
       <c r="A119" s="4" t="n">
@@ -2000,9 +2131,10 @@
       <c r="C119" s="6" t="n"/>
       <c r="D119" s="6" t="n"/>
       <c r="E119" s="6" t="n"/>
-      <c r="F119" s="5" t="n"/>
+      <c r="F119" s="6" t="n"/>
       <c r="G119" s="5" t="n"/>
-      <c r="H119" s="6" t="n"/>
+      <c r="H119" s="5" t="n"/>
+      <c r="I119" s="6" t="n"/>
     </row>
     <row r="120" outlineLevel="2">
       <c r="A120" s="4" t="n">
@@ -2012,9 +2144,10 @@
       <c r="C120" s="6" t="n"/>
       <c r="D120" s="6" t="n"/>
       <c r="E120" s="6" t="n"/>
-      <c r="F120" s="5" t="n"/>
+      <c r="F120" s="6" t="n"/>
       <c r="G120" s="5" t="n"/>
-      <c r="H120" s="6" t="n"/>
+      <c r="H120" s="5" t="n"/>
+      <c r="I120" s="6" t="n"/>
     </row>
     <row r="121" outlineLevel="2">
       <c r="A121" s="4" t="n">
@@ -2024,9 +2157,10 @@
       <c r="C121" s="6" t="n"/>
       <c r="D121" s="6" t="n"/>
       <c r="E121" s="6" t="n"/>
-      <c r="F121" s="5" t="n"/>
+      <c r="F121" s="6" t="n"/>
       <c r="G121" s="5" t="n"/>
-      <c r="H121" s="6" t="n"/>
+      <c r="H121" s="5" t="n"/>
+      <c r="I121" s="6" t="n"/>
     </row>
     <row r="122" outlineLevel="1">
       <c r="A122" s="4" t="n">
@@ -2036,9 +2170,10 @@
       <c r="C122" s="6" t="n"/>
       <c r="D122" s="6" t="n"/>
       <c r="E122" s="6" t="n"/>
-      <c r="F122" s="5" t="n"/>
+      <c r="F122" s="6" t="n"/>
       <c r="G122" s="5" t="n"/>
-      <c r="H122" s="6" t="n"/>
+      <c r="H122" s="5" t="n"/>
+      <c r="I122" s="6" t="n"/>
     </row>
     <row r="123" outlineLevel="2">
       <c r="A123" s="4" t="n">
@@ -2048,9 +2183,10 @@
       <c r="C123" s="6" t="n"/>
       <c r="D123" s="6" t="n"/>
       <c r="E123" s="6" t="n"/>
-      <c r="F123" s="5" t="n"/>
+      <c r="F123" s="6" t="n"/>
       <c r="G123" s="5" t="n"/>
-      <c r="H123" s="6" t="n"/>
+      <c r="H123" s="5" t="n"/>
+      <c r="I123" s="6" t="n"/>
     </row>
     <row r="124" outlineLevel="2">
       <c r="A124" s="4" t="n">
@@ -2060,9 +2196,10 @@
       <c r="C124" s="6" t="n"/>
       <c r="D124" s="6" t="n"/>
       <c r="E124" s="6" t="n"/>
-      <c r="F124" s="5" t="n"/>
+      <c r="F124" s="6" t="n"/>
       <c r="G124" s="5" t="n"/>
-      <c r="H124" s="6" t="n"/>
+      <c r="H124" s="5" t="n"/>
+      <c r="I124" s="6" t="n"/>
     </row>
     <row r="125" outlineLevel="2">
       <c r="A125" s="4" t="n">
@@ -2070,10 +2207,11 @@
       </c>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="5" t="n"/>
+      <c r="D125" s="6" t="n"/>
+      <c r="F125" s="6" t="n"/>
       <c r="G125" s="5" t="n"/>
-      <c r="H125" s="6" t="n"/>
+      <c r="H125" s="5" t="n"/>
+      <c r="I125" s="6" t="n"/>
     </row>
     <row r="126" outlineLevel="1">
       <c r="A126" s="4" t="n">
@@ -2083,9 +2221,10 @@
       <c r="C126" s="6" t="n"/>
       <c r="D126" s="6" t="n"/>
       <c r="E126" s="6" t="n"/>
-      <c r="F126" s="5" t="n"/>
+      <c r="F126" s="6" t="n"/>
       <c r="G126" s="5" t="n"/>
-      <c r="H126" s="6" t="n"/>
+      <c r="H126" s="5" t="n"/>
+      <c r="I126" s="6" t="n"/>
     </row>
     <row r="127" outlineLevel="2">
       <c r="A127" s="4" t="n">
@@ -2095,9 +2234,10 @@
       <c r="C127" s="6" t="n"/>
       <c r="D127" s="6" t="n"/>
       <c r="E127" s="6" t="n"/>
-      <c r="F127" s="5" t="n"/>
+      <c r="F127" s="6" t="n"/>
       <c r="G127" s="5" t="n"/>
-      <c r="H127" s="6" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="6" t="n"/>
     </row>
     <row r="128" outlineLevel="2">
       <c r="A128" s="4" t="n">
@@ -2107,9 +2247,10 @@
       <c r="C128" s="6" t="n"/>
       <c r="D128" s="6" t="n"/>
       <c r="E128" s="6" t="n"/>
-      <c r="F128" s="5" t="n"/>
+      <c r="F128" s="6" t="n"/>
       <c r="G128" s="5" t="n"/>
-      <c r="H128" s="6" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="6" t="n"/>
     </row>
     <row r="129" outlineLevel="2">
       <c r="A129" s="4" t="n">
@@ -2119,9 +2260,10 @@
       <c r="C129" s="6" t="n"/>
       <c r="D129" s="6" t="n"/>
       <c r="E129" s="6" t="n"/>
-      <c r="F129" s="5" t="n"/>
+      <c r="F129" s="6" t="n"/>
       <c r="G129" s="5" t="n"/>
-      <c r="H129" s="6" t="n"/>
+      <c r="H129" s="5" t="n"/>
+      <c r="I129" s="6" t="n"/>
     </row>
     <row r="130" outlineLevel="1">
       <c r="A130" s="4" t="n">
@@ -2131,9 +2273,10 @@
       <c r="C130" s="6" t="n"/>
       <c r="D130" s="6" t="n"/>
       <c r="E130" s="6" t="n"/>
-      <c r="F130" s="5" t="n"/>
+      <c r="F130" s="6" t="n"/>
       <c r="G130" s="5" t="n"/>
-      <c r="H130" s="6" t="n"/>
+      <c r="H130" s="5" t="n"/>
+      <c r="I130" s="6" t="n"/>
     </row>
     <row r="131" outlineLevel="2">
       <c r="A131" s="4" t="n">
@@ -2143,9 +2286,10 @@
       <c r="C131" s="6" t="n"/>
       <c r="D131" s="6" t="n"/>
       <c r="E131" s="6" t="n"/>
-      <c r="F131" s="5" t="n"/>
+      <c r="F131" s="6" t="n"/>
       <c r="G131" s="5" t="n"/>
-      <c r="H131" s="6" t="n"/>
+      <c r="H131" s="5" t="n"/>
+      <c r="I131" s="6" t="n"/>
     </row>
     <row r="132" outlineLevel="2">
       <c r="A132" s="4" t="n">
@@ -2155,9 +2299,10 @@
       <c r="C132" s="6" t="n"/>
       <c r="D132" s="6" t="n"/>
       <c r="E132" s="6" t="n"/>
-      <c r="F132" s="5" t="n"/>
+      <c r="F132" s="6" t="n"/>
       <c r="G132" s="5" t="n"/>
-      <c r="H132" s="6" t="n"/>
+      <c r="H132" s="5" t="n"/>
+      <c r="I132" s="6" t="n"/>
     </row>
     <row r="133" outlineLevel="2">
       <c r="A133" s="4" t="n">
@@ -2167,9 +2312,10 @@
       <c r="C133" s="6" t="n"/>
       <c r="D133" s="6" t="n"/>
       <c r="E133" s="6" t="n"/>
-      <c r="F133" s="5" t="n"/>
+      <c r="F133" s="6" t="n"/>
       <c r="G133" s="5" t="n"/>
-      <c r="H133" s="6" t="n"/>
+      <c r="H133" s="5" t="n"/>
+      <c r="I133" s="6" t="n"/>
     </row>
     <row r="134" outlineLevel="1">
       <c r="A134" s="4" t="n">
@@ -2179,9 +2325,10 @@
       <c r="C134" s="6" t="n"/>
       <c r="D134" s="6" t="n"/>
       <c r="E134" s="6" t="n"/>
-      <c r="F134" s="5" t="n"/>
+      <c r="F134" s="6" t="n"/>
       <c r="G134" s="5" t="n"/>
-      <c r="H134" s="6" t="n"/>
+      <c r="H134" s="5" t="n"/>
+      <c r="I134" s="6" t="n"/>
     </row>
     <row r="135" outlineLevel="2">
       <c r="A135" s="4" t="n">
@@ -2191,9 +2338,10 @@
       <c r="C135" s="6" t="n"/>
       <c r="D135" s="6" t="n"/>
       <c r="E135" s="6" t="n"/>
-      <c r="F135" s="5" t="n"/>
+      <c r="F135" s="6" t="n"/>
       <c r="G135" s="5" t="n"/>
-      <c r="H135" s="6" t="n"/>
+      <c r="H135" s="5" t="n"/>
+      <c r="I135" s="6" t="n"/>
     </row>
     <row r="136" outlineLevel="2">
       <c r="A136" s="4" t="n">
@@ -2203,9 +2351,10 @@
       <c r="C136" s="6" t="n"/>
       <c r="D136" s="6" t="n"/>
       <c r="E136" s="6" t="n"/>
-      <c r="F136" s="5" t="n"/>
+      <c r="F136" s="6" t="n"/>
       <c r="G136" s="5" t="n"/>
-      <c r="H136" s="6" t="n"/>
+      <c r="H136" s="5" t="n"/>
+      <c r="I136" s="6" t="n"/>
     </row>
     <row r="137" outlineLevel="2">
       <c r="A137" s="4" t="n">
@@ -2215,9 +2364,10 @@
       <c r="C137" s="6" t="n"/>
       <c r="D137" s="6" t="n"/>
       <c r="E137" s="6" t="n"/>
-      <c r="F137" s="5" t="n"/>
+      <c r="F137" s="6" t="n"/>
       <c r="G137" s="5" t="n"/>
-      <c r="H137" s="6" t="n"/>
+      <c r="H137" s="5" t="n"/>
+      <c r="I137" s="6" t="n"/>
     </row>
     <row r="138" ht="57.6" customHeight="1">
       <c r="A138" s="4" t="n">
@@ -2239,12 +2389,13 @@
       </c>
       <c r="D138" s="6" t="n"/>
       <c r="E138" s="6" t="n"/>
-      <c r="F138" s="5" t="n"/>
-      <c r="G138" s="5">
+      <c r="F138" s="6" t="n"/>
+      <c r="G138" s="5" t="n"/>
+      <c r="H138" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 20, 1060)</t>
         </is>
@@ -2258,9 +2409,10 @@
       <c r="C139" s="6" t="n"/>
       <c r="D139" s="6" t="n"/>
       <c r="E139" s="6" t="n"/>
-      <c r="F139" s="5" t="n"/>
+      <c r="F139" s="6" t="n"/>
       <c r="G139" s="5" t="n"/>
-      <c r="H139" s="6" t="n"/>
+      <c r="H139" s="5" t="n"/>
+      <c r="I139" s="6" t="n"/>
     </row>
     <row r="140" outlineLevel="2">
       <c r="A140" s="4" t="n">
@@ -2270,9 +2422,10 @@
       <c r="C140" s="6" t="n"/>
       <c r="D140" s="6" t="n"/>
       <c r="E140" s="6" t="n"/>
-      <c r="F140" s="5" t="n"/>
+      <c r="F140" s="6" t="n"/>
       <c r="G140" s="5" t="n"/>
-      <c r="H140" s="6" t="n"/>
+      <c r="H140" s="5" t="n"/>
+      <c r="I140" s="6" t="n"/>
     </row>
     <row r="141" outlineLevel="2">
       <c r="A141" s="4" t="n">
@@ -2282,9 +2435,10 @@
       <c r="C141" s="6" t="n"/>
       <c r="D141" s="6" t="n"/>
       <c r="E141" s="6" t="n"/>
-      <c r="F141" s="5" t="n"/>
+      <c r="F141" s="6" t="n"/>
       <c r="G141" s="5" t="n"/>
-      <c r="H141" s="6" t="n"/>
+      <c r="H141" s="5" t="n"/>
+      <c r="I141" s="6" t="n"/>
     </row>
     <row r="142" outlineLevel="1">
       <c r="A142" s="4" t="n">
@@ -2292,10 +2446,11 @@
       </c>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="5" t="n"/>
+      <c r="D142" s="6" t="n"/>
+      <c r="F142" s="6" t="n"/>
       <c r="G142" s="5" t="n"/>
-      <c r="H142" s="6" t="n"/>
+      <c r="H142" s="5" t="n"/>
+      <c r="I142" s="6" t="n"/>
     </row>
     <row r="143" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A143" s="4" t="n">
@@ -2305,9 +2460,10 @@
       <c r="C143" s="6" t="n"/>
       <c r="D143" s="6" t="n"/>
       <c r="E143" s="6" t="n"/>
-      <c r="F143" s="5" t="n"/>
+      <c r="F143" s="6" t="n"/>
       <c r="G143" s="5" t="n"/>
-      <c r="H143" s="6" t="n"/>
+      <c r="H143" s="5" t="n"/>
+      <c r="I143" s="6" t="n"/>
     </row>
     <row r="144" outlineLevel="2">
       <c r="A144" s="4" t="n">
@@ -2317,9 +2473,10 @@
       <c r="C144" s="6" t="n"/>
       <c r="D144" s="6" t="n"/>
       <c r="E144" s="6" t="n"/>
-      <c r="F144" s="5" t="n"/>
+      <c r="F144" s="6" t="n"/>
       <c r="G144" s="5" t="n"/>
-      <c r="H144" s="6" t="n"/>
+      <c r="H144" s="5" t="n"/>
+      <c r="I144" s="6" t="n"/>
     </row>
     <row r="145" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A145" s="4" t="n">
@@ -2329,9 +2486,10 @@
       <c r="C145" s="6" t="n"/>
       <c r="D145" s="6" t="n"/>
       <c r="E145" s="6" t="n"/>
-      <c r="F145" s="5" t="n"/>
+      <c r="F145" s="6" t="n"/>
       <c r="G145" s="5" t="n"/>
-      <c r="H145" s="6" t="n"/>
+      <c r="H145" s="5" t="n"/>
+      <c r="I145" s="6" t="n"/>
     </row>
     <row r="146" outlineLevel="1">
       <c r="A146" s="4" t="n">
@@ -2341,9 +2499,10 @@
       <c r="C146" s="6" t="n"/>
       <c r="D146" s="6" t="n"/>
       <c r="E146" s="6" t="n"/>
-      <c r="F146" s="5" t="n"/>
+      <c r="F146" s="6" t="n"/>
       <c r="G146" s="5" t="n"/>
-      <c r="H146" s="6" t="n"/>
+      <c r="H146" s="5" t="n"/>
+      <c r="I146" s="6" t="n"/>
     </row>
     <row r="147" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A147" s="4" t="n">
@@ -2355,15 +2514,16 @@
           <t>HERE steht zwei Viertel, bis IN kommt</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D147" s="6" t="n"/>
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>HERE -&gt; möglichst lange stehen lassen (bis der nächste text kommt)</t>
         </is>
       </c>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="5" t="n"/>
+      <c r="F147" s="6" t="n"/>
       <c r="G147" s="5" t="n"/>
-      <c r="H147" s="6" t="n"/>
+      <c r="H147" s="5" t="n"/>
+      <c r="I147" s="6" t="n"/>
     </row>
     <row r="148" outlineLevel="2">
       <c r="A148" s="4" t="n">
@@ -2373,9 +2533,10 @@
       <c r="C148" s="6" t="n"/>
       <c r="D148" s="6" t="n"/>
       <c r="E148" s="6" t="n"/>
-      <c r="F148" s="5" t="n"/>
+      <c r="F148" s="6" t="n"/>
       <c r="G148" s="5" t="n"/>
-      <c r="H148" s="6" t="n"/>
+      <c r="H148" s="5" t="n"/>
+      <c r="I148" s="6" t="n"/>
     </row>
     <row r="149" outlineLevel="2">
       <c r="A149" s="4" t="n">
@@ -2385,9 +2546,10 @@
       <c r="C149" s="6" t="n"/>
       <c r="D149" s="6" t="n"/>
       <c r="E149" s="6" t="n"/>
-      <c r="F149" s="5" t="n"/>
+      <c r="F149" s="6" t="n"/>
       <c r="G149" s="5" t="n"/>
-      <c r="H149" s="6" t="n"/>
+      <c r="H149" s="5" t="n"/>
+      <c r="I149" s="6" t="n"/>
     </row>
     <row r="150" outlineLevel="1">
       <c r="A150" s="4" t="n">
@@ -2397,9 +2559,10 @@
       <c r="C150" s="6" t="n"/>
       <c r="D150" s="6" t="n"/>
       <c r="E150" s="6" t="n"/>
-      <c r="F150" s="5" t="n"/>
+      <c r="F150" s="6" t="n"/>
       <c r="G150" s="5" t="n"/>
-      <c r="H150" s="6" t="n"/>
+      <c r="H150" s="5" t="n"/>
+      <c r="I150" s="6" t="n"/>
     </row>
     <row r="151" outlineLevel="2">
       <c r="A151" s="4" t="n">
@@ -2409,9 +2572,10 @@
       <c r="C151" s="6" t="n"/>
       <c r="D151" s="6" t="n"/>
       <c r="E151" s="6" t="n"/>
-      <c r="F151" s="5" t="n"/>
+      <c r="F151" s="6" t="n"/>
       <c r="G151" s="5" t="n"/>
-      <c r="H151" s="6" t="n"/>
+      <c r="H151" s="5" t="n"/>
+      <c r="I151" s="6" t="n"/>
     </row>
     <row r="152" outlineLevel="2">
       <c r="A152" s="4" t="n">
@@ -2421,9 +2585,10 @@
       <c r="C152" s="6" t="n"/>
       <c r="D152" s="6" t="n"/>
       <c r="E152" s="6" t="n"/>
-      <c r="F152" s="5" t="n"/>
+      <c r="F152" s="6" t="n"/>
       <c r="G152" s="5" t="n"/>
-      <c r="H152" s="6" t="n"/>
+      <c r="H152" s="5" t="n"/>
+      <c r="I152" s="6" t="n"/>
     </row>
     <row r="153" outlineLevel="2">
       <c r="A153" s="4" t="n">
@@ -2433,9 +2598,10 @@
       <c r="C153" s="6" t="n"/>
       <c r="D153" s="6" t="n"/>
       <c r="E153" s="6" t="n"/>
-      <c r="F153" s="5" t="n"/>
+      <c r="F153" s="6" t="n"/>
       <c r="G153" s="5" t="n"/>
-      <c r="H153" s="6" t="n"/>
+      <c r="H153" s="5" t="n"/>
+      <c r="I153" s="6" t="n"/>
     </row>
     <row r="154" ht="28.8" customHeight="1">
       <c r="A154" s="4" t="n">
@@ -2456,12 +2622,13 @@
       </c>
       <c r="D154" s="6" t="n"/>
       <c r="E154" s="6" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5">
+      <c r="F154" s="6" t="n"/>
+      <c r="G154" s="5" t="n"/>
+      <c r="H154" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H154" s="6" t="inlineStr">
+      <c r="I154" s="6" t="inlineStr">
         <is>
           <t>progStrobo(7965, 25, 50, getRandomCRGB())</t>
         </is>
@@ -2475,9 +2642,10 @@
       <c r="C155" s="6" t="n"/>
       <c r="D155" s="6" t="n"/>
       <c r="E155" s="6" t="n"/>
-      <c r="F155" s="5" t="n"/>
+      <c r="F155" s="6" t="n"/>
       <c r="G155" s="5" t="n"/>
-      <c r="H155" s="6" t="n"/>
+      <c r="H155" s="5" t="n"/>
+      <c r="I155" s="6" t="n"/>
     </row>
     <row r="156" outlineLevel="2">
       <c r="A156" s="4" t="n">
@@ -2487,9 +2655,10 @@
       <c r="C156" s="6" t="n"/>
       <c r="D156" s="6" t="n"/>
       <c r="E156" s="6" t="n"/>
-      <c r="F156" s="5" t="n"/>
+      <c r="F156" s="6" t="n"/>
       <c r="G156" s="5" t="n"/>
-      <c r="H156" s="6" t="n"/>
+      <c r="H156" s="5" t="n"/>
+      <c r="I156" s="6" t="n"/>
     </row>
     <row r="157" outlineLevel="2">
       <c r="A157" s="4" t="n">
@@ -2499,9 +2668,10 @@
       <c r="C157" s="6" t="n"/>
       <c r="D157" s="6" t="n"/>
       <c r="E157" s="6" t="n"/>
-      <c r="F157" s="5" t="n"/>
+      <c r="F157" s="6" t="n"/>
       <c r="G157" s="5" t="n"/>
-      <c r="H157" s="6" t="n"/>
+      <c r="H157" s="5" t="n"/>
+      <c r="I157" s="6" t="n"/>
     </row>
     <row r="158" outlineLevel="1">
       <c r="A158" s="4" t="n">
@@ -2511,9 +2681,10 @@
       <c r="C158" s="6" t="n"/>
       <c r="D158" s="6" t="n"/>
       <c r="E158" s="6" t="n"/>
-      <c r="F158" s="5" t="n"/>
+      <c r="F158" s="6" t="n"/>
       <c r="G158" s="5" t="n"/>
-      <c r="H158" s="6" t="n"/>
+      <c r="H158" s="5" t="n"/>
+      <c r="I158" s="6" t="n"/>
     </row>
     <row r="159" outlineLevel="2">
       <c r="A159" s="4" t="n">
@@ -2523,9 +2694,10 @@
       <c r="C159" s="6" t="n"/>
       <c r="D159" s="6" t="n"/>
       <c r="E159" s="6" t="n"/>
-      <c r="F159" s="5" t="n"/>
+      <c r="F159" s="6" t="n"/>
       <c r="G159" s="5" t="n"/>
-      <c r="H159" s="6" t="n"/>
+      <c r="H159" s="5" t="n"/>
+      <c r="I159" s="6" t="n"/>
     </row>
     <row r="160" outlineLevel="2">
       <c r="A160" s="4" t="n">
@@ -2535,9 +2707,10 @@
       <c r="C160" s="6" t="n"/>
       <c r="D160" s="6" t="n"/>
       <c r="E160" s="6" t="n"/>
-      <c r="F160" s="5" t="n"/>
+      <c r="F160" s="6" t="n"/>
       <c r="G160" s="5" t="n"/>
-      <c r="H160" s="6" t="n"/>
+      <c r="H160" s="5" t="n"/>
+      <c r="I160" s="6" t="n"/>
     </row>
     <row r="161" outlineLevel="2">
       <c r="A161" s="4" t="n">
@@ -2547,9 +2720,10 @@
       <c r="C161" s="6" t="n"/>
       <c r="D161" s="6" t="n"/>
       <c r="E161" s="6" t="n"/>
-      <c r="F161" s="5" t="n"/>
+      <c r="F161" s="6" t="n"/>
       <c r="G161" s="5" t="n"/>
-      <c r="H161" s="6" t="n"/>
+      <c r="H161" s="5" t="n"/>
+      <c r="I161" s="6" t="n"/>
     </row>
     <row r="162" outlineLevel="1">
       <c r="A162" s="4" t="n">
@@ -2559,9 +2733,10 @@
       <c r="C162" s="6" t="n"/>
       <c r="D162" s="6" t="n"/>
       <c r="E162" s="6" t="n"/>
-      <c r="F162" s="5" t="n"/>
+      <c r="F162" s="6" t="n"/>
       <c r="G162" s="5" t="n"/>
-      <c r="H162" s="6" t="n"/>
+      <c r="H162" s="5" t="n"/>
+      <c r="I162" s="6" t="n"/>
     </row>
     <row r="163" outlineLevel="2">
       <c r="A163" s="4" t="n">
@@ -2571,9 +2746,10 @@
       <c r="C163" s="6" t="n"/>
       <c r="D163" s="6" t="n"/>
       <c r="E163" s="6" t="n"/>
-      <c r="F163" s="5" t="n"/>
+      <c r="F163" s="6" t="n"/>
       <c r="G163" s="5" t="n"/>
-      <c r="H163" s="6" t="n"/>
+      <c r="H163" s="5" t="n"/>
+      <c r="I163" s="6" t="n"/>
     </row>
     <row r="164" outlineLevel="2">
       <c r="A164" s="4" t="n">
@@ -2583,9 +2759,10 @@
       <c r="C164" s="6" t="n"/>
       <c r="D164" s="6" t="n"/>
       <c r="E164" s="6" t="n"/>
-      <c r="F164" s="5" t="n"/>
+      <c r="F164" s="6" t="n"/>
       <c r="G164" s="5" t="n"/>
-      <c r="H164" s="6" t="n"/>
+      <c r="H164" s="5" t="n"/>
+      <c r="I164" s="6" t="n"/>
     </row>
     <row r="165" outlineLevel="2">
       <c r="A165" s="4" t="n">
@@ -2595,9 +2772,10 @@
       <c r="C165" s="6" t="n"/>
       <c r="D165" s="6" t="n"/>
       <c r="E165" s="6" t="n"/>
-      <c r="F165" s="5" t="n"/>
+      <c r="F165" s="6" t="n"/>
       <c r="G165" s="5" t="n"/>
-      <c r="H165" s="6" t="n"/>
+      <c r="H165" s="5" t="n"/>
+      <c r="I165" s="6" t="n"/>
     </row>
     <row r="166" outlineLevel="1">
       <c r="A166" s="4" t="n">
@@ -2607,9 +2785,10 @@
       <c r="C166" s="6" t="n"/>
       <c r="D166" s="6" t="n"/>
       <c r="E166" s="6" t="n"/>
-      <c r="F166" s="5" t="n"/>
+      <c r="F166" s="6" t="n"/>
       <c r="G166" s="5" t="n"/>
-      <c r="H166" s="6" t="n"/>
+      <c r="H166" s="5" t="n"/>
+      <c r="I166" s="6" t="n"/>
     </row>
     <row r="167" outlineLevel="2">
       <c r="A167" s="4" t="n">
@@ -2619,9 +2798,10 @@
       <c r="C167" s="6" t="n"/>
       <c r="D167" s="6" t="n"/>
       <c r="E167" s="6" t="n"/>
-      <c r="F167" s="5" t="n"/>
+      <c r="F167" s="6" t="n"/>
       <c r="G167" s="5" t="n"/>
-      <c r="H167" s="6" t="n"/>
+      <c r="H167" s="5" t="n"/>
+      <c r="I167" s="6" t="n"/>
     </row>
     <row r="168" outlineLevel="2">
       <c r="A168" s="4" t="n">
@@ -2631,9 +2811,10 @@
       <c r="C168" s="6" t="n"/>
       <c r="D168" s="6" t="n"/>
       <c r="E168" s="6" t="n"/>
-      <c r="F168" s="5" t="n"/>
+      <c r="F168" s="6" t="n"/>
       <c r="G168" s="5" t="n"/>
-      <c r="H168" s="6" t="n"/>
+      <c r="H168" s="5" t="n"/>
+      <c r="I168" s="6" t="n"/>
     </row>
     <row r="169" ht="28.8" customHeight="1">
       <c r="A169" s="4" t="n">
@@ -2652,12 +2833,13 @@
       </c>
       <c r="D169" s="6" t="n"/>
       <c r="E169" s="6" t="n"/>
-      <c r="F169" s="5" t="n"/>
-      <c r="G169" s="5">
+      <c r="F169" s="6" t="n"/>
+      <c r="G169" s="5" t="n"/>
+      <c r="H169" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H169" s="6" t="inlineStr">
+      <c r="I169" s="6" t="inlineStr">
         <is>
           <t>progBlack(520, 30)</t>
         </is>
@@ -2680,12 +2862,13 @@
       </c>
       <c r="D170" s="6" t="n"/>
       <c r="E170" s="6" t="n"/>
-      <c r="F170" s="5" t="n"/>
-      <c r="G170" s="5">
+      <c r="F170" s="6" t="n"/>
+      <c r="G170" s="5" t="n"/>
+      <c r="H170" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H170" s="6" t="inlineStr">
+      <c r="I170" s="6" t="inlineStr">
         <is>
           <t>progMovingLines(1590, 32)</t>
         </is>
@@ -2699,9 +2882,10 @@
       <c r="C171" s="6" t="n"/>
       <c r="D171" s="6" t="n"/>
       <c r="E171" s="6" t="n"/>
-      <c r="F171" s="5" t="n"/>
+      <c r="F171" s="6" t="n"/>
       <c r="G171" s="5" t="n"/>
-      <c r="H171" s="6" t="n"/>
+      <c r="H171" s="5" t="n"/>
+      <c r="I171" s="6" t="n"/>
     </row>
     <row r="172" outlineLevel="2">
       <c r="A172" s="4" t="n">
@@ -2711,9 +2895,10 @@
       <c r="C172" s="6" t="n"/>
       <c r="D172" s="6" t="n"/>
       <c r="E172" s="6" t="n"/>
-      <c r="F172" s="5" t="n"/>
+      <c r="F172" s="6" t="n"/>
       <c r="G172" s="5" t="n"/>
-      <c r="H172" s="6" t="n"/>
+      <c r="H172" s="5" t="n"/>
+      <c r="I172" s="6" t="n"/>
     </row>
     <row r="173" ht="43.2" customHeight="1">
       <c r="A173" s="4" t="n">
@@ -2733,12 +2918,13 @@
       </c>
       <c r="D173" s="6" t="n"/>
       <c r="E173" s="6" t="n"/>
-      <c r="F173" s="5" t="n"/>
-      <c r="G173" s="5">
+      <c r="F173" s="6" t="n"/>
+      <c r="G173" s="5" t="n"/>
+      <c r="H173" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="I173" s="6" t="inlineStr">
         <is>
           <t>progStrobo(540, 35, 50, getRandomCRGB())</t>
         </is>
@@ -2762,12 +2948,13 @@
       </c>
       <c r="D174" s="6" t="n"/>
       <c r="E174" s="6" t="n"/>
-      <c r="F174" s="5" t="n"/>
-      <c r="G174" s="5">
+      <c r="F174" s="6" t="n"/>
+      <c r="G174" s="5" t="n"/>
+      <c r="H174" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="I174" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(17000, 970, 40, 5, 26, 5, false, 4)</t>
         </is>
@@ -2781,9 +2968,10 @@
       <c r="C175" s="6" t="n"/>
       <c r="D175" s="6" t="n"/>
       <c r="E175" s="6" t="n"/>
-      <c r="F175" s="5" t="n"/>
+      <c r="F175" s="6" t="n"/>
       <c r="G175" s="5" t="n"/>
-      <c r="H175" s="6" t="n"/>
+      <c r="H175" s="5" t="n"/>
+      <c r="I175" s="6" t="n"/>
     </row>
     <row r="176" outlineLevel="2">
       <c r="A176" s="4" t="n">
@@ -2793,9 +2981,10 @@
       <c r="C176" s="6" t="n"/>
       <c r="D176" s="6" t="n"/>
       <c r="E176" s="6" t="n"/>
-      <c r="F176" s="5" t="n"/>
+      <c r="F176" s="6" t="n"/>
       <c r="G176" s="5" t="n"/>
-      <c r="H176" s="6" t="n"/>
+      <c r="H176" s="5" t="n"/>
+      <c r="I176" s="6" t="n"/>
     </row>
     <row r="177" outlineLevel="2">
       <c r="A177" s="4" t="n">
@@ -2805,9 +2994,10 @@
       <c r="C177" s="6" t="n"/>
       <c r="D177" s="6" t="n"/>
       <c r="E177" s="6" t="n"/>
-      <c r="F177" s="5" t="n"/>
+      <c r="F177" s="6" t="n"/>
       <c r="G177" s="5" t="n"/>
-      <c r="H177" s="6" t="n"/>
+      <c r="H177" s="5" t="n"/>
+      <c r="I177" s="6" t="n"/>
     </row>
     <row r="178" outlineLevel="1">
       <c r="A178" s="4" t="n">
@@ -2817,9 +3007,10 @@
       <c r="C178" s="6" t="n"/>
       <c r="D178" s="6" t="n"/>
       <c r="E178" s="6" t="n"/>
-      <c r="F178" s="5" t="n"/>
+      <c r="F178" s="6" t="n"/>
       <c r="G178" s="5" t="n"/>
-      <c r="H178" s="6" t="n"/>
+      <c r="H178" s="5" t="n"/>
+      <c r="I178" s="6" t="n"/>
     </row>
     <row r="179" outlineLevel="2">
       <c r="A179" s="4" t="n">
@@ -2829,9 +3020,10 @@
       <c r="C179" s="6" t="n"/>
       <c r="D179" s="6" t="n"/>
       <c r="E179" s="6" t="n"/>
-      <c r="F179" s="5" t="n"/>
+      <c r="F179" s="6" t="n"/>
       <c r="G179" s="5" t="n"/>
-      <c r="H179" s="6" t="n"/>
+      <c r="H179" s="5" t="n"/>
+      <c r="I179" s="6" t="n"/>
     </row>
     <row r="180" outlineLevel="2">
       <c r="A180" s="4" t="n">
@@ -2841,9 +3033,10 @@
       <c r="C180" s="6" t="n"/>
       <c r="D180" s="6" t="n"/>
       <c r="E180" s="6" t="n"/>
-      <c r="F180" s="5" t="n"/>
+      <c r="F180" s="6" t="n"/>
       <c r="G180" s="5" t="n"/>
-      <c r="H180" s="6" t="n"/>
+      <c r="H180" s="5" t="n"/>
+      <c r="I180" s="6" t="n"/>
     </row>
     <row r="181" outlineLevel="2">
       <c r="A181" s="4" t="n">
@@ -2853,9 +3046,10 @@
       <c r="C181" s="6" t="n"/>
       <c r="D181" s="6" t="n"/>
       <c r="E181" s="6" t="n"/>
-      <c r="F181" s="5" t="n"/>
+      <c r="F181" s="6" t="n"/>
       <c r="G181" s="5" t="n"/>
-      <c r="H181" s="6" t="n"/>
+      <c r="H181" s="5" t="n"/>
+      <c r="I181" s="6" t="n"/>
     </row>
     <row r="182" outlineLevel="1">
       <c r="A182" s="4" t="n">
@@ -2865,9 +3059,10 @@
       <c r="C182" s="6" t="n"/>
       <c r="D182" s="6" t="n"/>
       <c r="E182" s="6" t="n"/>
-      <c r="F182" s="5" t="n"/>
+      <c r="F182" s="6" t="n"/>
       <c r="G182" s="5" t="n"/>
-      <c r="H182" s="6" t="n"/>
+      <c r="H182" s="5" t="n"/>
+      <c r="I182" s="6" t="n"/>
     </row>
     <row r="183" outlineLevel="2">
       <c r="A183" s="4" t="n">
@@ -2877,9 +3072,10 @@
       <c r="C183" s="6" t="n"/>
       <c r="D183" s="6" t="n"/>
       <c r="E183" s="6" t="n"/>
-      <c r="F183" s="5" t="n"/>
+      <c r="F183" s="6" t="n"/>
       <c r="G183" s="5" t="n"/>
-      <c r="H183" s="6" t="n"/>
+      <c r="H183" s="5" t="n"/>
+      <c r="I183" s="6" t="n"/>
     </row>
     <row r="184" outlineLevel="2">
       <c r="A184" s="4" t="n">
@@ -2889,9 +3085,10 @@
       <c r="C184" s="6" t="n"/>
       <c r="D184" s="6" t="n"/>
       <c r="E184" s="6" t="n"/>
-      <c r="F184" s="5" t="n"/>
+      <c r="F184" s="6" t="n"/>
       <c r="G184" s="5" t="n"/>
-      <c r="H184" s="6" t="n"/>
+      <c r="H184" s="5" t="n"/>
+      <c r="I184" s="6" t="n"/>
     </row>
     <row r="185" outlineLevel="2">
       <c r="A185" s="4" t="n">
@@ -2901,9 +3098,10 @@
       <c r="C185" s="6" t="n"/>
       <c r="D185" s="6" t="n"/>
       <c r="E185" s="6" t="n"/>
-      <c r="F185" s="5" t="n"/>
+      <c r="F185" s="6" t="n"/>
       <c r="G185" s="5" t="n"/>
-      <c r="H185" s="6" t="n"/>
+      <c r="H185" s="5" t="n"/>
+      <c r="I185" s="6" t="n"/>
     </row>
     <row r="186" outlineLevel="1">
       <c r="A186" s="4" t="n">
@@ -2913,9 +3111,10 @@
       <c r="C186" s="6" t="n"/>
       <c r="D186" s="6" t="n"/>
       <c r="E186" s="6" t="n"/>
-      <c r="F186" s="5" t="n"/>
+      <c r="F186" s="6" t="n"/>
       <c r="G186" s="5" t="n"/>
-      <c r="H186" s="6" t="n"/>
+      <c r="H186" s="5" t="n"/>
+      <c r="I186" s="6" t="n"/>
     </row>
     <row r="187" outlineLevel="2">
       <c r="A187" s="4" t="n">
@@ -2925,9 +3124,10 @@
       <c r="C187" s="6" t="n"/>
       <c r="D187" s="6" t="n"/>
       <c r="E187" s="6" t="n"/>
-      <c r="F187" s="5" t="n"/>
+      <c r="F187" s="6" t="n"/>
       <c r="G187" s="5" t="n"/>
-      <c r="H187" s="6" t="n"/>
+      <c r="H187" s="5" t="n"/>
+      <c r="I187" s="6" t="n"/>
     </row>
     <row r="188" outlineLevel="2">
       <c r="A188" s="4" t="n">
@@ -2937,9 +3137,10 @@
       <c r="C188" s="6" t="n"/>
       <c r="D188" s="6" t="n"/>
       <c r="E188" s="6" t="n"/>
-      <c r="F188" s="5" t="n"/>
+      <c r="F188" s="6" t="n"/>
       <c r="G188" s="5" t="n"/>
-      <c r="H188" s="6" t="n"/>
+      <c r="H188" s="5" t="n"/>
+      <c r="I188" s="6" t="n"/>
     </row>
     <row r="189" outlineLevel="2">
       <c r="A189" s="4" t="n">
@@ -2949,9 +3150,10 @@
       <c r="C189" s="6" t="n"/>
       <c r="D189" s="6" t="n"/>
       <c r="E189" s="6" t="n"/>
-      <c r="F189" s="5" t="n"/>
+      <c r="F189" s="6" t="n"/>
       <c r="G189" s="5" t="n"/>
-      <c r="H189" s="6" t="n"/>
+      <c r="H189" s="5" t="n"/>
+      <c r="I189" s="6" t="n"/>
     </row>
     <row r="190" outlineLevel="1">
       <c r="A190" s="4" t="n">
@@ -2961,9 +3163,10 @@
       <c r="C190" s="6" t="n"/>
       <c r="D190" s="6" t="n"/>
       <c r="E190" s="6" t="n"/>
-      <c r="F190" s="5" t="n"/>
+      <c r="F190" s="6" t="n"/>
       <c r="G190" s="5" t="n"/>
-      <c r="H190" s="6" t="n"/>
+      <c r="H190" s="5" t="n"/>
+      <c r="I190" s="6" t="n"/>
     </row>
     <row r="191" outlineLevel="2">
       <c r="A191" s="4" t="n">
@@ -2973,9 +3176,10 @@
       <c r="C191" s="6" t="n"/>
       <c r="D191" s="6" t="n"/>
       <c r="E191" s="6" t="n"/>
-      <c r="F191" s="5" t="n"/>
+      <c r="F191" s="6" t="n"/>
       <c r="G191" s="5" t="n"/>
-      <c r="H191" s="6" t="n"/>
+      <c r="H191" s="5" t="n"/>
+      <c r="I191" s="6" t="n"/>
     </row>
     <row r="192" outlineLevel="2">
       <c r="A192" s="4" t="n">
@@ -2985,9 +3189,10 @@
       <c r="C192" s="6" t="n"/>
       <c r="D192" s="6" t="n"/>
       <c r="E192" s="6" t="n"/>
-      <c r="F192" s="5" t="n"/>
+      <c r="F192" s="6" t="n"/>
       <c r="G192" s="5" t="n"/>
-      <c r="H192" s="6" t="n"/>
+      <c r="H192" s="5" t="n"/>
+      <c r="I192" s="6" t="n"/>
     </row>
     <row r="193" outlineLevel="2">
       <c r="A193" s="4" t="n">
@@ -2997,9 +3202,10 @@
       <c r="C193" s="6" t="n"/>
       <c r="D193" s="6" t="n"/>
       <c r="E193" s="6" t="n"/>
-      <c r="F193" s="5" t="n"/>
+      <c r="F193" s="6" t="n"/>
       <c r="G193" s="5" t="n"/>
-      <c r="H193" s="6" t="n"/>
+      <c r="H193" s="5" t="n"/>
+      <c r="I193" s="6" t="n"/>
     </row>
     <row r="194" outlineLevel="1">
       <c r="A194" s="4" t="n">
@@ -3009,9 +3215,10 @@
       <c r="C194" s="6" t="n"/>
       <c r="D194" s="6" t="n"/>
       <c r="E194" s="6" t="n"/>
-      <c r="F194" s="5" t="n"/>
+      <c r="F194" s="6" t="n"/>
       <c r="G194" s="5" t="n"/>
-      <c r="H194" s="6" t="n"/>
+      <c r="H194" s="5" t="n"/>
+      <c r="I194" s="6" t="n"/>
     </row>
     <row r="195" outlineLevel="2">
       <c r="A195" s="4" t="n">
@@ -3021,9 +3228,10 @@
       <c r="C195" s="6" t="n"/>
       <c r="D195" s="6" t="n"/>
       <c r="E195" s="6" t="n"/>
-      <c r="F195" s="5" t="n"/>
+      <c r="F195" s="6" t="n"/>
       <c r="G195" s="5" t="n"/>
-      <c r="H195" s="6" t="n"/>
+      <c r="H195" s="5" t="n"/>
+      <c r="I195" s="6" t="n"/>
     </row>
     <row r="196" outlineLevel="2">
       <c r="A196" s="4" t="n">
@@ -3033,9 +3241,10 @@
       <c r="C196" s="6" t="n"/>
       <c r="D196" s="6" t="n"/>
       <c r="E196" s="6" t="n"/>
-      <c r="F196" s="5" t="n"/>
+      <c r="F196" s="6" t="n"/>
       <c r="G196" s="5" t="n"/>
-      <c r="H196" s="6" t="n"/>
+      <c r="H196" s="5" t="n"/>
+      <c r="I196" s="6" t="n"/>
     </row>
     <row r="197" outlineLevel="2">
       <c r="A197" s="4" t="n">
@@ -3045,9 +3254,10 @@
       <c r="C197" s="6" t="n"/>
       <c r="D197" s="6" t="n"/>
       <c r="E197" s="6" t="n"/>
-      <c r="F197" s="5" t="n"/>
+      <c r="F197" s="6" t="n"/>
       <c r="G197" s="5" t="n"/>
-      <c r="H197" s="6" t="n"/>
+      <c r="H197" s="5" t="n"/>
+      <c r="I197" s="6" t="n"/>
     </row>
     <row r="198" outlineLevel="1">
       <c r="A198" s="4" t="n">
@@ -3057,9 +3267,10 @@
       <c r="C198" s="6" t="n"/>
       <c r="D198" s="6" t="n"/>
       <c r="E198" s="6" t="n"/>
-      <c r="F198" s="5" t="n"/>
+      <c r="F198" s="6" t="n"/>
       <c r="G198" s="5" t="n"/>
-      <c r="H198" s="6" t="n"/>
+      <c r="H198" s="5" t="n"/>
+      <c r="I198" s="6" t="n"/>
     </row>
     <row r="199" outlineLevel="2">
       <c r="A199" s="4" t="n">
@@ -3069,9 +3280,10 @@
       <c r="C199" s="6" t="n"/>
       <c r="D199" s="6" t="n"/>
       <c r="E199" s="6" t="n"/>
-      <c r="F199" s="5" t="n"/>
+      <c r="F199" s="6" t="n"/>
       <c r="G199" s="5" t="n"/>
-      <c r="H199" s="6" t="n"/>
+      <c r="H199" s="5" t="n"/>
+      <c r="I199" s="6" t="n"/>
     </row>
     <row r="200" outlineLevel="2">
       <c r="A200" s="4" t="n">
@@ -3081,9 +3293,10 @@
       <c r="C200" s="6" t="n"/>
       <c r="D200" s="6" t="n"/>
       <c r="E200" s="6" t="n"/>
-      <c r="F200" s="5" t="n"/>
+      <c r="F200" s="6" t="n"/>
       <c r="G200" s="5" t="n"/>
-      <c r="H200" s="6" t="n"/>
+      <c r="H200" s="5" t="n"/>
+      <c r="I200" s="6" t="n"/>
     </row>
     <row r="201" outlineLevel="2">
       <c r="A201" s="4" t="n">
@@ -3093,9 +3306,10 @@
       <c r="C201" s="6" t="n"/>
       <c r="D201" s="6" t="n"/>
       <c r="E201" s="6" t="n"/>
-      <c r="F201" s="5" t="n"/>
+      <c r="F201" s="6" t="n"/>
       <c r="G201" s="5" t="n"/>
-      <c r="H201" s="6" t="n"/>
+      <c r="H201" s="5" t="n"/>
+      <c r="I201" s="6" t="n"/>
     </row>
     <row r="202" outlineLevel="1">
       <c r="A202" s="4" t="n">
@@ -3105,9 +3319,10 @@
       <c r="C202" s="6" t="n"/>
       <c r="D202" s="6" t="n"/>
       <c r="E202" s="6" t="n"/>
-      <c r="F202" s="5" t="n"/>
+      <c r="F202" s="6" t="n"/>
       <c r="G202" s="5" t="n"/>
-      <c r="H202" s="6" t="n"/>
+      <c r="H202" s="5" t="n"/>
+      <c r="I202" s="6" t="n"/>
     </row>
     <row r="203" outlineLevel="2">
       <c r="A203" s="4" t="n">
@@ -3117,9 +3332,10 @@
       <c r="C203" s="6" t="n"/>
       <c r="D203" s="6" t="n"/>
       <c r="E203" s="6" t="n"/>
-      <c r="F203" s="5" t="n"/>
+      <c r="F203" s="6" t="n"/>
       <c r="G203" s="5" t="n"/>
-      <c r="H203" s="6" t="n"/>
+      <c r="H203" s="5" t="n"/>
+      <c r="I203" s="6" t="n"/>
     </row>
     <row r="204" outlineLevel="2">
       <c r="A204" s="4" t="n">
@@ -3129,9 +3345,10 @@
       <c r="C204" s="6" t="n"/>
       <c r="D204" s="6" t="n"/>
       <c r="E204" s="6" t="n"/>
-      <c r="F204" s="5" t="n"/>
+      <c r="F204" s="6" t="n"/>
       <c r="G204" s="5" t="n"/>
-      <c r="H204" s="6" t="n"/>
+      <c r="H204" s="5" t="n"/>
+      <c r="I204" s="6" t="n"/>
     </row>
     <row r="205" outlineLevel="2">
       <c r="A205" s="4" t="n">
@@ -3141,9 +3358,10 @@
       <c r="C205" s="6" t="n"/>
       <c r="D205" s="6" t="n"/>
       <c r="E205" s="6" t="n"/>
-      <c r="F205" s="5" t="n"/>
+      <c r="F205" s="6" t="n"/>
       <c r="G205" s="5" t="n"/>
-      <c r="H205" s="6" t="n"/>
+      <c r="H205" s="5" t="n"/>
+      <c r="I205" s="6" t="n"/>
     </row>
     <row r="206" ht="43.2" customHeight="1">
       <c r="A206" s="4" t="n">
@@ -3162,12 +3380,13 @@
       </c>
       <c r="D206" s="6" t="n"/>
       <c r="E206" s="6" t="n"/>
-      <c r="F206" s="5" t="n"/>
-      <c r="G206" s="5">
+      <c r="F206" s="6" t="n"/>
+      <c r="G206" s="5" t="n"/>
+      <c r="H206" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H206" s="6" t="inlineStr">
+      <c r="I206" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 2, 45)</t>
         </is>
@@ -3181,9 +3400,10 @@
       <c r="C207" s="6" t="n"/>
       <c r="D207" s="6" t="n"/>
       <c r="E207" s="6" t="n"/>
-      <c r="F207" s="5" t="n"/>
+      <c r="F207" s="6" t="n"/>
       <c r="G207" s="5" t="n"/>
-      <c r="H207" s="6" t="n"/>
+      <c r="H207" s="5" t="n"/>
+      <c r="I207" s="6" t="n"/>
     </row>
     <row r="208" outlineLevel="2">
       <c r="A208" s="4" t="n">
@@ -3193,9 +3413,10 @@
       <c r="C208" s="6" t="n"/>
       <c r="D208" s="6" t="n"/>
       <c r="E208" s="6" t="n"/>
-      <c r="F208" s="5" t="n"/>
+      <c r="F208" s="6" t="n"/>
       <c r="G208" s="5" t="n"/>
-      <c r="H208" s="6" t="n"/>
+      <c r="H208" s="5" t="n"/>
+      <c r="I208" s="6" t="n"/>
     </row>
     <row r="209" outlineLevel="2">
       <c r="A209" s="4" t="n">
@@ -3205,9 +3426,10 @@
       <c r="C209" s="6" t="n"/>
       <c r="D209" s="6" t="n"/>
       <c r="E209" s="6" t="n"/>
-      <c r="F209" s="5" t="n"/>
+      <c r="F209" s="6" t="n"/>
       <c r="G209" s="5" t="n"/>
-      <c r="H209" s="6" t="n"/>
+      <c r="H209" s="5" t="n"/>
+      <c r="I209" s="6" t="n"/>
     </row>
     <row r="210" outlineLevel="1">
       <c r="A210" s="4" t="n">
@@ -3217,9 +3439,10 @@
       <c r="C210" s="6" t="n"/>
       <c r="D210" s="6" t="n"/>
       <c r="E210" s="6" t="n"/>
-      <c r="F210" s="5" t="n"/>
+      <c r="F210" s="6" t="n"/>
       <c r="G210" s="5" t="n"/>
-      <c r="H210" s="6" t="n"/>
+      <c r="H210" s="5" t="n"/>
+      <c r="I210" s="6" t="n"/>
     </row>
     <row r="211" outlineLevel="2">
       <c r="A211" s="4" t="n">
@@ -3229,9 +3452,10 @@
       <c r="C211" s="6" t="n"/>
       <c r="D211" s="6" t="n"/>
       <c r="E211" s="6" t="n"/>
-      <c r="F211" s="5" t="n"/>
+      <c r="F211" s="6" t="n"/>
       <c r="G211" s="5" t="n"/>
-      <c r="H211" s="6" t="n"/>
+      <c r="H211" s="5" t="n"/>
+      <c r="I211" s="6" t="n"/>
     </row>
     <row r="212" outlineLevel="2">
       <c r="A212" s="4" t="n">
@@ -3241,9 +3465,10 @@
       <c r="C212" s="6" t="n"/>
       <c r="D212" s="6" t="n"/>
       <c r="E212" s="6" t="n"/>
-      <c r="F212" s="5" t="n"/>
+      <c r="F212" s="6" t="n"/>
       <c r="G212" s="5" t="n"/>
-      <c r="H212" s="6" t="n"/>
+      <c r="H212" s="5" t="n"/>
+      <c r="I212" s="6" t="n"/>
     </row>
     <row r="213" outlineLevel="2">
       <c r="A213" s="4" t="n">
@@ -3253,9 +3478,10 @@
       <c r="C213" s="6" t="n"/>
       <c r="D213" s="6" t="n"/>
       <c r="E213" s="6" t="n"/>
-      <c r="F213" s="5" t="n"/>
+      <c r="F213" s="6" t="n"/>
       <c r="G213" s="5" t="n"/>
-      <c r="H213" s="6" t="n"/>
+      <c r="H213" s="5" t="n"/>
+      <c r="I213" s="6" t="n"/>
     </row>
     <row r="214" outlineLevel="1">
       <c r="A214" s="4" t="n">
@@ -3265,9 +3491,10 @@
       <c r="C214" s="6" t="n"/>
       <c r="D214" s="6" t="n"/>
       <c r="E214" s="6" t="n"/>
-      <c r="F214" s="5" t="n"/>
+      <c r="F214" s="6" t="n"/>
       <c r="G214" s="5" t="n"/>
-      <c r="H214" s="6" t="n"/>
+      <c r="H214" s="5" t="n"/>
+      <c r="I214" s="6" t="n"/>
     </row>
     <row r="215" outlineLevel="2">
       <c r="A215" s="4" t="n">
@@ -3277,9 +3504,10 @@
       <c r="C215" s="6" t="n"/>
       <c r="D215" s="6" t="n"/>
       <c r="E215" s="6" t="n"/>
-      <c r="F215" s="5" t="n"/>
+      <c r="F215" s="6" t="n"/>
       <c r="G215" s="5" t="n"/>
-      <c r="H215" s="6" t="n"/>
+      <c r="H215" s="5" t="n"/>
+      <c r="I215" s="6" t="n"/>
     </row>
     <row r="216" outlineLevel="2">
       <c r="A216" s="4" t="n">
@@ -3289,9 +3517,10 @@
       <c r="C216" s="6" t="n"/>
       <c r="D216" s="6" t="n"/>
       <c r="E216" s="6" t="n"/>
-      <c r="F216" s="5" t="n"/>
+      <c r="F216" s="6" t="n"/>
       <c r="G216" s="5" t="n"/>
-      <c r="H216" s="6" t="n"/>
+      <c r="H216" s="5" t="n"/>
+      <c r="I216" s="6" t="n"/>
     </row>
     <row r="217" outlineLevel="2">
       <c r="A217" s="4" t="n">
@@ -3301,9 +3530,10 @@
       <c r="C217" s="6" t="n"/>
       <c r="D217" s="6" t="n"/>
       <c r="E217" s="6" t="n"/>
-      <c r="F217" s="5" t="n"/>
+      <c r="F217" s="6" t="n"/>
       <c r="G217" s="5" t="n"/>
-      <c r="H217" s="6" t="n"/>
+      <c r="H217" s="5" t="n"/>
+      <c r="I217" s="6" t="n"/>
     </row>
     <row r="218" outlineLevel="1">
       <c r="A218" s="4" t="n">
@@ -3313,9 +3543,10 @@
       <c r="C218" s="6" t="n"/>
       <c r="D218" s="6" t="n"/>
       <c r="E218" s="6" t="n"/>
-      <c r="F218" s="5" t="n"/>
+      <c r="F218" s="6" t="n"/>
       <c r="G218" s="5" t="n"/>
-      <c r="H218" s="6" t="n"/>
+      <c r="H218" s="5" t="n"/>
+      <c r="I218" s="6" t="n"/>
     </row>
     <row r="219" outlineLevel="2">
       <c r="A219" s="4" t="n">
@@ -3325,9 +3556,10 @@
       <c r="C219" s="6" t="n"/>
       <c r="D219" s="6" t="n"/>
       <c r="E219" s="6" t="n"/>
-      <c r="F219" s="5" t="n"/>
+      <c r="F219" s="6" t="n"/>
       <c r="G219" s="5" t="n"/>
-      <c r="H219" s="6" t="n"/>
+      <c r="H219" s="5" t="n"/>
+      <c r="I219" s="6" t="n"/>
     </row>
     <row r="220" outlineLevel="2">
       <c r="A220" s="4" t="n">
@@ -3337,9 +3569,10 @@
       <c r="C220" s="6" t="n"/>
       <c r="D220" s="6" t="n"/>
       <c r="E220" s="6" t="n"/>
-      <c r="F220" s="5" t="n"/>
+      <c r="F220" s="6" t="n"/>
       <c r="G220" s="5" t="n"/>
-      <c r="H220" s="6" t="n"/>
+      <c r="H220" s="5" t="n"/>
+      <c r="I220" s="6" t="n"/>
     </row>
     <row r="221" outlineLevel="2">
       <c r="A221" s="4" t="n">
@@ -3349,9 +3582,10 @@
       <c r="C221" s="6" t="n"/>
       <c r="D221" s="6" t="n"/>
       <c r="E221" s="6" t="n"/>
-      <c r="F221" s="5" t="n"/>
+      <c r="F221" s="6" t="n"/>
       <c r="G221" s="5" t="n"/>
-      <c r="H221" s="6" t="n"/>
+      <c r="H221" s="5" t="n"/>
+      <c r="I221" s="6" t="n"/>
     </row>
     <row r="222" ht="28.8" customHeight="1">
       <c r="A222" s="4" t="n">
@@ -3362,20 +3596,26 @@
           <t>verse 1b</t>
         </is>
       </c>
-      <c r="C222" s="6" t="inlineStr">
+      <c r="C222" s="8" t="inlineStr">
+        <is>
+          <t>SCENE_VERSE_PLASMA, Farben SCHEME_ICE
+kleine Steigerung zum Part davor, ohne zweiten Regen: ruhige Farbwolken in Eisblau auf der Matrix, der Farbverlauf dreht sich um Gitarre und Bass und steigt in den Lampen auf, alles schwillt im Beat leicht an</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
         <is>
           <t>SCENE_VERSE, Farben SCHEME_ICE
 Dezenter Puls im Beat in Eisblau - kleine Steigerung zum Part davor.</t>
         </is>
       </c>
-      <c r="D222" s="6" t="n"/>
       <c r="E222" s="6" t="n"/>
-      <c r="F222" s="5" t="n"/>
-      <c r="G222" s="5">
+      <c r="F222" s="6" t="n"/>
+      <c r="G222" s="5" t="n"/>
+      <c r="H222" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H222" s="6" t="inlineStr">
+      <c r="I222" s="6" t="inlineStr">
         <is>
           <t>progPalette(8495, 3, 50)</t>
         </is>
@@ -3389,9 +3629,10 @@
       <c r="C223" s="6" t="n"/>
       <c r="D223" s="6" t="n"/>
       <c r="E223" s="6" t="n"/>
-      <c r="F223" s="5" t="n"/>
+      <c r="F223" s="6" t="n"/>
       <c r="G223" s="5" t="n"/>
-      <c r="H223" s="6" t="n"/>
+      <c r="H223" s="5" t="n"/>
+      <c r="I223" s="6" t="n"/>
     </row>
     <row r="224" outlineLevel="2">
       <c r="A224" s="4" t="n">
@@ -3401,9 +3642,10 @@
       <c r="C224" s="6" t="n"/>
       <c r="D224" s="6" t="n"/>
       <c r="E224" s="6" t="n"/>
-      <c r="F224" s="5" t="n"/>
+      <c r="F224" s="6" t="n"/>
       <c r="G224" s="5" t="n"/>
-      <c r="H224" s="6" t="n"/>
+      <c r="H224" s="5" t="n"/>
+      <c r="I224" s="6" t="n"/>
     </row>
     <row r="225" outlineLevel="2">
       <c r="A225" s="4" t="n">
@@ -3413,9 +3655,10 @@
       <c r="C225" s="6" t="n"/>
       <c r="D225" s="6" t="n"/>
       <c r="E225" s="6" t="n"/>
-      <c r="F225" s="5" t="n"/>
+      <c r="F225" s="6" t="n"/>
       <c r="G225" s="5" t="n"/>
-      <c r="H225" s="6" t="n"/>
+      <c r="H225" s="5" t="n"/>
+      <c r="I225" s="6" t="n"/>
     </row>
     <row r="226" outlineLevel="1">
       <c r="A226" s="4" t="n">
@@ -3425,9 +3668,10 @@
       <c r="C226" s="6" t="n"/>
       <c r="D226" s="6" t="n"/>
       <c r="E226" s="6" t="n"/>
-      <c r="F226" s="5" t="n"/>
+      <c r="F226" s="6" t="n"/>
       <c r="G226" s="5" t="n"/>
-      <c r="H226" s="6" t="n"/>
+      <c r="H226" s="5" t="n"/>
+      <c r="I226" s="6" t="n"/>
     </row>
     <row r="227" outlineLevel="2">
       <c r="A227" s="4" t="n">
@@ -3437,9 +3681,10 @@
       <c r="C227" s="6" t="n"/>
       <c r="D227" s="6" t="n"/>
       <c r="E227" s="6" t="n"/>
-      <c r="F227" s="5" t="n"/>
+      <c r="F227" s="6" t="n"/>
       <c r="G227" s="5" t="n"/>
-      <c r="H227" s="6" t="n"/>
+      <c r="H227" s="5" t="n"/>
+      <c r="I227" s="6" t="n"/>
     </row>
     <row r="228" outlineLevel="2">
       <c r="A228" s="4" t="n">
@@ -3449,9 +3694,10 @@
       <c r="C228" s="6" t="n"/>
       <c r="D228" s="6" t="n"/>
       <c r="E228" s="6" t="n"/>
-      <c r="F228" s="5" t="n"/>
+      <c r="F228" s="6" t="n"/>
       <c r="G228" s="5" t="n"/>
-      <c r="H228" s="6" t="n"/>
+      <c r="H228" s="5" t="n"/>
+      <c r="I228" s="6" t="n"/>
     </row>
     <row r="229" outlineLevel="2">
       <c r="A229" s="4" t="n">
@@ -3461,9 +3707,10 @@
       <c r="C229" s="6" t="n"/>
       <c r="D229" s="6" t="n"/>
       <c r="E229" s="6" t="n"/>
-      <c r="F229" s="5" t="n"/>
+      <c r="F229" s="6" t="n"/>
       <c r="G229" s="5" t="n"/>
-      <c r="H229" s="6" t="n"/>
+      <c r="H229" s="5" t="n"/>
+      <c r="I229" s="6" t="n"/>
     </row>
     <row r="230" outlineLevel="1">
       <c r="A230" s="4" t="n">
@@ -3473,9 +3720,10 @@
       <c r="C230" s="6" t="n"/>
       <c r="D230" s="6" t="n"/>
       <c r="E230" s="6" t="n"/>
-      <c r="F230" s="5" t="n"/>
+      <c r="F230" s="6" t="n"/>
       <c r="G230" s="5" t="n"/>
-      <c r="H230" s="6" t="n"/>
+      <c r="H230" s="5" t="n"/>
+      <c r="I230" s="6" t="n"/>
     </row>
     <row r="231" outlineLevel="2">
       <c r="A231" s="4" t="n">
@@ -3485,9 +3733,10 @@
       <c r="C231" s="6" t="n"/>
       <c r="D231" s="6" t="n"/>
       <c r="E231" s="6" t="n"/>
-      <c r="F231" s="5" t="n"/>
+      <c r="F231" s="6" t="n"/>
       <c r="G231" s="5" t="n"/>
-      <c r="H231" s="6" t="n"/>
+      <c r="H231" s="5" t="n"/>
+      <c r="I231" s="6" t="n"/>
     </row>
     <row r="232" outlineLevel="2">
       <c r="A232" s="4" t="n">
@@ -3497,9 +3746,10 @@
       <c r="C232" s="6" t="n"/>
       <c r="D232" s="6" t="n"/>
       <c r="E232" s="6" t="n"/>
-      <c r="F232" s="5" t="n"/>
+      <c r="F232" s="6" t="n"/>
       <c r="G232" s="5" t="n"/>
-      <c r="H232" s="6" t="n"/>
+      <c r="H232" s="5" t="n"/>
+      <c r="I232" s="6" t="n"/>
     </row>
     <row r="233" outlineLevel="2">
       <c r="A233" s="4" t="n">
@@ -3509,9 +3759,10 @@
       <c r="C233" s="6" t="n"/>
       <c r="D233" s="6" t="n"/>
       <c r="E233" s="6" t="n"/>
-      <c r="F233" s="5" t="n"/>
+      <c r="F233" s="6" t="n"/>
       <c r="G233" s="5" t="n"/>
-      <c r="H233" s="6" t="n"/>
+      <c r="H233" s="5" t="n"/>
+      <c r="I233" s="6" t="n"/>
     </row>
     <row r="234" outlineLevel="1">
       <c r="A234" s="4" t="n">
@@ -3521,9 +3772,10 @@
       <c r="C234" s="6" t="n"/>
       <c r="D234" s="6" t="n"/>
       <c r="E234" s="6" t="n"/>
-      <c r="F234" s="5" t="n"/>
+      <c r="F234" s="6" t="n"/>
       <c r="G234" s="5" t="n"/>
-      <c r="H234" s="6" t="n"/>
+      <c r="H234" s="5" t="n"/>
+      <c r="I234" s="6" t="n"/>
     </row>
     <row r="235" outlineLevel="2">
       <c r="A235" s="4" t="n">
@@ -3533,9 +3785,10 @@
       <c r="C235" s="6" t="n"/>
       <c r="D235" s="6" t="n"/>
       <c r="E235" s="6" t="n"/>
-      <c r="F235" s="5" t="n"/>
+      <c r="F235" s="6" t="n"/>
       <c r="G235" s="5" t="n"/>
-      <c r="H235" s="6" t="n"/>
+      <c r="H235" s="5" t="n"/>
+      <c r="I235" s="6" t="n"/>
     </row>
     <row r="236" outlineLevel="2">
       <c r="A236" s="4" t="n">
@@ -3545,9 +3798,10 @@
       <c r="C236" s="6" t="n"/>
       <c r="D236" s="6" t="n"/>
       <c r="E236" s="6" t="n"/>
-      <c r="F236" s="5" t="n"/>
+      <c r="F236" s="6" t="n"/>
       <c r="G236" s="5" t="n"/>
-      <c r="H236" s="6" t="n"/>
+      <c r="H236" s="5" t="n"/>
+      <c r="I236" s="6" t="n"/>
     </row>
     <row r="237" outlineLevel="2">
       <c r="A237" s="4" t="n">
@@ -3557,9 +3811,10 @@
       <c r="C237" s="6" t="n"/>
       <c r="D237" s="6" t="n"/>
       <c r="E237" s="6" t="n"/>
-      <c r="F237" s="5" t="n"/>
+      <c r="F237" s="6" t="n"/>
       <c r="G237" s="5" t="n"/>
-      <c r="H237" s="6" t="n"/>
+      <c r="H237" s="5" t="n"/>
+      <c r="I237" s="6" t="n"/>
     </row>
     <row r="238" ht="57.6" customHeight="1">
       <c r="A238" s="4" t="n">
@@ -3581,12 +3836,13 @@
       </c>
       <c r="D238" s="6" t="n"/>
       <c r="E238" s="6" t="n"/>
-      <c r="F238" s="5" t="n"/>
-      <c r="G238" s="5">
+      <c r="F238" s="6" t="n"/>
+      <c r="G238" s="5" t="n"/>
+      <c r="H238" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H238" s="6" t="inlineStr">
+      <c r="I238" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 55, 1060)</t>
         </is>
@@ -3600,9 +3856,10 @@
       <c r="C239" s="6" t="n"/>
       <c r="D239" s="6" t="n"/>
       <c r="E239" s="6" t="n"/>
-      <c r="F239" s="5" t="n"/>
+      <c r="F239" s="6" t="n"/>
       <c r="G239" s="5" t="n"/>
-      <c r="H239" s="6" t="n"/>
+      <c r="H239" s="5" t="n"/>
+      <c r="I239" s="6" t="n"/>
     </row>
     <row r="240" outlineLevel="2">
       <c r="A240" s="4" t="n">
@@ -3612,9 +3869,10 @@
       <c r="C240" s="6" t="n"/>
       <c r="D240" s="6" t="n"/>
       <c r="E240" s="6" t="n"/>
-      <c r="F240" s="5" t="n"/>
+      <c r="F240" s="6" t="n"/>
       <c r="G240" s="5" t="n"/>
-      <c r="H240" s="6" t="n"/>
+      <c r="H240" s="5" t="n"/>
+      <c r="I240" s="6" t="n"/>
     </row>
     <row r="241" outlineLevel="2">
       <c r="A241" s="4" t="n">
@@ -3624,9 +3882,10 @@
       <c r="C241" s="6" t="n"/>
       <c r="D241" s="6" t="n"/>
       <c r="E241" s="6" t="n"/>
-      <c r="F241" s="5" t="n"/>
+      <c r="F241" s="6" t="n"/>
       <c r="G241" s="5" t="n"/>
-      <c r="H241" s="6" t="n"/>
+      <c r="H241" s="5" t="n"/>
+      <c r="I241" s="6" t="n"/>
     </row>
     <row r="242" outlineLevel="1">
       <c r="A242" s="4" t="n">
@@ -3634,10 +3893,11 @@
       </c>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6" t="n"/>
-      <c r="E242" s="6" t="n"/>
-      <c r="F242" s="5" t="n"/>
+      <c r="D242" s="6" t="n"/>
+      <c r="F242" s="6" t="n"/>
       <c r="G242" s="5" t="n"/>
-      <c r="H242" s="6" t="n"/>
+      <c r="H242" s="5" t="n"/>
+      <c r="I242" s="6" t="n"/>
     </row>
     <row r="243" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A243" s="4" t="n">
@@ -3647,9 +3907,10 @@
       <c r="C243" s="6" t="n"/>
       <c r="D243" s="6" t="n"/>
       <c r="E243" s="6" t="n"/>
-      <c r="F243" s="5" t="n"/>
+      <c r="F243" s="6" t="n"/>
       <c r="G243" s="5" t="n"/>
-      <c r="H243" s="6" t="n"/>
+      <c r="H243" s="5" t="n"/>
+      <c r="I243" s="6" t="n"/>
     </row>
     <row r="244" outlineLevel="2">
       <c r="A244" s="4" t="n">
@@ -3659,9 +3920,10 @@
       <c r="C244" s="6" t="n"/>
       <c r="D244" s="6" t="n"/>
       <c r="E244" s="6" t="n"/>
-      <c r="F244" s="5" t="n"/>
+      <c r="F244" s="6" t="n"/>
       <c r="G244" s="5" t="n"/>
-      <c r="H244" s="6" t="n"/>
+      <c r="H244" s="5" t="n"/>
+      <c r="I244" s="6" t="n"/>
     </row>
     <row r="245" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A245" s="4" t="n">
@@ -3671,9 +3933,10 @@
       <c r="C245" s="6" t="n"/>
       <c r="D245" s="6" t="n"/>
       <c r="E245" s="6" t="n"/>
-      <c r="F245" s="5" t="n"/>
+      <c r="F245" s="6" t="n"/>
       <c r="G245" s="5" t="n"/>
-      <c r="H245" s="6" t="n"/>
+      <c r="H245" s="5" t="n"/>
+      <c r="I245" s="6" t="n"/>
     </row>
     <row r="246" outlineLevel="1">
       <c r="A246" s="4" t="n">
@@ -3683,9 +3946,10 @@
       <c r="C246" s="6" t="n"/>
       <c r="D246" s="6" t="n"/>
       <c r="E246" s="6" t="n"/>
-      <c r="F246" s="5" t="n"/>
+      <c r="F246" s="6" t="n"/>
       <c r="G246" s="5" t="n"/>
-      <c r="H246" s="6" t="n"/>
+      <c r="H246" s="5" t="n"/>
+      <c r="I246" s="6" t="n"/>
     </row>
     <row r="247" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A247" s="4" t="n">
@@ -3697,15 +3961,16 @@
           <t>HERE steht zwei Viertel, bis IN kommt</t>
         </is>
       </c>
-      <c r="D247" s="6" t="inlineStr">
+      <c r="D247" s="6" t="n"/>
+      <c r="E247" s="6" t="inlineStr">
         <is>
           <t>HERE -&gt; möglichst lange stehen lassen (bis der nächste text kommt)</t>
         </is>
       </c>
-      <c r="E247" s="6" t="n"/>
-      <c r="F247" s="5" t="n"/>
+      <c r="F247" s="6" t="n"/>
       <c r="G247" s="5" t="n"/>
-      <c r="H247" s="6" t="n"/>
+      <c r="H247" s="5" t="n"/>
+      <c r="I247" s="6" t="n"/>
     </row>
     <row r="248" outlineLevel="2">
       <c r="A248" s="4" t="n">
@@ -3715,9 +3980,10 @@
       <c r="C248" s="6" t="n"/>
       <c r="D248" s="6" t="n"/>
       <c r="E248" s="6" t="n"/>
-      <c r="F248" s="5" t="n"/>
+      <c r="F248" s="6" t="n"/>
       <c r="G248" s="5" t="n"/>
-      <c r="H248" s="6" t="n"/>
+      <c r="H248" s="5" t="n"/>
+      <c r="I248" s="6" t="n"/>
     </row>
     <row r="249" outlineLevel="2">
       <c r="A249" s="4" t="n">
@@ -3727,9 +3993,10 @@
       <c r="C249" s="6" t="n"/>
       <c r="D249" s="6" t="n"/>
       <c r="E249" s="6" t="n"/>
-      <c r="F249" s="5" t="n"/>
+      <c r="F249" s="6" t="n"/>
       <c r="G249" s="5" t="n"/>
-      <c r="H249" s="6" t="n"/>
+      <c r="H249" s="5" t="n"/>
+      <c r="I249" s="6" t="n"/>
     </row>
     <row r="250" outlineLevel="1">
       <c r="A250" s="4" t="n">
@@ -3739,9 +4006,10 @@
       <c r="C250" s="6" t="n"/>
       <c r="D250" s="6" t="n"/>
       <c r="E250" s="6" t="n"/>
-      <c r="F250" s="5" t="n"/>
+      <c r="F250" s="6" t="n"/>
       <c r="G250" s="5" t="n"/>
-      <c r="H250" s="6" t="n"/>
+      <c r="H250" s="5" t="n"/>
+      <c r="I250" s="6" t="n"/>
     </row>
     <row r="251" outlineLevel="2">
       <c r="A251" s="4" t="n">
@@ -3751,9 +4019,10 @@
       <c r="C251" s="6" t="n"/>
       <c r="D251" s="6" t="n"/>
       <c r="E251" s="6" t="n"/>
-      <c r="F251" s="5" t="n"/>
+      <c r="F251" s="6" t="n"/>
       <c r="G251" s="5" t="n"/>
-      <c r="H251" s="6" t="n"/>
+      <c r="H251" s="5" t="n"/>
+      <c r="I251" s="6" t="n"/>
     </row>
     <row r="252" outlineLevel="2">
       <c r="A252" s="4" t="n">
@@ -3763,9 +4032,10 @@
       <c r="C252" s="6" t="n"/>
       <c r="D252" s="6" t="n"/>
       <c r="E252" s="6" t="n"/>
-      <c r="F252" s="5" t="n"/>
+      <c r="F252" s="6" t="n"/>
       <c r="G252" s="5" t="n"/>
-      <c r="H252" s="6" t="n"/>
+      <c r="H252" s="5" t="n"/>
+      <c r="I252" s="6" t="n"/>
     </row>
     <row r="253" outlineLevel="2">
       <c r="A253" s="4" t="n">
@@ -3775,9 +4045,10 @@
       <c r="C253" s="6" t="n"/>
       <c r="D253" s="6" t="n"/>
       <c r="E253" s="6" t="n"/>
-      <c r="F253" s="5" t="n"/>
+      <c r="F253" s="6" t="n"/>
       <c r="G253" s="5" t="n"/>
-      <c r="H253" s="6" t="n"/>
+      <c r="H253" s="5" t="n"/>
+      <c r="I253" s="6" t="n"/>
     </row>
     <row r="254" ht="28.8" customHeight="1">
       <c r="A254" s="4" t="n">
@@ -3798,12 +4069,13 @@
       </c>
       <c r="D254" s="6" t="n"/>
       <c r="E254" s="6" t="n"/>
-      <c r="F254" s="5" t="n"/>
-      <c r="G254" s="5">
+      <c r="F254" s="6" t="n"/>
+      <c r="G254" s="5" t="n"/>
+      <c r="H254" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H254" s="6" t="inlineStr">
+      <c r="I254" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 60, 50, getRandomCRGB())</t>
         </is>
@@ -3817,9 +4089,10 @@
       <c r="C255" s="6" t="n"/>
       <c r="D255" s="6" t="n"/>
       <c r="E255" s="6" t="n"/>
-      <c r="F255" s="5" t="n"/>
+      <c r="F255" s="6" t="n"/>
       <c r="G255" s="5" t="n"/>
-      <c r="H255" s="6" t="n"/>
+      <c r="H255" s="5" t="n"/>
+      <c r="I255" s="6" t="n"/>
     </row>
     <row r="256" outlineLevel="2">
       <c r="A256" s="4" t="n">
@@ -3829,9 +4102,10 @@
       <c r="C256" s="6" t="n"/>
       <c r="D256" s="6" t="n"/>
       <c r="E256" s="6" t="n"/>
-      <c r="F256" s="5" t="n"/>
+      <c r="F256" s="6" t="n"/>
       <c r="G256" s="5" t="n"/>
-      <c r="H256" s="6" t="n"/>
+      <c r="H256" s="5" t="n"/>
+      <c r="I256" s="6" t="n"/>
     </row>
     <row r="257" outlineLevel="2">
       <c r="A257" s="4" t="n">
@@ -3841,9 +4115,10 @@
       <c r="C257" s="6" t="n"/>
       <c r="D257" s="6" t="n"/>
       <c r="E257" s="6" t="n"/>
-      <c r="F257" s="5" t="n"/>
+      <c r="F257" s="6" t="n"/>
       <c r="G257" s="5" t="n"/>
-      <c r="H257" s="6" t="n"/>
+      <c r="H257" s="5" t="n"/>
+      <c r="I257" s="6" t="n"/>
     </row>
     <row r="258" outlineLevel="1">
       <c r="A258" s="4" t="n">
@@ -3853,9 +4128,10 @@
       <c r="C258" s="6" t="n"/>
       <c r="D258" s="6" t="n"/>
       <c r="E258" s="6" t="n"/>
-      <c r="F258" s="5" t="n"/>
+      <c r="F258" s="6" t="n"/>
       <c r="G258" s="5" t="n"/>
-      <c r="H258" s="6" t="n"/>
+      <c r="H258" s="5" t="n"/>
+      <c r="I258" s="6" t="n"/>
     </row>
     <row r="259" outlineLevel="2">
       <c r="A259" s="4" t="n">
@@ -3865,9 +4141,10 @@
       <c r="C259" s="6" t="n"/>
       <c r="D259" s="6" t="n"/>
       <c r="E259" s="6" t="n"/>
-      <c r="F259" s="5" t="n"/>
+      <c r="F259" s="6" t="n"/>
       <c r="G259" s="5" t="n"/>
-      <c r="H259" s="6" t="n"/>
+      <c r="H259" s="5" t="n"/>
+      <c r="I259" s="6" t="n"/>
     </row>
     <row r="260" outlineLevel="2">
       <c r="A260" s="4" t="n">
@@ -3877,9 +4154,10 @@
       <c r="C260" s="6" t="n"/>
       <c r="D260" s="6" t="n"/>
       <c r="E260" s="6" t="n"/>
-      <c r="F260" s="5" t="n"/>
+      <c r="F260" s="6" t="n"/>
       <c r="G260" s="5" t="n"/>
-      <c r="H260" s="6" t="n"/>
+      <c r="H260" s="5" t="n"/>
+      <c r="I260" s="6" t="n"/>
     </row>
     <row r="261" outlineLevel="2">
       <c r="A261" s="4" t="n">
@@ -3889,9 +4167,10 @@
       <c r="C261" s="6" t="n"/>
       <c r="D261" s="6" t="n"/>
       <c r="E261" s="6" t="n"/>
-      <c r="F261" s="5" t="n"/>
+      <c r="F261" s="6" t="n"/>
       <c r="G261" s="5" t="n"/>
-      <c r="H261" s="6" t="n"/>
+      <c r="H261" s="5" t="n"/>
+      <c r="I261" s="6" t="n"/>
     </row>
     <row r="262" outlineLevel="1">
       <c r="A262" s="4" t="n">
@@ -3901,9 +4180,10 @@
       <c r="C262" s="6" t="n"/>
       <c r="D262" s="6" t="n"/>
       <c r="E262" s="6" t="n"/>
-      <c r="F262" s="5" t="n"/>
+      <c r="F262" s="6" t="n"/>
       <c r="G262" s="5" t="n"/>
-      <c r="H262" s="6" t="n"/>
+      <c r="H262" s="5" t="n"/>
+      <c r="I262" s="6" t="n"/>
     </row>
     <row r="263" outlineLevel="2">
       <c r="A263" s="4" t="n">
@@ -3913,9 +4193,10 @@
       <c r="C263" s="6" t="n"/>
       <c r="D263" s="6" t="n"/>
       <c r="E263" s="6" t="n"/>
-      <c r="F263" s="5" t="n"/>
+      <c r="F263" s="6" t="n"/>
       <c r="G263" s="5" t="n"/>
-      <c r="H263" s="6" t="n"/>
+      <c r="H263" s="5" t="n"/>
+      <c r="I263" s="6" t="n"/>
     </row>
     <row r="264" outlineLevel="2">
       <c r="A264" s="4" t="n">
@@ -3925,9 +4206,10 @@
       <c r="C264" s="6" t="n"/>
       <c r="D264" s="6" t="n"/>
       <c r="E264" s="6" t="n"/>
-      <c r="F264" s="5" t="n"/>
+      <c r="F264" s="6" t="n"/>
       <c r="G264" s="5" t="n"/>
-      <c r="H264" s="6" t="n"/>
+      <c r="H264" s="5" t="n"/>
+      <c r="I264" s="6" t="n"/>
     </row>
     <row r="265" outlineLevel="2">
       <c r="A265" s="4" t="n">
@@ -3937,9 +4219,10 @@
       <c r="C265" s="6" t="n"/>
       <c r="D265" s="6" t="n"/>
       <c r="E265" s="6" t="n"/>
-      <c r="F265" s="5" t="n"/>
+      <c r="F265" s="6" t="n"/>
       <c r="G265" s="5" t="n"/>
-      <c r="H265" s="6" t="n"/>
+      <c r="H265" s="5" t="n"/>
+      <c r="I265" s="6" t="n"/>
     </row>
     <row r="266" outlineLevel="1">
       <c r="A266" s="4" t="n">
@@ -3949,9 +4232,10 @@
       <c r="C266" s="6" t="n"/>
       <c r="D266" s="6" t="n"/>
       <c r="E266" s="6" t="n"/>
-      <c r="F266" s="5" t="n"/>
+      <c r="F266" s="6" t="n"/>
       <c r="G266" s="5" t="n"/>
-      <c r="H266" s="6" t="n"/>
+      <c r="H266" s="5" t="n"/>
+      <c r="I266" s="6" t="n"/>
     </row>
     <row r="267" outlineLevel="2">
       <c r="A267" s="4" t="n">
@@ -3961,9 +4245,10 @@
       <c r="C267" s="6" t="n"/>
       <c r="D267" s="6" t="n"/>
       <c r="E267" s="6" t="n"/>
-      <c r="F267" s="5" t="n"/>
+      <c r="F267" s="6" t="n"/>
       <c r="G267" s="5" t="n"/>
-      <c r="H267" s="6" t="n"/>
+      <c r="H267" s="5" t="n"/>
+      <c r="I267" s="6" t="n"/>
     </row>
     <row r="268" outlineLevel="2">
       <c r="A268" s="4" t="n">
@@ -3973,9 +4258,10 @@
       <c r="C268" s="6" t="n"/>
       <c r="D268" s="6" t="n"/>
       <c r="E268" s="6" t="n"/>
-      <c r="F268" s="5" t="n"/>
+      <c r="F268" s="6" t="n"/>
       <c r="G268" s="5" t="n"/>
-      <c r="H268" s="6" t="n"/>
+      <c r="H268" s="5" t="n"/>
+      <c r="I268" s="6" t="n"/>
     </row>
     <row r="269" outlineLevel="2">
       <c r="A269" s="4" t="n">
@@ -3985,9 +4271,10 @@
       <c r="C269" s="6" t="n"/>
       <c r="D269" s="6" t="n"/>
       <c r="E269" s="6" t="n"/>
-      <c r="F269" s="5" t="n"/>
+      <c r="F269" s="6" t="n"/>
       <c r="G269" s="5" t="n"/>
-      <c r="H269" s="6" t="n"/>
+      <c r="H269" s="5" t="n"/>
+      <c r="I269" s="6" t="n"/>
     </row>
     <row r="270" ht="72" customHeight="1">
       <c r="A270" s="4" t="n">
@@ -4008,12 +4295,13 @@
       </c>
       <c r="D270" s="6" t="n"/>
       <c r="E270" s="6" t="n"/>
-      <c r="F270" s="5" t="n"/>
-      <c r="G270" s="5">
+      <c r="F270" s="6" t="n"/>
+      <c r="G270" s="5" t="n"/>
+      <c r="H270" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H270" s="6" t="inlineStr">
+      <c r="I270" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 65, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 65))</t>
         </is>
@@ -4027,9 +4315,10 @@
       <c r="C271" s="6" t="n"/>
       <c r="D271" s="6" t="n"/>
       <c r="E271" s="6" t="n"/>
-      <c r="F271" s="5" t="n"/>
+      <c r="F271" s="6" t="n"/>
       <c r="G271" s="5" t="n"/>
-      <c r="H271" s="6" t="n"/>
+      <c r="H271" s="5" t="n"/>
+      <c r="I271" s="6" t="n"/>
     </row>
     <row r="272" outlineLevel="2">
       <c r="A272" s="4" t="n">
@@ -4039,9 +4328,10 @@
       <c r="C272" s="6" t="n"/>
       <c r="D272" s="6" t="n"/>
       <c r="E272" s="6" t="n"/>
-      <c r="F272" s="5" t="n"/>
+      <c r="F272" s="6" t="n"/>
       <c r="G272" s="5" t="n"/>
-      <c r="H272" s="6" t="n"/>
+      <c r="H272" s="5" t="n"/>
+      <c r="I272" s="6" t="n"/>
     </row>
     <row r="273" outlineLevel="2">
       <c r="A273" s="4" t="n">
@@ -4051,9 +4341,10 @@
       <c r="C273" s="6" t="n"/>
       <c r="D273" s="6" t="n"/>
       <c r="E273" s="6" t="n"/>
-      <c r="F273" s="5" t="n"/>
+      <c r="F273" s="6" t="n"/>
       <c r="G273" s="5" t="n"/>
-      <c r="H273" s="6" t="n"/>
+      <c r="H273" s="5" t="n"/>
+      <c r="I273" s="6" t="n"/>
     </row>
     <row r="274" ht="57.6" customHeight="1">
       <c r="A274" s="4" t="n">
@@ -4073,12 +4364,13 @@
       </c>
       <c r="D274" s="6" t="n"/>
       <c r="E274" s="6" t="n"/>
-      <c r="F274" s="5" t="n"/>
-      <c r="G274" s="5">
+      <c r="F274" s="6" t="n"/>
+      <c r="G274" s="5" t="n"/>
+      <c r="H274" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H274" s="6" t="inlineStr">
+      <c r="I274" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 70)</t>
         </is>
@@ -4092,9 +4384,10 @@
       <c r="C275" s="6" t="n"/>
       <c r="D275" s="6" t="n"/>
       <c r="E275" s="6" t="n"/>
-      <c r="F275" s="5" t="n"/>
+      <c r="F275" s="6" t="n"/>
       <c r="G275" s="5" t="n"/>
-      <c r="H275" s="6" t="n"/>
+      <c r="H275" s="5" t="n"/>
+      <c r="I275" s="6" t="n"/>
     </row>
     <row r="276" outlineLevel="2">
       <c r="A276" s="4" t="n">
@@ -4104,9 +4397,10 @@
       <c r="C276" s="6" t="n"/>
       <c r="D276" s="6" t="n"/>
       <c r="E276" s="6" t="n"/>
-      <c r="F276" s="5" t="n"/>
+      <c r="F276" s="6" t="n"/>
       <c r="G276" s="5" t="n"/>
-      <c r="H276" s="6" t="n"/>
+      <c r="H276" s="5" t="n"/>
+      <c r="I276" s="6" t="n"/>
     </row>
     <row r="277" outlineLevel="2">
       <c r="A277" s="4" t="n">
@@ -4116,9 +4410,10 @@
       <c r="C277" s="6" t="n"/>
       <c r="D277" s="6" t="n"/>
       <c r="E277" s="6" t="n"/>
-      <c r="F277" s="5" t="n"/>
+      <c r="F277" s="6" t="n"/>
       <c r="G277" s="5" t="n"/>
-      <c r="H277" s="6" t="n"/>
+      <c r="H277" s="5" t="n"/>
+      <c r="I277" s="6" t="n"/>
     </row>
     <row r="278" outlineLevel="1">
       <c r="A278" s="4" t="n">
@@ -4128,9 +4423,10 @@
       <c r="C278" s="6" t="n"/>
       <c r="D278" s="6" t="n"/>
       <c r="E278" s="6" t="n"/>
-      <c r="F278" s="5" t="n"/>
+      <c r="F278" s="6" t="n"/>
       <c r="G278" s="5" t="n"/>
-      <c r="H278" s="6" t="n"/>
+      <c r="H278" s="5" t="n"/>
+      <c r="I278" s="6" t="n"/>
     </row>
     <row r="279" outlineLevel="2">
       <c r="A279" s="4" t="n">
@@ -4140,9 +4436,10 @@
       <c r="C279" s="6" t="n"/>
       <c r="D279" s="6" t="n"/>
       <c r="E279" s="6" t="n"/>
-      <c r="F279" s="5" t="n"/>
+      <c r="F279" s="6" t="n"/>
       <c r="G279" s="5" t="n"/>
-      <c r="H279" s="6" t="n"/>
+      <c r="H279" s="5" t="n"/>
+      <c r="I279" s="6" t="n"/>
     </row>
     <row r="280" outlineLevel="2">
       <c r="A280" s="4" t="n">
@@ -4152,9 +4449,10 @@
       <c r="C280" s="6" t="n"/>
       <c r="D280" s="6" t="n"/>
       <c r="E280" s="6" t="n"/>
-      <c r="F280" s="5" t="n"/>
+      <c r="F280" s="6" t="n"/>
       <c r="G280" s="5" t="n"/>
-      <c r="H280" s="6" t="n"/>
+      <c r="H280" s="5" t="n"/>
+      <c r="I280" s="6" t="n"/>
     </row>
     <row r="281" outlineLevel="2">
       <c r="A281" s="4" t="n">
@@ -4164,9 +4462,10 @@
       <c r="C281" s="6" t="n"/>
       <c r="D281" s="6" t="n"/>
       <c r="E281" s="6" t="n"/>
-      <c r="F281" s="5" t="n"/>
+      <c r="F281" s="6" t="n"/>
       <c r="G281" s="5" t="n"/>
-      <c r="H281" s="6" t="n"/>
+      <c r="H281" s="5" t="n"/>
+      <c r="I281" s="6" t="n"/>
     </row>
     <row r="282" outlineLevel="1">
       <c r="A282" s="4" t="n">
@@ -4176,9 +4475,10 @@
       <c r="C282" s="6" t="n"/>
       <c r="D282" s="6" t="n"/>
       <c r="E282" s="6" t="n"/>
-      <c r="F282" s="5" t="n"/>
+      <c r="F282" s="6" t="n"/>
       <c r="G282" s="5" t="n"/>
-      <c r="H282" s="6" t="n"/>
+      <c r="H282" s="5" t="n"/>
+      <c r="I282" s="6" t="n"/>
     </row>
     <row r="283" outlineLevel="2">
       <c r="A283" s="4" t="n">
@@ -4188,9 +4488,10 @@
       <c r="C283" s="6" t="n"/>
       <c r="D283" s="6" t="n"/>
       <c r="E283" s="6" t="n"/>
-      <c r="F283" s="5" t="n"/>
+      <c r="F283" s="6" t="n"/>
       <c r="G283" s="5" t="n"/>
-      <c r="H283" s="6" t="n"/>
+      <c r="H283" s="5" t="n"/>
+      <c r="I283" s="6" t="n"/>
     </row>
     <row r="284" outlineLevel="2">
       <c r="A284" s="4" t="n">
@@ -4200,9 +4501,10 @@
       <c r="C284" s="6" t="n"/>
       <c r="D284" s="6" t="n"/>
       <c r="E284" s="6" t="n"/>
-      <c r="F284" s="5" t="n"/>
+      <c r="F284" s="6" t="n"/>
       <c r="G284" s="5" t="n"/>
-      <c r="H284" s="6" t="n"/>
+      <c r="H284" s="5" t="n"/>
+      <c r="I284" s="6" t="n"/>
     </row>
     <row r="285" outlineLevel="2">
       <c r="A285" s="4" t="n">
@@ -4212,9 +4514,10 @@
       <c r="C285" s="6" t="n"/>
       <c r="D285" s="6" t="n"/>
       <c r="E285" s="6" t="n"/>
-      <c r="F285" s="5" t="n"/>
+      <c r="F285" s="6" t="n"/>
       <c r="G285" s="5" t="n"/>
-      <c r="H285" s="6" t="n"/>
+      <c r="H285" s="5" t="n"/>
+      <c r="I285" s="6" t="n"/>
     </row>
     <row r="286" outlineLevel="1">
       <c r="A286" s="4" t="n">
@@ -4224,9 +4527,10 @@
       <c r="C286" s="6" t="n"/>
       <c r="D286" s="6" t="n"/>
       <c r="E286" s="6" t="n"/>
-      <c r="F286" s="5" t="n"/>
+      <c r="F286" s="6" t="n"/>
       <c r="G286" s="5" t="n"/>
-      <c r="H286" s="6" t="n"/>
+      <c r="H286" s="5" t="n"/>
+      <c r="I286" s="6" t="n"/>
     </row>
     <row r="287" outlineLevel="2">
       <c r="A287" s="4" t="n">
@@ -4236,9 +4540,10 @@
       <c r="C287" s="6" t="n"/>
       <c r="D287" s="6" t="n"/>
       <c r="E287" s="6" t="n"/>
-      <c r="F287" s="5" t="n"/>
+      <c r="F287" s="6" t="n"/>
       <c r="G287" s="5" t="n"/>
-      <c r="H287" s="6" t="n"/>
+      <c r="H287" s="5" t="n"/>
+      <c r="I287" s="6" t="n"/>
     </row>
     <row r="288" outlineLevel="2">
       <c r="A288" s="4" t="n">
@@ -4248,9 +4553,10 @@
       <c r="C288" s="6" t="n"/>
       <c r="D288" s="6" t="n"/>
       <c r="E288" s="6" t="n"/>
-      <c r="F288" s="5" t="n"/>
+      <c r="F288" s="6" t="n"/>
       <c r="G288" s="5" t="n"/>
-      <c r="H288" s="6" t="n"/>
+      <c r="H288" s="5" t="n"/>
+      <c r="I288" s="6" t="n"/>
     </row>
     <row r="289" outlineLevel="2">
       <c r="A289" s="4" t="n">
@@ -4260,9 +4566,10 @@
       <c r="C289" s="6" t="n"/>
       <c r="D289" s="6" t="n"/>
       <c r="E289" s="6" t="n"/>
-      <c r="F289" s="5" t="n"/>
+      <c r="F289" s="6" t="n"/>
       <c r="G289" s="5" t="n"/>
-      <c r="H289" s="6" t="n"/>
+      <c r="H289" s="5" t="n"/>
+      <c r="I289" s="6" t="n"/>
     </row>
     <row r="290" ht="28.8" customHeight="1">
       <c r="A290" s="4" t="n">
@@ -4281,12 +4588,13 @@
       </c>
       <c r="D290" s="6" t="n"/>
       <c r="E290" s="6" t="n"/>
-      <c r="F290" s="5" t="n"/>
-      <c r="G290" s="5">
+      <c r="F290" s="6" t="n"/>
+      <c r="G290" s="5" t="n"/>
+      <c r="H290" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H290" s="6" t="inlineStr">
+      <c r="I290" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 75)</t>
         </is>
@@ -4300,9 +4608,10 @@
       <c r="C291" s="6" t="n"/>
       <c r="D291" s="6" t="n"/>
       <c r="E291" s="6" t="n"/>
-      <c r="F291" s="5" t="n"/>
+      <c r="F291" s="6" t="n"/>
       <c r="G291" s="5" t="n"/>
-      <c r="H291" s="6" t="n"/>
+      <c r="H291" s="5" t="n"/>
+      <c r="I291" s="6" t="n"/>
     </row>
     <row r="292" outlineLevel="2">
       <c r="A292" s="4" t="n">
@@ -4312,9 +4621,10 @@
       <c r="C292" s="6" t="n"/>
       <c r="D292" s="6" t="n"/>
       <c r="E292" s="6" t="n"/>
-      <c r="F292" s="5" t="n"/>
+      <c r="F292" s="6" t="n"/>
       <c r="G292" s="5" t="n"/>
-      <c r="H292" s="6" t="n"/>
+      <c r="H292" s="5" t="n"/>
+      <c r="I292" s="6" t="n"/>
     </row>
     <row r="293" outlineLevel="2">
       <c r="A293" s="4" t="n">
@@ -4324,9 +4634,10 @@
       <c r="C293" s="6" t="n"/>
       <c r="D293" s="6" t="n"/>
       <c r="E293" s="6" t="n"/>
-      <c r="F293" s="5" t="n"/>
+      <c r="F293" s="6" t="n"/>
       <c r="G293" s="5" t="n"/>
-      <c r="H293" s="6" t="n"/>
+      <c r="H293" s="5" t="n"/>
+      <c r="I293" s="6" t="n"/>
     </row>
     <row r="294" outlineLevel="1">
       <c r="A294" s="4" t="n">
@@ -4336,9 +4647,10 @@
       <c r="C294" s="6" t="n"/>
       <c r="D294" s="6" t="n"/>
       <c r="E294" s="6" t="n"/>
-      <c r="F294" s="5" t="n"/>
+      <c r="F294" s="6" t="n"/>
       <c r="G294" s="5" t="n"/>
-      <c r="H294" s="6" t="n"/>
+      <c r="H294" s="5" t="n"/>
+      <c r="I294" s="6" t="n"/>
     </row>
     <row r="295" outlineLevel="2">
       <c r="A295" s="4" t="n">
@@ -4348,9 +4660,10 @@
       <c r="C295" s="6" t="n"/>
       <c r="D295" s="6" t="n"/>
       <c r="E295" s="6" t="n"/>
-      <c r="F295" s="5" t="n"/>
+      <c r="F295" s="6" t="n"/>
       <c r="G295" s="5" t="n"/>
-      <c r="H295" s="6" t="n"/>
+      <c r="H295" s="5" t="n"/>
+      <c r="I295" s="6" t="n"/>
     </row>
     <row r="296" outlineLevel="2">
       <c r="A296" s="4" t="n">
@@ -4360,9 +4673,10 @@
       <c r="C296" s="6" t="n"/>
       <c r="D296" s="6" t="n"/>
       <c r="E296" s="6" t="n"/>
-      <c r="F296" s="5" t="n"/>
+      <c r="F296" s="6" t="n"/>
       <c r="G296" s="5" t="n"/>
-      <c r="H296" s="6" t="n"/>
+      <c r="H296" s="5" t="n"/>
+      <c r="I296" s="6" t="n"/>
     </row>
     <row r="297" outlineLevel="2">
       <c r="A297" s="4" t="n">
@@ -4372,9 +4686,10 @@
       <c r="C297" s="6" t="n"/>
       <c r="D297" s="6" t="n"/>
       <c r="E297" s="6" t="n"/>
-      <c r="F297" s="5" t="n"/>
+      <c r="F297" s="6" t="n"/>
       <c r="G297" s="5" t="n"/>
-      <c r="H297" s="6" t="n"/>
+      <c r="H297" s="5" t="n"/>
+      <c r="I297" s="6" t="n"/>
     </row>
     <row r="298" outlineLevel="1">
       <c r="A298" s="4" t="n">
@@ -4384,9 +4699,10 @@
       <c r="C298" s="6" t="n"/>
       <c r="D298" s="6" t="n"/>
       <c r="E298" s="6" t="n"/>
-      <c r="F298" s="5" t="n"/>
+      <c r="F298" s="6" t="n"/>
       <c r="G298" s="5" t="n"/>
-      <c r="H298" s="6" t="n"/>
+      <c r="H298" s="5" t="n"/>
+      <c r="I298" s="6" t="n"/>
     </row>
     <row r="299" outlineLevel="2">
       <c r="A299" s="4" t="n">
@@ -4396,9 +4712,10 @@
       <c r="C299" s="6" t="n"/>
       <c r="D299" s="6" t="n"/>
       <c r="E299" s="6" t="n"/>
-      <c r="F299" s="5" t="n"/>
+      <c r="F299" s="6" t="n"/>
       <c r="G299" s="5" t="n"/>
-      <c r="H299" s="6" t="n"/>
+      <c r="H299" s="5" t="n"/>
+      <c r="I299" s="6" t="n"/>
     </row>
     <row r="300" outlineLevel="2">
       <c r="A300" s="4" t="n">
@@ -4408,9 +4725,10 @@
       <c r="C300" s="6" t="n"/>
       <c r="D300" s="6" t="n"/>
       <c r="E300" s="6" t="n"/>
-      <c r="F300" s="5" t="n"/>
+      <c r="F300" s="6" t="n"/>
       <c r="G300" s="5" t="n"/>
-      <c r="H300" s="6" t="n"/>
+      <c r="H300" s="5" t="n"/>
+      <c r="I300" s="6" t="n"/>
     </row>
     <row r="301" outlineLevel="2">
       <c r="A301" s="4" t="n">
@@ -4420,9 +4738,10 @@
       <c r="C301" s="6" t="n"/>
       <c r="D301" s="6" t="n"/>
       <c r="E301" s="6" t="n"/>
-      <c r="F301" s="5" t="n"/>
+      <c r="F301" s="6" t="n"/>
       <c r="G301" s="5" t="n"/>
-      <c r="H301" s="6" t="n"/>
+      <c r="H301" s="5" t="n"/>
+      <c r="I301" s="6" t="n"/>
     </row>
     <row r="302" outlineLevel="1">
       <c r="A302" s="4" t="n">
@@ -4432,9 +4751,10 @@
       <c r="C302" s="6" t="n"/>
       <c r="D302" s="6" t="n"/>
       <c r="E302" s="6" t="n"/>
-      <c r="F302" s="5" t="n"/>
+      <c r="F302" s="6" t="n"/>
       <c r="G302" s="5" t="n"/>
-      <c r="H302" s="6" t="n"/>
+      <c r="H302" s="5" t="n"/>
+      <c r="I302" s="6" t="n"/>
     </row>
     <row r="303" outlineLevel="2">
       <c r="A303" s="4" t="n">
@@ -4444,9 +4764,10 @@
       <c r="C303" s="6" t="n"/>
       <c r="D303" s="6" t="n"/>
       <c r="E303" s="6" t="n"/>
-      <c r="F303" s="5" t="n"/>
+      <c r="F303" s="6" t="n"/>
       <c r="G303" s="5" t="n"/>
-      <c r="H303" s="6" t="n"/>
+      <c r="H303" s="5" t="n"/>
+      <c r="I303" s="6" t="n"/>
     </row>
     <row r="304" outlineLevel="2">
       <c r="A304" s="4" t="n">
@@ -4456,9 +4777,10 @@
       <c r="C304" s="6" t="n"/>
       <c r="D304" s="6" t="n"/>
       <c r="E304" s="6" t="n"/>
-      <c r="F304" s="5" t="n"/>
+      <c r="F304" s="6" t="n"/>
       <c r="G304" s="5" t="n"/>
-      <c r="H304" s="6" t="n"/>
+      <c r="H304" s="5" t="n"/>
+      <c r="I304" s="6" t="n"/>
     </row>
     <row r="305" outlineLevel="2">
       <c r="A305" s="4" t="n">
@@ -4468,9 +4790,10 @@
       <c r="C305" s="6" t="n"/>
       <c r="D305" s="6" t="n"/>
       <c r="E305" s="6" t="n"/>
-      <c r="F305" s="5" t="n"/>
+      <c r="F305" s="6" t="n"/>
       <c r="G305" s="5" t="n"/>
-      <c r="H305" s="6" t="n"/>
+      <c r="H305" s="5" t="n"/>
+      <c r="I305" s="6" t="n"/>
     </row>
     <row r="306" ht="43.2" customHeight="1">
       <c r="A306" s="4" t="n">
@@ -4490,18 +4813,19 @@
 Bass-Solo: zwei schnelle orange Kometen jagen um den Bass, auf jeder Eins blitzt der Bass warmweiß auf - er leuchtet voll, alles andere mit 45 %. Dort spielen Gitarre und Lampen Frage/Antwort im Takt, auf der Matrix dreht sich die Doppelhelix (eine Umdrehung in 2 Takten); die Farben wandern alle 2 Takte von Blau/Lila zur Gegenfarbe und zurück.</t>
         </is>
       </c>
-      <c r="D306" s="6" t="inlineStr">
+      <c r="D306" s="6" t="n"/>
+      <c r="E306" s="6" t="inlineStr">
         <is>
           <t>diese solo scene ist von der idee her gut (also Fokus auf das intrument mit dem solo, rest etwas dezenter). Aber das ist hier doch sehr langweilig! Das solo instzrument (hier der bass) muss deutlich rauskommen, aber auf den anderen geräter muss etwas mehr und interessanteres laufen. überleg dir mal etwas neues dafür!!</t>
         </is>
       </c>
-      <c r="E306" s="6" t="n"/>
-      <c r="F306" s="5" t="n"/>
-      <c r="G306" s="5">
+      <c r="F306" s="6" t="n"/>
+      <c r="G306" s="5" t="n"/>
+      <c r="H306" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H306" s="6" t="inlineStr">
+      <c r="I306" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(16990, 80, 50, true, true)
 ! der alte Code setzt hier Marker: markerLED5 = ESaite_F_hoch</t>
@@ -4516,9 +4840,10 @@
       <c r="C307" s="6" t="n"/>
       <c r="D307" s="6" t="n"/>
       <c r="E307" s="6" t="n"/>
-      <c r="F307" s="5" t="n"/>
+      <c r="F307" s="6" t="n"/>
       <c r="G307" s="5" t="n"/>
-      <c r="H307" s="6" t="n"/>
+      <c r="H307" s="5" t="n"/>
+      <c r="I307" s="6" t="n"/>
     </row>
     <row r="308" outlineLevel="2">
       <c r="A308" s="4" t="n">
@@ -4528,9 +4853,10 @@
       <c r="C308" s="6" t="n"/>
       <c r="D308" s="6" t="n"/>
       <c r="E308" s="6" t="n"/>
-      <c r="F308" s="5" t="n"/>
+      <c r="F308" s="6" t="n"/>
       <c r="G308" s="5" t="n"/>
-      <c r="H308" s="6" t="n"/>
+      <c r="H308" s="5" t="n"/>
+      <c r="I308" s="6" t="n"/>
     </row>
     <row r="309" outlineLevel="2">
       <c r="A309" s="4" t="n">
@@ -4540,9 +4866,10 @@
       <c r="C309" s="6" t="n"/>
       <c r="D309" s="6" t="n"/>
       <c r="E309" s="6" t="n"/>
-      <c r="F309" s="5" t="n"/>
+      <c r="F309" s="6" t="n"/>
       <c r="G309" s="5" t="n"/>
-      <c r="H309" s="6" t="n"/>
+      <c r="H309" s="5" t="n"/>
+      <c r="I309" s="6" t="n"/>
     </row>
     <row r="310" outlineLevel="1">
       <c r="A310" s="4" t="n">
@@ -4552,9 +4879,10 @@
       <c r="C310" s="6" t="n"/>
       <c r="D310" s="6" t="n"/>
       <c r="E310" s="6" t="n"/>
-      <c r="F310" s="5" t="n"/>
+      <c r="F310" s="6" t="n"/>
       <c r="G310" s="5" t="n"/>
-      <c r="H310" s="6" t="n"/>
+      <c r="H310" s="5" t="n"/>
+      <c r="I310" s="6" t="n"/>
     </row>
     <row r="311" outlineLevel="2">
       <c r="A311" s="4" t="n">
@@ -4564,9 +4892,10 @@
       <c r="C311" s="6" t="n"/>
       <c r="D311" s="6" t="n"/>
       <c r="E311" s="6" t="n"/>
-      <c r="F311" s="5" t="n"/>
+      <c r="F311" s="6" t="n"/>
       <c r="G311" s="5" t="n"/>
-      <c r="H311" s="6" t="n"/>
+      <c r="H311" s="5" t="n"/>
+      <c r="I311" s="6" t="n"/>
     </row>
     <row r="312" outlineLevel="2">
       <c r="A312" s="4" t="n">
@@ -4576,9 +4905,10 @@
       <c r="C312" s="6" t="n"/>
       <c r="D312" s="6" t="n"/>
       <c r="E312" s="6" t="n"/>
-      <c r="F312" s="5" t="n"/>
+      <c r="F312" s="6" t="n"/>
       <c r="G312" s="5" t="n"/>
-      <c r="H312" s="6" t="n"/>
+      <c r="H312" s="5" t="n"/>
+      <c r="I312" s="6" t="n"/>
     </row>
     <row r="313" outlineLevel="2">
       <c r="A313" s="4" t="n">
@@ -4588,9 +4918,10 @@
       <c r="C313" s="6" t="n"/>
       <c r="D313" s="6" t="n"/>
       <c r="E313" s="6" t="n"/>
-      <c r="F313" s="5" t="n"/>
+      <c r="F313" s="6" t="n"/>
       <c r="G313" s="5" t="n"/>
-      <c r="H313" s="6" t="n"/>
+      <c r="H313" s="5" t="n"/>
+      <c r="I313" s="6" t="n"/>
     </row>
     <row r="314" outlineLevel="1">
       <c r="A314" s="4" t="n">
@@ -4600,9 +4931,10 @@
       <c r="C314" s="6" t="n"/>
       <c r="D314" s="6" t="n"/>
       <c r="E314" s="6" t="n"/>
-      <c r="F314" s="5" t="n"/>
+      <c r="F314" s="6" t="n"/>
       <c r="G314" s="5" t="n"/>
-      <c r="H314" s="6" t="n"/>
+      <c r="H314" s="5" t="n"/>
+      <c r="I314" s="6" t="n"/>
     </row>
     <row r="315" outlineLevel="2">
       <c r="A315" s="4" t="n">
@@ -4612,9 +4944,10 @@
       <c r="C315" s="6" t="n"/>
       <c r="D315" s="6" t="n"/>
       <c r="E315" s="6" t="n"/>
-      <c r="F315" s="5" t="n"/>
+      <c r="F315" s="6" t="n"/>
       <c r="G315" s="5" t="n"/>
-      <c r="H315" s="6" t="n"/>
+      <c r="H315" s="5" t="n"/>
+      <c r="I315" s="6" t="n"/>
     </row>
     <row r="316" outlineLevel="2">
       <c r="A316" s="4" t="n">
@@ -4624,9 +4957,10 @@
       <c r="C316" s="6" t="n"/>
       <c r="D316" s="6" t="n"/>
       <c r="E316" s="6" t="n"/>
-      <c r="F316" s="5" t="n"/>
+      <c r="F316" s="6" t="n"/>
       <c r="G316" s="5" t="n"/>
-      <c r="H316" s="6" t="n"/>
+      <c r="H316" s="5" t="n"/>
+      <c r="I316" s="6" t="n"/>
     </row>
     <row r="317" outlineLevel="2">
       <c r="A317" s="4" t="n">
@@ -4636,9 +4970,10 @@
       <c r="C317" s="6" t="n"/>
       <c r="D317" s="6" t="n"/>
       <c r="E317" s="6" t="n"/>
-      <c r="F317" s="5" t="n"/>
+      <c r="F317" s="6" t="n"/>
       <c r="G317" s="5" t="n"/>
-      <c r="H317" s="6" t="n"/>
+      <c r="H317" s="5" t="n"/>
+      <c r="I317" s="6" t="n"/>
     </row>
     <row r="318" outlineLevel="1">
       <c r="A318" s="4" t="n">
@@ -4648,9 +4983,10 @@
       <c r="C318" s="6" t="n"/>
       <c r="D318" s="6" t="n"/>
       <c r="E318" s="6" t="n"/>
-      <c r="F318" s="5" t="n"/>
+      <c r="F318" s="6" t="n"/>
       <c r="G318" s="5" t="n"/>
-      <c r="H318" s="6" t="n"/>
+      <c r="H318" s="5" t="n"/>
+      <c r="I318" s="6" t="n"/>
     </row>
     <row r="319" outlineLevel="2">
       <c r="A319" s="4" t="n">
@@ -4660,9 +4996,10 @@
       <c r="C319" s="6" t="n"/>
       <c r="D319" s="6" t="n"/>
       <c r="E319" s="6" t="n"/>
-      <c r="F319" s="5" t="n"/>
+      <c r="F319" s="6" t="n"/>
       <c r="G319" s="5" t="n"/>
-      <c r="H319" s="6" t="n"/>
+      <c r="H319" s="5" t="n"/>
+      <c r="I319" s="6" t="n"/>
     </row>
     <row r="320" outlineLevel="2">
       <c r="A320" s="4" t="n">
@@ -4672,9 +5009,10 @@
       <c r="C320" s="6" t="n"/>
       <c r="D320" s="6" t="n"/>
       <c r="E320" s="6" t="n"/>
-      <c r="F320" s="5" t="n"/>
+      <c r="F320" s="6" t="n"/>
       <c r="G320" s="5" t="n"/>
-      <c r="H320" s="6" t="n"/>
+      <c r="H320" s="5" t="n"/>
+      <c r="I320" s="6" t="n"/>
     </row>
     <row r="321" outlineLevel="2">
       <c r="A321" s="4" t="n">
@@ -4684,9 +5022,10 @@
       <c r="C321" s="6" t="n"/>
       <c r="D321" s="6" t="n"/>
       <c r="E321" s="6" t="n"/>
-      <c r="F321" s="5" t="n"/>
+      <c r="F321" s="6" t="n"/>
       <c r="G321" s="5" t="n"/>
-      <c r="H321" s="6" t="n"/>
+      <c r="H321" s="5" t="n"/>
+      <c r="I321" s="6" t="n"/>
     </row>
     <row r="322" outlineLevel="1">
       <c r="A322" s="4" t="n">
@@ -4696,9 +5035,10 @@
       <c r="C322" s="6" t="n"/>
       <c r="D322" s="6" t="n"/>
       <c r="E322" s="6" t="n"/>
-      <c r="F322" s="5" t="n"/>
+      <c r="F322" s="6" t="n"/>
       <c r="G322" s="5" t="n"/>
-      <c r="H322" s="6" t="n"/>
+      <c r="H322" s="5" t="n"/>
+      <c r="I322" s="6" t="n"/>
     </row>
     <row r="323" outlineLevel="2">
       <c r="A323" s="4" t="n">
@@ -4708,9 +5048,10 @@
       <c r="C323" s="6" t="n"/>
       <c r="D323" s="6" t="n"/>
       <c r="E323" s="6" t="n"/>
-      <c r="F323" s="5" t="n"/>
+      <c r="F323" s="6" t="n"/>
       <c r="G323" s="5" t="n"/>
-      <c r="H323" s="6" t="n"/>
+      <c r="H323" s="5" t="n"/>
+      <c r="I323" s="6" t="n"/>
     </row>
     <row r="324" outlineLevel="2">
       <c r="A324" s="4" t="n">
@@ -4720,9 +5061,10 @@
       <c r="C324" s="6" t="n"/>
       <c r="D324" s="6" t="n"/>
       <c r="E324" s="6" t="n"/>
-      <c r="F324" s="5" t="n"/>
+      <c r="F324" s="6" t="n"/>
       <c r="G324" s="5" t="n"/>
-      <c r="H324" s="6" t="n"/>
+      <c r="H324" s="5" t="n"/>
+      <c r="I324" s="6" t="n"/>
     </row>
     <row r="325" outlineLevel="2">
       <c r="A325" s="4" t="n">
@@ -4732,9 +5074,10 @@
       <c r="C325" s="6" t="n"/>
       <c r="D325" s="6" t="n"/>
       <c r="E325" s="6" t="n"/>
-      <c r="F325" s="5" t="n"/>
+      <c r="F325" s="6" t="n"/>
       <c r="G325" s="5" t="n"/>
-      <c r="H325" s="6" t="n"/>
+      <c r="H325" s="5" t="n"/>
+      <c r="I325" s="6" t="n"/>
     </row>
     <row r="326" outlineLevel="1">
       <c r="A326" s="4" t="n">
@@ -4744,9 +5087,10 @@
       <c r="C326" s="6" t="n"/>
       <c r="D326" s="6" t="n"/>
       <c r="E326" s="6" t="n"/>
-      <c r="F326" s="5" t="n"/>
+      <c r="F326" s="6" t="n"/>
       <c r="G326" s="5" t="n"/>
-      <c r="H326" s="6" t="n"/>
+      <c r="H326" s="5" t="n"/>
+      <c r="I326" s="6" t="n"/>
     </row>
     <row r="327" outlineLevel="2">
       <c r="A327" s="4" t="n">
@@ -4756,9 +5100,10 @@
       <c r="C327" s="6" t="n"/>
       <c r="D327" s="6" t="n"/>
       <c r="E327" s="6" t="n"/>
-      <c r="F327" s="5" t="n"/>
+      <c r="F327" s="6" t="n"/>
       <c r="G327" s="5" t="n"/>
-      <c r="H327" s="6" t="n"/>
+      <c r="H327" s="5" t="n"/>
+      <c r="I327" s="6" t="n"/>
     </row>
     <row r="328" outlineLevel="2">
       <c r="A328" s="4" t="n">
@@ -4768,9 +5113,10 @@
       <c r="C328" s="6" t="n"/>
       <c r="D328" s="6" t="n"/>
       <c r="E328" s="6" t="n"/>
-      <c r="F328" s="5" t="n"/>
+      <c r="F328" s="6" t="n"/>
       <c r="G328" s="5" t="n"/>
-      <c r="H328" s="6" t="n"/>
+      <c r="H328" s="5" t="n"/>
+      <c r="I328" s="6" t="n"/>
     </row>
     <row r="329" outlineLevel="2">
       <c r="A329" s="4" t="n">
@@ -4780,9 +5126,10 @@
       <c r="C329" s="6" t="n"/>
       <c r="D329" s="6" t="n"/>
       <c r="E329" s="6" t="n"/>
-      <c r="F329" s="5" t="n"/>
+      <c r="F329" s="6" t="n"/>
       <c r="G329" s="5" t="n"/>
-      <c r="H329" s="6" t="n"/>
+      <c r="H329" s="5" t="n"/>
+      <c r="I329" s="6" t="n"/>
     </row>
     <row r="330" outlineLevel="1">
       <c r="A330" s="4" t="n">
@@ -4792,9 +5139,10 @@
       <c r="C330" s="6" t="n"/>
       <c r="D330" s="6" t="n"/>
       <c r="E330" s="6" t="n"/>
-      <c r="F330" s="5" t="n"/>
+      <c r="F330" s="6" t="n"/>
       <c r="G330" s="5" t="n"/>
-      <c r="H330" s="6" t="n"/>
+      <c r="H330" s="5" t="n"/>
+      <c r="I330" s="6" t="n"/>
     </row>
     <row r="331" outlineLevel="2">
       <c r="A331" s="4" t="n">
@@ -4804,9 +5152,10 @@
       <c r="C331" s="6" t="n"/>
       <c r="D331" s="6" t="n"/>
       <c r="E331" s="6" t="n"/>
-      <c r="F331" s="5" t="n"/>
+      <c r="F331" s="6" t="n"/>
       <c r="G331" s="5" t="n"/>
-      <c r="H331" s="6" t="n"/>
+      <c r="H331" s="5" t="n"/>
+      <c r="I331" s="6" t="n"/>
     </row>
     <row r="332" outlineLevel="2">
       <c r="A332" s="4" t="n">
@@ -4816,9 +5165,10 @@
       <c r="C332" s="6" t="n"/>
       <c r="D332" s="6" t="n"/>
       <c r="E332" s="6" t="n"/>
-      <c r="F332" s="5" t="n"/>
+      <c r="F332" s="6" t="n"/>
       <c r="G332" s="5" t="n"/>
-      <c r="H332" s="6" t="n"/>
+      <c r="H332" s="5" t="n"/>
+      <c r="I332" s="6" t="n"/>
     </row>
     <row r="333" outlineLevel="2">
       <c r="A333" s="4" t="n">
@@ -4828,9 +5178,10 @@
       <c r="C333" s="6" t="n"/>
       <c r="D333" s="6" t="n"/>
       <c r="E333" s="6" t="n"/>
-      <c r="F333" s="5" t="n"/>
+      <c r="F333" s="6" t="n"/>
       <c r="G333" s="5" t="n"/>
-      <c r="H333" s="6" t="n"/>
+      <c r="H333" s="5" t="n"/>
+      <c r="I333" s="6" t="n"/>
     </row>
     <row r="334" outlineLevel="1">
       <c r="A334" s="4" t="n">
@@ -4840,9 +5191,10 @@
       <c r="C334" s="6" t="n"/>
       <c r="D334" s="6" t="n"/>
       <c r="E334" s="6" t="n"/>
-      <c r="F334" s="5" t="n"/>
+      <c r="F334" s="6" t="n"/>
       <c r="G334" s="5" t="n"/>
-      <c r="H334" s="6" t="n"/>
+      <c r="H334" s="5" t="n"/>
+      <c r="I334" s="6" t="n"/>
     </row>
     <row r="335" outlineLevel="2">
       <c r="A335" s="4" t="n">
@@ -4852,9 +5204,10 @@
       <c r="C335" s="6" t="n"/>
       <c r="D335" s="6" t="n"/>
       <c r="E335" s="6" t="n"/>
-      <c r="F335" s="5" t="n"/>
+      <c r="F335" s="6" t="n"/>
       <c r="G335" s="5" t="n"/>
-      <c r="H335" s="6" t="n"/>
+      <c r="H335" s="5" t="n"/>
+      <c r="I335" s="6" t="n"/>
     </row>
     <row r="336" outlineLevel="2">
       <c r="A336" s="4" t="n">
@@ -4864,9 +5217,10 @@
       <c r="C336" s="6" t="n"/>
       <c r="D336" s="6" t="n"/>
       <c r="E336" s="6" t="n"/>
-      <c r="F336" s="5" t="n"/>
+      <c r="F336" s="6" t="n"/>
       <c r="G336" s="5" t="n"/>
-      <c r="H336" s="6" t="n"/>
+      <c r="H336" s="5" t="n"/>
+      <c r="I336" s="6" t="n"/>
     </row>
     <row r="337" outlineLevel="2">
       <c r="A337" s="4" t="n">
@@ -4876,9 +5230,10 @@
       <c r="C337" s="6" t="n"/>
       <c r="D337" s="6" t="n"/>
       <c r="E337" s="6" t="n"/>
-      <c r="F337" s="5" t="n"/>
+      <c r="F337" s="6" t="n"/>
       <c r="G337" s="5" t="n"/>
-      <c r="H337" s="6" t="n"/>
+      <c r="H337" s="5" t="n"/>
+      <c r="I337" s="6" t="n"/>
     </row>
     <row r="338" ht="43.2" customHeight="1">
       <c r="A338" s="4" t="n">
@@ -4900,12 +5255,13 @@
       </c>
       <c r="D338" s="6" t="n"/>
       <c r="E338" s="6" t="n"/>
-      <c r="F338" s="5" t="n"/>
-      <c r="G338" s="5">
+      <c r="F338" s="6" t="n"/>
+      <c r="G338" s="5" t="n"/>
+      <c r="H338" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H338" s="6" t="inlineStr">
+      <c r="I338" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8495, 85, 1060)
 ! der alte Code setzt hier Marker: markerLED5 = 0</t>
@@ -4920,9 +5276,10 @@
       <c r="C339" s="6" t="n"/>
       <c r="D339" s="6" t="n"/>
       <c r="E339" s="6" t="n"/>
-      <c r="F339" s="5" t="n"/>
+      <c r="F339" s="6" t="n"/>
       <c r="G339" s="5" t="n"/>
-      <c r="H339" s="6" t="n"/>
+      <c r="H339" s="5" t="n"/>
+      <c r="I339" s="6" t="n"/>
     </row>
     <row r="340" outlineLevel="2">
       <c r="A340" s="4" t="n">
@@ -4932,9 +5289,10 @@
       <c r="C340" s="6" t="n"/>
       <c r="D340" s="6" t="n"/>
       <c r="E340" s="6" t="n"/>
-      <c r="F340" s="5" t="n"/>
+      <c r="F340" s="6" t="n"/>
       <c r="G340" s="5" t="n"/>
-      <c r="H340" s="6" t="n"/>
+      <c r="H340" s="5" t="n"/>
+      <c r="I340" s="6" t="n"/>
     </row>
     <row r="341" outlineLevel="2">
       <c r="A341" s="4" t="n">
@@ -4944,9 +5302,10 @@
       <c r="C341" s="6" t="n"/>
       <c r="D341" s="6" t="n"/>
       <c r="E341" s="6" t="n"/>
-      <c r="F341" s="5" t="n"/>
+      <c r="F341" s="6" t="n"/>
       <c r="G341" s="5" t="n"/>
-      <c r="H341" s="6" t="n"/>
+      <c r="H341" s="5" t="n"/>
+      <c r="I341" s="6" t="n"/>
     </row>
     <row r="342" outlineLevel="1">
       <c r="A342" s="4" t="n">
@@ -4954,10 +5313,11 @@
       </c>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6" t="n"/>
-      <c r="E342" s="6" t="n"/>
-      <c r="F342" s="5" t="n"/>
+      <c r="D342" s="6" t="n"/>
+      <c r="F342" s="6" t="n"/>
       <c r="G342" s="5" t="n"/>
-      <c r="H342" s="6" t="n"/>
+      <c r="H342" s="5" t="n"/>
+      <c r="I342" s="6" t="n"/>
     </row>
     <row r="343" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A343" s="4" t="n">
@@ -4967,9 +5327,10 @@
       <c r="C343" s="6" t="n"/>
       <c r="D343" s="6" t="n"/>
       <c r="E343" s="6" t="n"/>
-      <c r="F343" s="5" t="n"/>
+      <c r="F343" s="6" t="n"/>
       <c r="G343" s="5" t="n"/>
-      <c r="H343" s="6" t="n"/>
+      <c r="H343" s="5" t="n"/>
+      <c r="I343" s="6" t="n"/>
     </row>
     <row r="344" outlineLevel="2">
       <c r="A344" s="4" t="n">
@@ -4979,9 +5340,10 @@
       <c r="C344" s="6" t="n"/>
       <c r="D344" s="6" t="n"/>
       <c r="E344" s="6" t="n"/>
-      <c r="F344" s="5" t="n"/>
+      <c r="F344" s="6" t="n"/>
       <c r="G344" s="5" t="n"/>
-      <c r="H344" s="6" t="n"/>
+      <c r="H344" s="5" t="n"/>
+      <c r="I344" s="6" t="n"/>
     </row>
     <row r="345" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A345" s="4" t="n">
@@ -4991,9 +5353,10 @@
       <c r="C345" s="6" t="n"/>
       <c r="D345" s="6" t="n"/>
       <c r="E345" s="6" t="n"/>
-      <c r="F345" s="5" t="n"/>
+      <c r="F345" s="6" t="n"/>
       <c r="G345" s="5" t="n"/>
-      <c r="H345" s="6" t="n"/>
+      <c r="H345" s="5" t="n"/>
+      <c r="I345" s="6" t="n"/>
     </row>
     <row r="346" outlineLevel="1">
       <c r="A346" s="4" t="n">
@@ -5003,9 +5366,10 @@
       <c r="C346" s="6" t="n"/>
       <c r="D346" s="6" t="n"/>
       <c r="E346" s="6" t="n"/>
-      <c r="F346" s="5" t="n"/>
+      <c r="F346" s="6" t="n"/>
       <c r="G346" s="5" t="n"/>
-      <c r="H346" s="6" t="n"/>
+      <c r="H346" s="5" t="n"/>
+      <c r="I346" s="6" t="n"/>
     </row>
     <row r="347" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A347" s="4" t="n">
@@ -5017,15 +5381,16 @@
           <t>HERE steht zwei Viertel, bis IN kommt</t>
         </is>
       </c>
-      <c r="D347" s="6" t="inlineStr">
+      <c r="D347" s="6" t="n"/>
+      <c r="E347" s="6" t="inlineStr">
         <is>
           <t>HERE -&gt; möglichst lange stehen lassen (bis der nächste text kommt)</t>
         </is>
       </c>
-      <c r="E347" s="6" t="n"/>
-      <c r="F347" s="5" t="n"/>
+      <c r="F347" s="6" t="n"/>
       <c r="G347" s="5" t="n"/>
-      <c r="H347" s="6" t="n"/>
+      <c r="H347" s="5" t="n"/>
+      <c r="I347" s="6" t="n"/>
     </row>
     <row r="348" outlineLevel="2">
       <c r="A348" s="4" t="n">
@@ -5035,9 +5400,10 @@
       <c r="C348" s="6" t="n"/>
       <c r="D348" s="6" t="n"/>
       <c r="E348" s="6" t="n"/>
-      <c r="F348" s="5" t="n"/>
+      <c r="F348" s="6" t="n"/>
       <c r="G348" s="5" t="n"/>
-      <c r="H348" s="6" t="n"/>
+      <c r="H348" s="5" t="n"/>
+      <c r="I348" s="6" t="n"/>
     </row>
     <row r="349" outlineLevel="2">
       <c r="A349" s="4" t="n">
@@ -5047,9 +5413,10 @@
       <c r="C349" s="6" t="n"/>
       <c r="D349" s="6" t="n"/>
       <c r="E349" s="6" t="n"/>
-      <c r="F349" s="5" t="n"/>
+      <c r="F349" s="6" t="n"/>
       <c r="G349" s="5" t="n"/>
-      <c r="H349" s="6" t="n"/>
+      <c r="H349" s="5" t="n"/>
+      <c r="I349" s="6" t="n"/>
     </row>
     <row r="350" outlineLevel="1">
       <c r="A350" s="4" t="n">
@@ -5059,9 +5426,10 @@
       <c r="C350" s="6" t="n"/>
       <c r="D350" s="6" t="n"/>
       <c r="E350" s="6" t="n"/>
-      <c r="F350" s="5" t="n"/>
+      <c r="F350" s="6" t="n"/>
       <c r="G350" s="5" t="n"/>
-      <c r="H350" s="6" t="n"/>
+      <c r="H350" s="5" t="n"/>
+      <c r="I350" s="6" t="n"/>
     </row>
     <row r="351" outlineLevel="2">
       <c r="A351" s="4" t="n">
@@ -5071,9 +5439,10 @@
       <c r="C351" s="6" t="n"/>
       <c r="D351" s="6" t="n"/>
       <c r="E351" s="6" t="n"/>
-      <c r="F351" s="5" t="n"/>
+      <c r="F351" s="6" t="n"/>
       <c r="G351" s="5" t="n"/>
-      <c r="H351" s="6" t="n"/>
+      <c r="H351" s="5" t="n"/>
+      <c r="I351" s="6" t="n"/>
     </row>
     <row r="352" outlineLevel="2">
       <c r="A352" s="4" t="n">
@@ -5083,9 +5452,10 @@
       <c r="C352" s="6" t="n"/>
       <c r="D352" s="6" t="n"/>
       <c r="E352" s="6" t="n"/>
-      <c r="F352" s="5" t="n"/>
+      <c r="F352" s="6" t="n"/>
       <c r="G352" s="5" t="n"/>
-      <c r="H352" s="6" t="n"/>
+      <c r="H352" s="5" t="n"/>
+      <c r="I352" s="6" t="n"/>
     </row>
     <row r="353" outlineLevel="2">
       <c r="A353" s="4" t="n">
@@ -5095,9 +5465,10 @@
       <c r="C353" s="6" t="n"/>
       <c r="D353" s="6" t="n"/>
       <c r="E353" s="6" t="n"/>
-      <c r="F353" s="5" t="n"/>
+      <c r="F353" s="6" t="n"/>
       <c r="G353" s="5" t="n"/>
-      <c r="H353" s="6" t="n"/>
+      <c r="H353" s="5" t="n"/>
+      <c r="I353" s="6" t="n"/>
     </row>
     <row r="354" ht="28.8" customHeight="1">
       <c r="A354" s="4" t="n">
@@ -5118,12 +5489,13 @@
       </c>
       <c r="D354" s="6" t="n"/>
       <c r="E354" s="6" t="n"/>
-      <c r="F354" s="5" t="n"/>
-      <c r="G354" s="5">
+      <c r="F354" s="6" t="n"/>
+      <c r="G354" s="5" t="n"/>
+      <c r="H354" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H354" s="6" t="inlineStr">
+      <c r="I354" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 90, 50, getRandomCRGB())</t>
         </is>
@@ -5137,9 +5509,10 @@
       <c r="C355" s="6" t="n"/>
       <c r="D355" s="6" t="n"/>
       <c r="E355" s="6" t="n"/>
-      <c r="F355" s="5" t="n"/>
+      <c r="F355" s="6" t="n"/>
       <c r="G355" s="5" t="n"/>
-      <c r="H355" s="6" t="n"/>
+      <c r="H355" s="5" t="n"/>
+      <c r="I355" s="6" t="n"/>
     </row>
     <row r="356" outlineLevel="2">
       <c r="A356" s="4" t="n">
@@ -5149,9 +5522,10 @@
       <c r="C356" s="6" t="n"/>
       <c r="D356" s="6" t="n"/>
       <c r="E356" s="6" t="n"/>
-      <c r="F356" s="5" t="n"/>
+      <c r="F356" s="6" t="n"/>
       <c r="G356" s="5" t="n"/>
-      <c r="H356" s="6" t="n"/>
+      <c r="H356" s="5" t="n"/>
+      <c r="I356" s="6" t="n"/>
     </row>
     <row r="357" outlineLevel="2">
       <c r="A357" s="4" t="n">
@@ -5161,9 +5535,10 @@
       <c r="C357" s="6" t="n"/>
       <c r="D357" s="6" t="n"/>
       <c r="E357" s="6" t="n"/>
-      <c r="F357" s="5" t="n"/>
+      <c r="F357" s="6" t="n"/>
       <c r="G357" s="5" t="n"/>
-      <c r="H357" s="6" t="n"/>
+      <c r="H357" s="5" t="n"/>
+      <c r="I357" s="6" t="n"/>
     </row>
     <row r="358" outlineLevel="1">
       <c r="A358" s="4" t="n">
@@ -5173,9 +5548,10 @@
       <c r="C358" s="6" t="n"/>
       <c r="D358" s="6" t="n"/>
       <c r="E358" s="6" t="n"/>
-      <c r="F358" s="5" t="n"/>
+      <c r="F358" s="6" t="n"/>
       <c r="G358" s="5" t="n"/>
-      <c r="H358" s="6" t="n"/>
+      <c r="H358" s="5" t="n"/>
+      <c r="I358" s="6" t="n"/>
     </row>
     <row r="359" outlineLevel="2">
       <c r="A359" s="4" t="n">
@@ -5185,9 +5561,10 @@
       <c r="C359" s="6" t="n"/>
       <c r="D359" s="6" t="n"/>
       <c r="E359" s="6" t="n"/>
-      <c r="F359" s="5" t="n"/>
+      <c r="F359" s="6" t="n"/>
       <c r="G359" s="5" t="n"/>
-      <c r="H359" s="6" t="n"/>
+      <c r="H359" s="5" t="n"/>
+      <c r="I359" s="6" t="n"/>
     </row>
     <row r="360" outlineLevel="2">
       <c r="A360" s="4" t="n">
@@ -5197,9 +5574,10 @@
       <c r="C360" s="6" t="n"/>
       <c r="D360" s="6" t="n"/>
       <c r="E360" s="6" t="n"/>
-      <c r="F360" s="5" t="n"/>
+      <c r="F360" s="6" t="n"/>
       <c r="G360" s="5" t="n"/>
-      <c r="H360" s="6" t="n"/>
+      <c r="H360" s="5" t="n"/>
+      <c r="I360" s="6" t="n"/>
     </row>
     <row r="361" outlineLevel="2">
       <c r="A361" s="4" t="n">
@@ -5209,9 +5587,10 @@
       <c r="C361" s="6" t="n"/>
       <c r="D361" s="6" t="n"/>
       <c r="E361" s="6" t="n"/>
-      <c r="F361" s="5" t="n"/>
+      <c r="F361" s="6" t="n"/>
       <c r="G361" s="5" t="n"/>
-      <c r="H361" s="6" t="n"/>
+      <c r="H361" s="5" t="n"/>
+      <c r="I361" s="6" t="n"/>
     </row>
     <row r="362" outlineLevel="1">
       <c r="A362" s="4" t="n">
@@ -5221,9 +5600,10 @@
       <c r="C362" s="6" t="n"/>
       <c r="D362" s="6" t="n"/>
       <c r="E362" s="6" t="n"/>
-      <c r="F362" s="5" t="n"/>
+      <c r="F362" s="6" t="n"/>
       <c r="G362" s="5" t="n"/>
-      <c r="H362" s="6" t="n"/>
+      <c r="H362" s="5" t="n"/>
+      <c r="I362" s="6" t="n"/>
     </row>
     <row r="363" outlineLevel="2">
       <c r="A363" s="4" t="n">
@@ -5233,9 +5613,10 @@
       <c r="C363" s="6" t="n"/>
       <c r="D363" s="6" t="n"/>
       <c r="E363" s="6" t="n"/>
-      <c r="F363" s="5" t="n"/>
+      <c r="F363" s="6" t="n"/>
       <c r="G363" s="5" t="n"/>
-      <c r="H363" s="6" t="n"/>
+      <c r="H363" s="5" t="n"/>
+      <c r="I363" s="6" t="n"/>
     </row>
     <row r="364" outlineLevel="2">
       <c r="A364" s="4" t="n">
@@ -5245,9 +5626,10 @@
       <c r="C364" s="6" t="n"/>
       <c r="D364" s="6" t="n"/>
       <c r="E364" s="6" t="n"/>
-      <c r="F364" s="5" t="n"/>
+      <c r="F364" s="6" t="n"/>
       <c r="G364" s="5" t="n"/>
-      <c r="H364" s="6" t="n"/>
+      <c r="H364" s="5" t="n"/>
+      <c r="I364" s="6" t="n"/>
     </row>
     <row r="365" outlineLevel="2">
       <c r="A365" s="4" t="n">
@@ -5257,9 +5639,10 @@
       <c r="C365" s="6" t="n"/>
       <c r="D365" s="6" t="n"/>
       <c r="E365" s="6" t="n"/>
-      <c r="F365" s="5" t="n"/>
+      <c r="F365" s="6" t="n"/>
       <c r="G365" s="5" t="n"/>
-      <c r="H365" s="6" t="n"/>
+      <c r="H365" s="5" t="n"/>
+      <c r="I365" s="6" t="n"/>
     </row>
     <row r="366" outlineLevel="1">
       <c r="A366" s="4" t="n">
@@ -5269,9 +5652,10 @@
       <c r="C366" s="6" t="n"/>
       <c r="D366" s="6" t="n"/>
       <c r="E366" s="6" t="n"/>
-      <c r="F366" s="5" t="n"/>
+      <c r="F366" s="6" t="n"/>
       <c r="G366" s="5" t="n"/>
-      <c r="H366" s="6" t="n"/>
+      <c r="H366" s="5" t="n"/>
+      <c r="I366" s="6" t="n"/>
     </row>
     <row r="367" outlineLevel="2">
       <c r="A367" s="4" t="n">
@@ -5281,9 +5665,10 @@
       <c r="C367" s="6" t="n"/>
       <c r="D367" s="6" t="n"/>
       <c r="E367" s="6" t="n"/>
-      <c r="F367" s="5" t="n"/>
+      <c r="F367" s="6" t="n"/>
       <c r="G367" s="5" t="n"/>
-      <c r="H367" s="6" t="n"/>
+      <c r="H367" s="5" t="n"/>
+      <c r="I367" s="6" t="n"/>
     </row>
     <row r="368" outlineLevel="2">
       <c r="A368" s="4" t="n">
@@ -5293,9 +5678,10 @@
       <c r="C368" s="6" t="n"/>
       <c r="D368" s="6" t="n"/>
       <c r="E368" s="6" t="n"/>
-      <c r="F368" s="5" t="n"/>
+      <c r="F368" s="6" t="n"/>
       <c r="G368" s="5" t="n"/>
-      <c r="H368" s="6" t="n"/>
+      <c r="H368" s="5" t="n"/>
+      <c r="I368" s="6" t="n"/>
     </row>
     <row r="369" outlineLevel="2">
       <c r="A369" s="4" t="n">
@@ -5305,9 +5691,10 @@
       <c r="C369" s="6" t="n"/>
       <c r="D369" s="6" t="n"/>
       <c r="E369" s="6" t="n"/>
-      <c r="F369" s="5" t="n"/>
+      <c r="F369" s="6" t="n"/>
       <c r="G369" s="5" t="n"/>
-      <c r="H369" s="6" t="n"/>
+      <c r="H369" s="5" t="n"/>
+      <c r="I369" s="6" t="n"/>
     </row>
     <row r="370" ht="43.2" customHeight="1">
       <c r="A370" s="4" t="n">
@@ -5329,12 +5716,13 @@
       </c>
       <c r="D370" s="6" t="n"/>
       <c r="E370" s="6" t="n"/>
-      <c r="F370" s="5" t="n"/>
-      <c r="G370" s="5">
+      <c r="F370" s="6" t="n"/>
+      <c r="G370" s="5" t="n"/>
+      <c r="H370" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H370" s="6" t="inlineStr">
+      <c r="I370" s="6" t="inlineStr">
         <is>
           <t>progFullColors(8500, 95, 1060)</t>
         </is>
@@ -5348,9 +5736,10 @@
       <c r="C371" s="6" t="n"/>
       <c r="D371" s="6" t="n"/>
       <c r="E371" s="6" t="n"/>
-      <c r="F371" s="5" t="n"/>
+      <c r="F371" s="6" t="n"/>
       <c r="G371" s="5" t="n"/>
-      <c r="H371" s="6" t="n"/>
+      <c r="H371" s="5" t="n"/>
+      <c r="I371" s="6" t="n"/>
     </row>
     <row r="372" outlineLevel="2">
       <c r="A372" s="4" t="n">
@@ -5360,9 +5749,10 @@
       <c r="C372" s="6" t="n"/>
       <c r="D372" s="6" t="n"/>
       <c r="E372" s="6" t="n"/>
-      <c r="F372" s="5" t="n"/>
+      <c r="F372" s="6" t="n"/>
       <c r="G372" s="5" t="n"/>
-      <c r="H372" s="6" t="n"/>
+      <c r="H372" s="5" t="n"/>
+      <c r="I372" s="6" t="n"/>
     </row>
     <row r="373" outlineLevel="2">
       <c r="A373" s="4" t="n">
@@ -5372,9 +5762,10 @@
       <c r="C373" s="6" t="n"/>
       <c r="D373" s="6" t="n"/>
       <c r="E373" s="6" t="n"/>
-      <c r="F373" s="5" t="n"/>
+      <c r="F373" s="6" t="n"/>
       <c r="G373" s="5" t="n"/>
-      <c r="H373" s="6" t="n"/>
+      <c r="H373" s="5" t="n"/>
+      <c r="I373" s="6" t="n"/>
     </row>
     <row r="374" outlineLevel="1">
       <c r="A374" s="4" t="n">
@@ -5382,10 +5773,11 @@
       </c>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6" t="n"/>
-      <c r="E374" s="6" t="n"/>
-      <c r="F374" s="5" t="n"/>
+      <c r="D374" s="6" t="n"/>
+      <c r="F374" s="6" t="n"/>
       <c r="G374" s="5" t="n"/>
-      <c r="H374" s="6" t="n"/>
+      <c r="H374" s="5" t="n"/>
+      <c r="I374" s="6" t="n"/>
     </row>
     <row r="375" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A375" s="4" t="n">
@@ -5395,9 +5787,10 @@
       <c r="C375" s="6" t="n"/>
       <c r="D375" s="6" t="n"/>
       <c r="E375" s="6" t="n"/>
-      <c r="F375" s="5" t="n"/>
+      <c r="F375" s="6" t="n"/>
       <c r="G375" s="5" t="n"/>
-      <c r="H375" s="6" t="n"/>
+      <c r="H375" s="5" t="n"/>
+      <c r="I375" s="6" t="n"/>
     </row>
     <row r="376" outlineLevel="2">
       <c r="A376" s="4" t="n">
@@ -5407,9 +5800,10 @@
       <c r="C376" s="6" t="n"/>
       <c r="D376" s="6" t="n"/>
       <c r="E376" s="6" t="n"/>
-      <c r="F376" s="5" t="n"/>
+      <c r="F376" s="6" t="n"/>
       <c r="G376" s="5" t="n"/>
-      <c r="H376" s="6" t="n"/>
+      <c r="H376" s="5" t="n"/>
+      <c r="I376" s="6" t="n"/>
     </row>
     <row r="377" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A377" s="4" t="n">
@@ -5419,9 +5813,10 @@
       <c r="C377" s="6" t="n"/>
       <c r="D377" s="6" t="n"/>
       <c r="E377" s="6" t="n"/>
-      <c r="F377" s="5" t="n"/>
+      <c r="F377" s="6" t="n"/>
       <c r="G377" s="5" t="n"/>
-      <c r="H377" s="6" t="n"/>
+      <c r="H377" s="5" t="n"/>
+      <c r="I377" s="6" t="n"/>
     </row>
     <row r="378" outlineLevel="1">
       <c r="A378" s="4" t="n">
@@ -5431,9 +5826,10 @@
       <c r="C378" s="6" t="n"/>
       <c r="D378" s="6" t="n"/>
       <c r="E378" s="6" t="n"/>
-      <c r="F378" s="5" t="n"/>
+      <c r="F378" s="6" t="n"/>
       <c r="G378" s="5" t="n"/>
-      <c r="H378" s="6" t="n"/>
+      <c r="H378" s="5" t="n"/>
+      <c r="I378" s="6" t="n"/>
     </row>
     <row r="379" outlineLevel="2" ht="28.8" customHeight="1">
       <c r="A379" s="4" t="n">
@@ -5445,15 +5841,16 @@
           <t>HERE steht zwei Viertel, bis IN kommt</t>
         </is>
       </c>
-      <c r="D379" s="6" t="inlineStr">
+      <c r="D379" s="6" t="n"/>
+      <c r="E379" s="6" t="inlineStr">
         <is>
           <t>HERE -&gt; möglichst lange stehen lassen (bis der nächste text kommt)</t>
         </is>
       </c>
-      <c r="E379" s="6" t="n"/>
-      <c r="F379" s="5" t="n"/>
+      <c r="F379" s="6" t="n"/>
       <c r="G379" s="5" t="n"/>
-      <c r="H379" s="6" t="n"/>
+      <c r="H379" s="5" t="n"/>
+      <c r="I379" s="6" t="n"/>
     </row>
     <row r="380" outlineLevel="2">
       <c r="A380" s="4" t="n">
@@ -5463,9 +5860,10 @@
       <c r="C380" s="6" t="n"/>
       <c r="D380" s="6" t="n"/>
       <c r="E380" s="6" t="n"/>
-      <c r="F380" s="5" t="n"/>
+      <c r="F380" s="6" t="n"/>
       <c r="G380" s="5" t="n"/>
-      <c r="H380" s="6" t="n"/>
+      <c r="H380" s="5" t="n"/>
+      <c r="I380" s="6" t="n"/>
     </row>
     <row r="381" outlineLevel="2">
       <c r="A381" s="4" t="n">
@@ -5475,9 +5873,10 @@
       <c r="C381" s="6" t="n"/>
       <c r="D381" s="6" t="n"/>
       <c r="E381" s="6" t="n"/>
-      <c r="F381" s="5" t="n"/>
+      <c r="F381" s="6" t="n"/>
       <c r="G381" s="5" t="n"/>
-      <c r="H381" s="6" t="n"/>
+      <c r="H381" s="5" t="n"/>
+      <c r="I381" s="6" t="n"/>
     </row>
     <row r="382" outlineLevel="1">
       <c r="A382" s="4" t="n">
@@ -5487,9 +5886,10 @@
       <c r="C382" s="6" t="n"/>
       <c r="D382" s="6" t="n"/>
       <c r="E382" s="6" t="n"/>
-      <c r="F382" s="5" t="n"/>
+      <c r="F382" s="6" t="n"/>
       <c r="G382" s="5" t="n"/>
-      <c r="H382" s="6" t="n"/>
+      <c r="H382" s="5" t="n"/>
+      <c r="I382" s="6" t="n"/>
     </row>
     <row r="383" outlineLevel="2">
       <c r="A383" s="4" t="n">
@@ -5499,9 +5899,10 @@
       <c r="C383" s="6" t="n"/>
       <c r="D383" s="6" t="n"/>
       <c r="E383" s="6" t="n"/>
-      <c r="F383" s="5" t="n"/>
+      <c r="F383" s="6" t="n"/>
       <c r="G383" s="5" t="n"/>
-      <c r="H383" s="6" t="n"/>
+      <c r="H383" s="5" t="n"/>
+      <c r="I383" s="6" t="n"/>
     </row>
     <row r="384" outlineLevel="2">
       <c r="A384" s="4" t="n">
@@ -5511,9 +5912,10 @@
       <c r="C384" s="6" t="n"/>
       <c r="D384" s="6" t="n"/>
       <c r="E384" s="6" t="n"/>
-      <c r="F384" s="5" t="n"/>
+      <c r="F384" s="6" t="n"/>
       <c r="G384" s="5" t="n"/>
-      <c r="H384" s="6" t="n"/>
+      <c r="H384" s="5" t="n"/>
+      <c r="I384" s="6" t="n"/>
     </row>
     <row r="385" outlineLevel="2">
       <c r="A385" s="4" t="n">
@@ -5523,9 +5925,10 @@
       <c r="C385" s="6" t="n"/>
       <c r="D385" s="6" t="n"/>
       <c r="E385" s="6" t="n"/>
-      <c r="F385" s="5" t="n"/>
+      <c r="F385" s="6" t="n"/>
       <c r="G385" s="5" t="n"/>
-      <c r="H385" s="6" t="n"/>
+      <c r="H385" s="5" t="n"/>
+      <c r="I385" s="6" t="n"/>
     </row>
     <row r="386" ht="43.2" customHeight="1">
       <c r="A386" s="4" t="n">
@@ -5545,12 +5948,13 @@
       </c>
       <c r="D386" s="6" t="n"/>
       <c r="E386" s="6" t="n"/>
-      <c r="F386" s="5" t="n"/>
-      <c r="G386" s="5">
+      <c r="F386" s="6" t="n"/>
+      <c r="G386" s="5" t="n"/>
+      <c r="H386" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H386" s="6" t="inlineStr">
+      <c r="I386" s="6" t="inlineStr">
         <is>
           <t>progStrobo(8495, 100, 50, getRandomCRGB())</t>
         </is>
@@ -5564,9 +5968,10 @@
       <c r="C387" s="6" t="n"/>
       <c r="D387" s="6" t="n"/>
       <c r="E387" s="6" t="n"/>
-      <c r="F387" s="5" t="n"/>
+      <c r="F387" s="6" t="n"/>
       <c r="G387" s="5" t="n"/>
-      <c r="H387" s="6" t="n"/>
+      <c r="H387" s="5" t="n"/>
+      <c r="I387" s="6" t="n"/>
     </row>
     <row r="388" outlineLevel="2">
       <c r="A388" s="4" t="n">
@@ -5576,9 +5981,10 @@
       <c r="C388" s="6" t="n"/>
       <c r="D388" s="6" t="n"/>
       <c r="E388" s="6" t="n"/>
-      <c r="F388" s="5" t="n"/>
+      <c r="F388" s="6" t="n"/>
       <c r="G388" s="5" t="n"/>
-      <c r="H388" s="6" t="n"/>
+      <c r="H388" s="5" t="n"/>
+      <c r="I388" s="6" t="n"/>
     </row>
     <row r="389" outlineLevel="2">
       <c r="A389" s="4" t="n">
@@ -5588,9 +5994,10 @@
       <c r="C389" s="6" t="n"/>
       <c r="D389" s="6" t="n"/>
       <c r="E389" s="6" t="n"/>
-      <c r="F389" s="5" t="n"/>
+      <c r="F389" s="6" t="n"/>
       <c r="G389" s="5" t="n"/>
-      <c r="H389" s="6" t="n"/>
+      <c r="H389" s="5" t="n"/>
+      <c r="I389" s="6" t="n"/>
     </row>
     <row r="390" outlineLevel="1">
       <c r="A390" s="4" t="n">
@@ -5600,9 +6007,10 @@
       <c r="C390" s="6" t="n"/>
       <c r="D390" s="6" t="n"/>
       <c r="E390" s="6" t="n"/>
-      <c r="F390" s="5" t="n"/>
+      <c r="F390" s="6" t="n"/>
       <c r="G390" s="5" t="n"/>
-      <c r="H390" s="6" t="n"/>
+      <c r="H390" s="5" t="n"/>
+      <c r="I390" s="6" t="n"/>
     </row>
     <row r="391" outlineLevel="2">
       <c r="A391" s="4" t="n">
@@ -5612,9 +6020,10 @@
       <c r="C391" s="6" t="n"/>
       <c r="D391" s="6" t="n"/>
       <c r="E391" s="6" t="n"/>
-      <c r="F391" s="5" t="n"/>
+      <c r="F391" s="6" t="n"/>
       <c r="G391" s="5" t="n"/>
-      <c r="H391" s="6" t="n"/>
+      <c r="H391" s="5" t="n"/>
+      <c r="I391" s="6" t="n"/>
     </row>
     <row r="392" outlineLevel="2">
       <c r="A392" s="4" t="n">
@@ -5624,9 +6033,10 @@
       <c r="C392" s="6" t="n"/>
       <c r="D392" s="6" t="n"/>
       <c r="E392" s="6" t="n"/>
-      <c r="F392" s="5" t="n"/>
+      <c r="F392" s="6" t="n"/>
       <c r="G392" s="5" t="n"/>
-      <c r="H392" s="6" t="n"/>
+      <c r="H392" s="5" t="n"/>
+      <c r="I392" s="6" t="n"/>
     </row>
     <row r="393" outlineLevel="2">
       <c r="A393" s="4" t="n">
@@ -5636,9 +6046,10 @@
       <c r="C393" s="6" t="n"/>
       <c r="D393" s="6" t="n"/>
       <c r="E393" s="6" t="n"/>
-      <c r="F393" s="5" t="n"/>
+      <c r="F393" s="6" t="n"/>
       <c r="G393" s="5" t="n"/>
-      <c r="H393" s="6" t="n"/>
+      <c r="H393" s="5" t="n"/>
+      <c r="I393" s="6" t="n"/>
     </row>
     <row r="394" outlineLevel="1">
       <c r="A394" s="4" t="n">
@@ -5648,9 +6059,10 @@
       <c r="C394" s="6" t="n"/>
       <c r="D394" s="6" t="n"/>
       <c r="E394" s="6" t="n"/>
-      <c r="F394" s="5" t="n"/>
+      <c r="F394" s="6" t="n"/>
       <c r="G394" s="5" t="n"/>
-      <c r="H394" s="6" t="n"/>
+      <c r="H394" s="5" t="n"/>
+      <c r="I394" s="6" t="n"/>
     </row>
     <row r="395" outlineLevel="2">
       <c r="A395" s="4" t="n">
@@ -5660,9 +6072,10 @@
       <c r="C395" s="6" t="n"/>
       <c r="D395" s="6" t="n"/>
       <c r="E395" s="6" t="n"/>
-      <c r="F395" s="5" t="n"/>
+      <c r="F395" s="6" t="n"/>
       <c r="G395" s="5" t="n"/>
-      <c r="H395" s="6" t="n"/>
+      <c r="H395" s="5" t="n"/>
+      <c r="I395" s="6" t="n"/>
     </row>
     <row r="396" outlineLevel="2">
       <c r="A396" s="4" t="n">
@@ -5672,9 +6085,10 @@
       <c r="C396" s="6" t="n"/>
       <c r="D396" s="6" t="n"/>
       <c r="E396" s="6" t="n"/>
-      <c r="F396" s="5" t="n"/>
+      <c r="F396" s="6" t="n"/>
       <c r="G396" s="5" t="n"/>
-      <c r="H396" s="6" t="n"/>
+      <c r="H396" s="5" t="n"/>
+      <c r="I396" s="6" t="n"/>
     </row>
     <row r="397" outlineLevel="2">
       <c r="A397" s="4" t="n">
@@ -5684,9 +6098,10 @@
       <c r="C397" s="6" t="n"/>
       <c r="D397" s="6" t="n"/>
       <c r="E397" s="6" t="n"/>
-      <c r="F397" s="5" t="n"/>
+      <c r="F397" s="6" t="n"/>
       <c r="G397" s="5" t="n"/>
-      <c r="H397" s="6" t="n"/>
+      <c r="H397" s="5" t="n"/>
+      <c r="I397" s="6" t="n"/>
     </row>
     <row r="398" outlineLevel="1">
       <c r="A398" s="4" t="n">
@@ -5696,9 +6111,10 @@
       <c r="C398" s="6" t="n"/>
       <c r="D398" s="6" t="n"/>
       <c r="E398" s="6" t="n"/>
-      <c r="F398" s="5" t="n"/>
+      <c r="F398" s="6" t="n"/>
       <c r="G398" s="5" t="n"/>
-      <c r="H398" s="6" t="n"/>
+      <c r="H398" s="5" t="n"/>
+      <c r="I398" s="6" t="n"/>
     </row>
     <row r="399" outlineLevel="2">
       <c r="A399" s="4" t="n">
@@ -5708,9 +6124,10 @@
       <c r="C399" s="6" t="n"/>
       <c r="D399" s="6" t="n"/>
       <c r="E399" s="6" t="n"/>
-      <c r="F399" s="5" t="n"/>
+      <c r="F399" s="6" t="n"/>
       <c r="G399" s="5" t="n"/>
-      <c r="H399" s="6" t="n"/>
+      <c r="H399" s="5" t="n"/>
+      <c r="I399" s="6" t="n"/>
     </row>
     <row r="400" outlineLevel="2">
       <c r="A400" s="4" t="n">
@@ -5720,9 +6137,10 @@
       <c r="C400" s="6" t="n"/>
       <c r="D400" s="6" t="n"/>
       <c r="E400" s="6" t="n"/>
-      <c r="F400" s="5" t="n"/>
+      <c r="F400" s="6" t="n"/>
       <c r="G400" s="5" t="n"/>
-      <c r="H400" s="6" t="n"/>
+      <c r="H400" s="5" t="n"/>
+      <c r="I400" s="6" t="n"/>
     </row>
     <row r="401" outlineLevel="2">
       <c r="A401" s="4" t="n">
@@ -5732,9 +6150,10 @@
       <c r="C401" s="6" t="n"/>
       <c r="D401" s="6" t="n"/>
       <c r="E401" s="6" t="n"/>
-      <c r="F401" s="5" t="n"/>
+      <c r="F401" s="6" t="n"/>
       <c r="G401" s="5" t="n"/>
-      <c r="H401" s="6" t="n"/>
+      <c r="H401" s="5" t="n"/>
+      <c r="I401" s="6" t="n"/>
     </row>
     <row r="402" ht="72" customHeight="1">
       <c r="A402" s="4" t="n">
@@ -5755,12 +6174,13 @@
       </c>
       <c r="D402" s="6" t="n"/>
       <c r="E402" s="6" t="n"/>
-      <c r="F402" s="5" t="n"/>
-      <c r="G402" s="5">
+      <c r="F402" s="6" t="n"/>
+      <c r="G402" s="5" t="n"/>
+      <c r="H402" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H402" s="6" t="inlineStr">
+      <c r="I402" s="6" t="inlineStr">
         <is>
           <t>progStrobo(2125, 105, 490, getRandomCRGB())   (Matrix: progScrollText("1 2 3 4", 2125, 25, getRandomColor(), 105))</t>
         </is>
@@ -5774,9 +6194,10 @@
       <c r="C403" s="6" t="n"/>
       <c r="D403" s="6" t="n"/>
       <c r="E403" s="6" t="n"/>
-      <c r="F403" s="5" t="n"/>
+      <c r="F403" s="6" t="n"/>
       <c r="G403" s="5" t="n"/>
-      <c r="H403" s="6" t="n"/>
+      <c r="H403" s="5" t="n"/>
+      <c r="I403" s="6" t="n"/>
     </row>
     <row r="404" outlineLevel="2">
       <c r="A404" s="4" t="n">
@@ -5786,9 +6207,10 @@
       <c r="C404" s="6" t="n"/>
       <c r="D404" s="6" t="n"/>
       <c r="E404" s="6" t="n"/>
-      <c r="F404" s="5" t="n"/>
+      <c r="F404" s="6" t="n"/>
       <c r="G404" s="5" t="n"/>
-      <c r="H404" s="6" t="n"/>
+      <c r="H404" s="5" t="n"/>
+      <c r="I404" s="6" t="n"/>
     </row>
     <row r="405" outlineLevel="2">
       <c r="A405" s="4" t="n">
@@ -5798,9 +6220,10 @@
       <c r="C405" s="6" t="n"/>
       <c r="D405" s="6" t="n"/>
       <c r="E405" s="6" t="n"/>
-      <c r="F405" s="5" t="n"/>
+      <c r="F405" s="6" t="n"/>
       <c r="G405" s="5" t="n"/>
-      <c r="H405" s="6" t="n"/>
+      <c r="H405" s="5" t="n"/>
+      <c r="I405" s="6" t="n"/>
     </row>
     <row r="406" ht="57.6" customHeight="1">
       <c r="A406" s="4" t="n">
@@ -5820,12 +6243,13 @@
       </c>
       <c r="D406" s="6" t="n"/>
       <c r="E406" s="6" t="n"/>
-      <c r="F406" s="5" t="n"/>
-      <c r="G406" s="5">
+      <c r="F406" s="6" t="n"/>
+      <c r="G406" s="5" t="n"/>
+      <c r="H406" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H406" s="6" t="inlineStr">
+      <c r="I406" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 2, 110)</t>
         </is>
@@ -5839,9 +6263,10 @@
       <c r="C407" s="6" t="n"/>
       <c r="D407" s="6" t="n"/>
       <c r="E407" s="6" t="n"/>
-      <c r="F407" s="5" t="n"/>
+      <c r="F407" s="6" t="n"/>
       <c r="G407" s="5" t="n"/>
-      <c r="H407" s="6" t="n"/>
+      <c r="H407" s="5" t="n"/>
+      <c r="I407" s="6" t="n"/>
     </row>
     <row r="408" outlineLevel="2">
       <c r="A408" s="4" t="n">
@@ -5851,9 +6276,10 @@
       <c r="C408" s="6" t="n"/>
       <c r="D408" s="6" t="n"/>
       <c r="E408" s="6" t="n"/>
-      <c r="F408" s="5" t="n"/>
+      <c r="F408" s="6" t="n"/>
       <c r="G408" s="5" t="n"/>
-      <c r="H408" s="6" t="n"/>
+      <c r="H408" s="5" t="n"/>
+      <c r="I408" s="6" t="n"/>
     </row>
     <row r="409" outlineLevel="2">
       <c r="A409" s="4" t="n">
@@ -5863,9 +6289,10 @@
       <c r="C409" s="6" t="n"/>
       <c r="D409" s="6" t="n"/>
       <c r="E409" s="6" t="n"/>
-      <c r="F409" s="5" t="n"/>
+      <c r="F409" s="6" t="n"/>
       <c r="G409" s="5" t="n"/>
-      <c r="H409" s="6" t="n"/>
+      <c r="H409" s="5" t="n"/>
+      <c r="I409" s="6" t="n"/>
     </row>
     <row r="410" outlineLevel="1">
       <c r="A410" s="4" t="n">
@@ -5875,9 +6302,10 @@
       <c r="C410" s="6" t="n"/>
       <c r="D410" s="6" t="n"/>
       <c r="E410" s="6" t="n"/>
-      <c r="F410" s="5" t="n"/>
+      <c r="F410" s="6" t="n"/>
       <c r="G410" s="5" t="n"/>
-      <c r="H410" s="6" t="n"/>
+      <c r="H410" s="5" t="n"/>
+      <c r="I410" s="6" t="n"/>
     </row>
     <row r="411" outlineLevel="2">
       <c r="A411" s="4" t="n">
@@ -5887,9 +6315,10 @@
       <c r="C411" s="6" t="n"/>
       <c r="D411" s="6" t="n"/>
       <c r="E411" s="6" t="n"/>
-      <c r="F411" s="5" t="n"/>
+      <c r="F411" s="6" t="n"/>
       <c r="G411" s="5" t="n"/>
-      <c r="H411" s="6" t="n"/>
+      <c r="H411" s="5" t="n"/>
+      <c r="I411" s="6" t="n"/>
     </row>
     <row r="412" outlineLevel="2">
       <c r="A412" s="4" t="n">
@@ -5899,9 +6328,10 @@
       <c r="C412" s="6" t="n"/>
       <c r="D412" s="6" t="n"/>
       <c r="E412" s="6" t="n"/>
-      <c r="F412" s="5" t="n"/>
+      <c r="F412" s="6" t="n"/>
       <c r="G412" s="5" t="n"/>
-      <c r="H412" s="6" t="n"/>
+      <c r="H412" s="5" t="n"/>
+      <c r="I412" s="6" t="n"/>
     </row>
     <row r="413" outlineLevel="2">
       <c r="A413" s="4" t="n">
@@ -5911,9 +6341,10 @@
       <c r="C413" s="6" t="n"/>
       <c r="D413" s="6" t="n"/>
       <c r="E413" s="6" t="n"/>
-      <c r="F413" s="5" t="n"/>
+      <c r="F413" s="6" t="n"/>
       <c r="G413" s="5" t="n"/>
-      <c r="H413" s="6" t="n"/>
+      <c r="H413" s="5" t="n"/>
+      <c r="I413" s="6" t="n"/>
     </row>
     <row r="414" outlineLevel="1">
       <c r="A414" s="4" t="n">
@@ -5923,9 +6354,10 @@
       <c r="C414" s="6" t="n"/>
       <c r="D414" s="6" t="n"/>
       <c r="E414" s="6" t="n"/>
-      <c r="F414" s="5" t="n"/>
+      <c r="F414" s="6" t="n"/>
       <c r="G414" s="5" t="n"/>
-      <c r="H414" s="6" t="n"/>
+      <c r="H414" s="5" t="n"/>
+      <c r="I414" s="6" t="n"/>
     </row>
     <row r="415" outlineLevel="2">
       <c r="A415" s="4" t="n">
@@ -5935,9 +6367,10 @@
       <c r="C415" s="6" t="n"/>
       <c r="D415" s="6" t="n"/>
       <c r="E415" s="6" t="n"/>
-      <c r="F415" s="5" t="n"/>
+      <c r="F415" s="6" t="n"/>
       <c r="G415" s="5" t="n"/>
-      <c r="H415" s="6" t="n"/>
+      <c r="H415" s="5" t="n"/>
+      <c r="I415" s="6" t="n"/>
     </row>
     <row r="416" outlineLevel="2">
       <c r="A416" s="4" t="n">
@@ -5947,9 +6380,10 @@
       <c r="C416" s="6" t="n"/>
       <c r="D416" s="6" t="n"/>
       <c r="E416" s="6" t="n"/>
-      <c r="F416" s="5" t="n"/>
+      <c r="F416" s="6" t="n"/>
       <c r="G416" s="5" t="n"/>
-      <c r="H416" s="6" t="n"/>
+      <c r="H416" s="5" t="n"/>
+      <c r="I416" s="6" t="n"/>
     </row>
     <row r="417" outlineLevel="2">
       <c r="A417" s="4" t="n">
@@ -5959,9 +6393,10 @@
       <c r="C417" s="6" t="n"/>
       <c r="D417" s="6" t="n"/>
       <c r="E417" s="6" t="n"/>
-      <c r="F417" s="5" t="n"/>
+      <c r="F417" s="6" t="n"/>
       <c r="G417" s="5" t="n"/>
-      <c r="H417" s="6" t="n"/>
+      <c r="H417" s="5" t="n"/>
+      <c r="I417" s="6" t="n"/>
     </row>
     <row r="418" outlineLevel="1">
       <c r="A418" s="4" t="n">
@@ -5971,9 +6406,10 @@
       <c r="C418" s="6" t="n"/>
       <c r="D418" s="6" t="n"/>
       <c r="E418" s="6" t="n"/>
-      <c r="F418" s="5" t="n"/>
+      <c r="F418" s="6" t="n"/>
       <c r="G418" s="5" t="n"/>
-      <c r="H418" s="6" t="n"/>
+      <c r="H418" s="5" t="n"/>
+      <c r="I418" s="6" t="n"/>
     </row>
     <row r="419" outlineLevel="2">
       <c r="A419" s="4" t="n">
@@ -5983,9 +6419,10 @@
       <c r="C419" s="6" t="n"/>
       <c r="D419" s="6" t="n"/>
       <c r="E419" s="6" t="n"/>
-      <c r="F419" s="5" t="n"/>
+      <c r="F419" s="6" t="n"/>
       <c r="G419" s="5" t="n"/>
-      <c r="H419" s="6" t="n"/>
+      <c r="H419" s="5" t="n"/>
+      <c r="I419" s="6" t="n"/>
     </row>
     <row r="420" outlineLevel="2">
       <c r="A420" s="4" t="n">
@@ -5995,9 +6432,10 @@
       <c r="C420" s="6" t="n"/>
       <c r="D420" s="6" t="n"/>
       <c r="E420" s="6" t="n"/>
-      <c r="F420" s="5" t="n"/>
+      <c r="F420" s="6" t="n"/>
       <c r="G420" s="5" t="n"/>
-      <c r="H420" s="6" t="n"/>
+      <c r="H420" s="5" t="n"/>
+      <c r="I420" s="6" t="n"/>
     </row>
     <row r="421" outlineLevel="2">
       <c r="A421" s="4" t="n">
@@ -6007,9 +6445,10 @@
       <c r="C421" s="6" t="n"/>
       <c r="D421" s="6" t="n"/>
       <c r="E421" s="6" t="n"/>
-      <c r="F421" s="5" t="n"/>
+      <c r="F421" s="6" t="n"/>
       <c r="G421" s="5" t="n"/>
-      <c r="H421" s="6" t="n"/>
+      <c r="H421" s="5" t="n"/>
+      <c r="I421" s="6" t="n"/>
     </row>
     <row r="422" ht="28.8" customHeight="1">
       <c r="A422" s="4" t="n">
@@ -6028,12 +6467,13 @@
       </c>
       <c r="D422" s="6" t="n"/>
       <c r="E422" s="6" t="n"/>
-      <c r="F422" s="5" t="n"/>
-      <c r="G422" s="5">
+      <c r="F422" s="6" t="n"/>
+      <c r="G422" s="5" t="n"/>
+      <c r="H422" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H422" s="6" t="inlineStr">
+      <c r="I422" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 4, 115)</t>
         </is>
@@ -6047,9 +6487,10 @@
       <c r="C423" s="6" t="n"/>
       <c r="D423" s="6" t="n"/>
       <c r="E423" s="6" t="n"/>
-      <c r="F423" s="5" t="n"/>
+      <c r="F423" s="6" t="n"/>
       <c r="G423" s="5" t="n"/>
-      <c r="H423" s="6" t="n"/>
+      <c r="H423" s="5" t="n"/>
+      <c r="I423" s="6" t="n"/>
     </row>
     <row r="424" outlineLevel="2">
       <c r="A424" s="4" t="n">
@@ -6059,9 +6500,10 @@
       <c r="C424" s="6" t="n"/>
       <c r="D424" s="6" t="n"/>
       <c r="E424" s="6" t="n"/>
-      <c r="F424" s="5" t="n"/>
+      <c r="F424" s="6" t="n"/>
       <c r="G424" s="5" t="n"/>
-      <c r="H424" s="6" t="n"/>
+      <c r="H424" s="5" t="n"/>
+      <c r="I424" s="6" t="n"/>
     </row>
     <row r="425" outlineLevel="2">
       <c r="A425" s="4" t="n">
@@ -6071,9 +6513,10 @@
       <c r="C425" s="6" t="n"/>
       <c r="D425" s="6" t="n"/>
       <c r="E425" s="6" t="n"/>
-      <c r="F425" s="5" t="n"/>
+      <c r="F425" s="6" t="n"/>
       <c r="G425" s="5" t="n"/>
-      <c r="H425" s="6" t="n"/>
+      <c r="H425" s="5" t="n"/>
+      <c r="I425" s="6" t="n"/>
     </row>
     <row r="426" outlineLevel="1">
       <c r="A426" s="4" t="n">
@@ -6083,9 +6526,10 @@
       <c r="C426" s="6" t="n"/>
       <c r="D426" s="6" t="n"/>
       <c r="E426" s="6" t="n"/>
-      <c r="F426" s="5" t="n"/>
+      <c r="F426" s="6" t="n"/>
       <c r="G426" s="5" t="n"/>
-      <c r="H426" s="6" t="n"/>
+      <c r="H426" s="5" t="n"/>
+      <c r="I426" s="6" t="n"/>
     </row>
     <row r="427" outlineLevel="2">
       <c r="A427" s="4" t="n">
@@ -6095,9 +6539,10 @@
       <c r="C427" s="6" t="n"/>
       <c r="D427" s="6" t="n"/>
       <c r="E427" s="6" t="n"/>
-      <c r="F427" s="5" t="n"/>
+      <c r="F427" s="6" t="n"/>
       <c r="G427" s="5" t="n"/>
-      <c r="H427" s="6" t="n"/>
+      <c r="H427" s="5" t="n"/>
+      <c r="I427" s="6" t="n"/>
     </row>
     <row r="428" outlineLevel="2">
       <c r="A428" s="4" t="n">
@@ -6107,9 +6552,10 @@
       <c r="C428" s="6" t="n"/>
       <c r="D428" s="6" t="n"/>
       <c r="E428" s="6" t="n"/>
-      <c r="F428" s="5" t="n"/>
+      <c r="F428" s="6" t="n"/>
       <c r="G428" s="5" t="n"/>
-      <c r="H428" s="6" t="n"/>
+      <c r="H428" s="5" t="n"/>
+      <c r="I428" s="6" t="n"/>
     </row>
     <row r="429" outlineLevel="2">
       <c r="A429" s="4" t="n">
@@ -6119,9 +6565,10 @@
       <c r="C429" s="6" t="n"/>
       <c r="D429" s="6" t="n"/>
       <c r="E429" s="6" t="n"/>
-      <c r="F429" s="5" t="n"/>
+      <c r="F429" s="6" t="n"/>
       <c r="G429" s="5" t="n"/>
-      <c r="H429" s="6" t="n"/>
+      <c r="H429" s="5" t="n"/>
+      <c r="I429" s="6" t="n"/>
     </row>
     <row r="430" outlineLevel="1">
       <c r="A430" s="4" t="n">
@@ -6131,9 +6578,10 @@
       <c r="C430" s="6" t="n"/>
       <c r="D430" s="6" t="n"/>
       <c r="E430" s="6" t="n"/>
-      <c r="F430" s="5" t="n"/>
+      <c r="F430" s="6" t="n"/>
       <c r="G430" s="5" t="n"/>
-      <c r="H430" s="6" t="n"/>
+      <c r="H430" s="5" t="n"/>
+      <c r="I430" s="6" t="n"/>
     </row>
     <row r="431" outlineLevel="2">
       <c r="A431" s="4" t="n">
@@ -6143,9 +6591,10 @@
       <c r="C431" s="6" t="n"/>
       <c r="D431" s="6" t="n"/>
       <c r="E431" s="6" t="n"/>
-      <c r="F431" s="5" t="n"/>
+      <c r="F431" s="6" t="n"/>
       <c r="G431" s="5" t="n"/>
-      <c r="H431" s="6" t="n"/>
+      <c r="H431" s="5" t="n"/>
+      <c r="I431" s="6" t="n"/>
     </row>
     <row r="432" outlineLevel="2">
       <c r="A432" s="4" t="n">
@@ -6155,9 +6604,10 @@
       <c r="C432" s="6" t="n"/>
       <c r="D432" s="6" t="n"/>
       <c r="E432" s="6" t="n"/>
-      <c r="F432" s="5" t="n"/>
+      <c r="F432" s="6" t="n"/>
       <c r="G432" s="5" t="n"/>
-      <c r="H432" s="6" t="n"/>
+      <c r="H432" s="5" t="n"/>
+      <c r="I432" s="6" t="n"/>
     </row>
     <row r="433" outlineLevel="2">
       <c r="A433" s="4" t="n">
@@ -6167,9 +6617,10 @@
       <c r="C433" s="6" t="n"/>
       <c r="D433" s="6" t="n"/>
       <c r="E433" s="6" t="n"/>
-      <c r="F433" s="5" t="n"/>
+      <c r="F433" s="6" t="n"/>
       <c r="G433" s="5" t="n"/>
-      <c r="H433" s="6" t="n"/>
+      <c r="H433" s="5" t="n"/>
+      <c r="I433" s="6" t="n"/>
     </row>
     <row r="434" outlineLevel="1">
       <c r="A434" s="4" t="n">
@@ -6179,9 +6630,10 @@
       <c r="C434" s="6" t="n"/>
       <c r="D434" s="6" t="n"/>
       <c r="E434" s="6" t="n"/>
-      <c r="F434" s="5" t="n"/>
+      <c r="F434" s="6" t="n"/>
       <c r="G434" s="5" t="n"/>
-      <c r="H434" s="6" t="n"/>
+      <c r="H434" s="5" t="n"/>
+      <c r="I434" s="6" t="n"/>
     </row>
     <row r="435" outlineLevel="2">
       <c r="A435" s="4" t="n">
@@ -6191,9 +6643,10 @@
       <c r="C435" s="6" t="n"/>
       <c r="D435" s="6" t="n"/>
       <c r="E435" s="6" t="n"/>
-      <c r="F435" s="5" t="n"/>
+      <c r="F435" s="6" t="n"/>
       <c r="G435" s="5" t="n"/>
-      <c r="H435" s="6" t="n"/>
+      <c r="H435" s="5" t="n"/>
+      <c r="I435" s="6" t="n"/>
     </row>
     <row r="436" outlineLevel="2">
       <c r="A436" s="4" t="n">
@@ -6203,9 +6656,10 @@
       <c r="C436" s="6" t="n"/>
       <c r="D436" s="6" t="n"/>
       <c r="E436" s="6" t="n"/>
-      <c r="F436" s="5" t="n"/>
+      <c r="F436" s="6" t="n"/>
       <c r="G436" s="5" t="n"/>
-      <c r="H436" s="6" t="n"/>
+      <c r="H436" s="5" t="n"/>
+      <c r="I436" s="6" t="n"/>
     </row>
     <row r="437" outlineLevel="2">
       <c r="A437" s="4" t="n">
@@ -6215,9 +6669,10 @@
       <c r="C437" s="6" t="n"/>
       <c r="D437" s="6" t="n"/>
       <c r="E437" s="6" t="n"/>
-      <c r="F437" s="5" t="n"/>
+      <c r="F437" s="6" t="n"/>
       <c r="G437" s="5" t="n"/>
-      <c r="H437" s="6" t="n"/>
+      <c r="H437" s="5" t="n"/>
+      <c r="I437" s="6" t="n"/>
     </row>
     <row r="438" ht="28.8" customHeight="1">
       <c r="A438" s="4" t="n">
@@ -6236,12 +6691,13 @@
       </c>
       <c r="D438" s="6" t="n"/>
       <c r="E438" s="6" t="n"/>
-      <c r="F438" s="5" t="n"/>
-      <c r="G438" s="5">
+      <c r="F438" s="6" t="n"/>
+      <c r="G438" s="5" t="n"/>
+      <c r="H438" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H438" s="6" t="inlineStr">
+      <c r="I438" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 6, 120)</t>
         </is>
@@ -6255,9 +6711,10 @@
       <c r="C439" s="6" t="n"/>
       <c r="D439" s="6" t="n"/>
       <c r="E439" s="6" t="n"/>
-      <c r="F439" s="5" t="n"/>
+      <c r="F439" s="6" t="n"/>
       <c r="G439" s="5" t="n"/>
-      <c r="H439" s="6" t="n"/>
+      <c r="H439" s="5" t="n"/>
+      <c r="I439" s="6" t="n"/>
     </row>
     <row r="440" outlineLevel="2">
       <c r="A440" s="4" t="n">
@@ -6267,9 +6724,10 @@
       <c r="C440" s="6" t="n"/>
       <c r="D440" s="6" t="n"/>
       <c r="E440" s="6" t="n"/>
-      <c r="F440" s="5" t="n"/>
+      <c r="F440" s="6" t="n"/>
       <c r="G440" s="5" t="n"/>
-      <c r="H440" s="6" t="n"/>
+      <c r="H440" s="5" t="n"/>
+      <c r="I440" s="6" t="n"/>
     </row>
     <row r="441" outlineLevel="2">
       <c r="A441" s="4" t="n">
@@ -6279,9 +6737,10 @@
       <c r="C441" s="6" t="n"/>
       <c r="D441" s="6" t="n"/>
       <c r="E441" s="6" t="n"/>
-      <c r="F441" s="5" t="n"/>
+      <c r="F441" s="6" t="n"/>
       <c r="G441" s="5" t="n"/>
-      <c r="H441" s="6" t="n"/>
+      <c r="H441" s="5" t="n"/>
+      <c r="I441" s="6" t="n"/>
     </row>
     <row r="442" outlineLevel="1">
       <c r="A442" s="4" t="n">
@@ -6291,9 +6750,10 @@
       <c r="C442" s="6" t="n"/>
       <c r="D442" s="6" t="n"/>
       <c r="E442" s="6" t="n"/>
-      <c r="F442" s="5" t="n"/>
+      <c r="F442" s="6" t="n"/>
       <c r="G442" s="5" t="n"/>
-      <c r="H442" s="6" t="n"/>
+      <c r="H442" s="5" t="n"/>
+      <c r="I442" s="6" t="n"/>
     </row>
     <row r="443" outlineLevel="2">
       <c r="A443" s="4" t="n">
@@ -6303,9 +6763,10 @@
       <c r="C443" s="6" t="n"/>
       <c r="D443" s="6" t="n"/>
       <c r="E443" s="6" t="n"/>
-      <c r="F443" s="5" t="n"/>
+      <c r="F443" s="6" t="n"/>
       <c r="G443" s="5" t="n"/>
-      <c r="H443" s="6" t="n"/>
+      <c r="H443" s="5" t="n"/>
+      <c r="I443" s="6" t="n"/>
     </row>
     <row r="444" outlineLevel="2">
       <c r="A444" s="4" t="n">
@@ -6315,9 +6776,10 @@
       <c r="C444" s="6" t="n"/>
       <c r="D444" s="6" t="n"/>
       <c r="E444" s="6" t="n"/>
-      <c r="F444" s="5" t="n"/>
+      <c r="F444" s="6" t="n"/>
       <c r="G444" s="5" t="n"/>
-      <c r="H444" s="6" t="n"/>
+      <c r="H444" s="5" t="n"/>
+      <c r="I444" s="6" t="n"/>
     </row>
     <row r="445" outlineLevel="2">
       <c r="A445" s="4" t="n">
@@ -6327,9 +6789,10 @@
       <c r="C445" s="6" t="n"/>
       <c r="D445" s="6" t="n"/>
       <c r="E445" s="6" t="n"/>
-      <c r="F445" s="5" t="n"/>
+      <c r="F445" s="6" t="n"/>
       <c r="G445" s="5" t="n"/>
-      <c r="H445" s="6" t="n"/>
+      <c r="H445" s="5" t="n"/>
+      <c r="I445" s="6" t="n"/>
     </row>
     <row r="446" outlineLevel="1">
       <c r="A446" s="4" t="n">
@@ -6339,9 +6802,10 @@
       <c r="C446" s="6" t="n"/>
       <c r="D446" s="6" t="n"/>
       <c r="E446" s="6" t="n"/>
-      <c r="F446" s="5" t="n"/>
+      <c r="F446" s="6" t="n"/>
       <c r="G446" s="5" t="n"/>
-      <c r="H446" s="6" t="n"/>
+      <c r="H446" s="5" t="n"/>
+      <c r="I446" s="6" t="n"/>
     </row>
     <row r="447" outlineLevel="2">
       <c r="A447" s="4" t="n">
@@ -6351,9 +6815,10 @@
       <c r="C447" s="6" t="n"/>
       <c r="D447" s="6" t="n"/>
       <c r="E447" s="6" t="n"/>
-      <c r="F447" s="5" t="n"/>
+      <c r="F447" s="6" t="n"/>
       <c r="G447" s="5" t="n"/>
-      <c r="H447" s="6" t="n"/>
+      <c r="H447" s="5" t="n"/>
+      <c r="I447" s="6" t="n"/>
     </row>
     <row r="448" outlineLevel="2">
       <c r="A448" s="4" t="n">
@@ -6363,9 +6828,10 @@
       <c r="C448" s="6" t="n"/>
       <c r="D448" s="6" t="n"/>
       <c r="E448" s="6" t="n"/>
-      <c r="F448" s="5" t="n"/>
+      <c r="F448" s="6" t="n"/>
       <c r="G448" s="5" t="n"/>
-      <c r="H448" s="6" t="n"/>
+      <c r="H448" s="5" t="n"/>
+      <c r="I448" s="6" t="n"/>
     </row>
     <row r="449" outlineLevel="2">
       <c r="A449" s="4" t="n">
@@ -6375,9 +6841,10 @@
       <c r="C449" s="6" t="n"/>
       <c r="D449" s="6" t="n"/>
       <c r="E449" s="6" t="n"/>
-      <c r="F449" s="5" t="n"/>
+      <c r="F449" s="6" t="n"/>
       <c r="G449" s="5" t="n"/>
-      <c r="H449" s="6" t="n"/>
+      <c r="H449" s="5" t="n"/>
+      <c r="I449" s="6" t="n"/>
     </row>
     <row r="450" outlineLevel="1">
       <c r="A450" s="4" t="n">
@@ -6387,9 +6854,10 @@
       <c r="C450" s="6" t="n"/>
       <c r="D450" s="6" t="n"/>
       <c r="E450" s="6" t="n"/>
-      <c r="F450" s="5" t="n"/>
+      <c r="F450" s="6" t="n"/>
       <c r="G450" s="5" t="n"/>
-      <c r="H450" s="6" t="n"/>
+      <c r="H450" s="5" t="n"/>
+      <c r="I450" s="6" t="n"/>
     </row>
     <row r="451" outlineLevel="2">
       <c r="A451" s="4" t="n">
@@ -6399,9 +6867,10 @@
       <c r="C451" s="6" t="n"/>
       <c r="D451" s="6" t="n"/>
       <c r="E451" s="6" t="n"/>
-      <c r="F451" s="5" t="n"/>
+      <c r="F451" s="6" t="n"/>
       <c r="G451" s="5" t="n"/>
-      <c r="H451" s="6" t="n"/>
+      <c r="H451" s="5" t="n"/>
+      <c r="I451" s="6" t="n"/>
     </row>
     <row r="452" outlineLevel="2">
       <c r="A452" s="4" t="n">
@@ -6411,9 +6880,10 @@
       <c r="C452" s="6" t="n"/>
       <c r="D452" s="6" t="n"/>
       <c r="E452" s="6" t="n"/>
-      <c r="F452" s="5" t="n"/>
+      <c r="F452" s="6" t="n"/>
       <c r="G452" s="5" t="n"/>
-      <c r="H452" s="6" t="n"/>
+      <c r="H452" s="5" t="n"/>
+      <c r="I452" s="6" t="n"/>
     </row>
     <row r="453" outlineLevel="2">
       <c r="A453" s="4" t="n">
@@ -6423,9 +6893,10 @@
       <c r="C453" s="6" t="n"/>
       <c r="D453" s="6" t="n"/>
       <c r="E453" s="6" t="n"/>
-      <c r="F453" s="5" t="n"/>
+      <c r="F453" s="6" t="n"/>
       <c r="G453" s="5" t="n"/>
-      <c r="H453" s="6" t="n"/>
+      <c r="H453" s="5" t="n"/>
+      <c r="I453" s="6" t="n"/>
     </row>
     <row r="454" ht="86.40000000000001" customHeight="1">
       <c r="A454" s="4" t="n">
@@ -6445,12 +6916,13 @@
       </c>
       <c r="D454" s="6" t="n"/>
       <c r="E454" s="6" t="n"/>
-      <c r="F454" s="5" t="n"/>
-      <c r="G454" s="5">
+      <c r="F454" s="6" t="n"/>
+      <c r="G454" s="5" t="n"/>
+      <c r="H454" s="5">
         <f>$C$3</f>
         <v/>
       </c>
-      <c r="H454" s="6" t="inlineStr">
+      <c r="I454" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(8495, 8, 135)</t>
         </is>
@@ -6464,9 +6936,10 @@
       <c r="C455" s="6" t="n"/>
       <c r="D455" s="6" t="n"/>
       <c r="E455" s="6" t="n"/>
-      <c r="F455" s="5" t="n"/>
+      <c r="F455" s="6" t="n"/>
       <c r="G455" s="5" t="n"/>
-      <c r="H455" s="6" t="n"/>
+      <c r="H455" s="5" t="n"/>
+      <c r="I455" s="6" t="n"/>
     </row>
     <row r="456" outlineLevel="2">
       <c r="A456" s="4" t="n">
@@ -6476,9 +6949,10 @@
       <c r="C456" s="6" t="n"/>
       <c r="D456" s="6" t="n"/>
       <c r="E456" s="6" t="n"/>
-      <c r="F456" s="5" t="n"/>
+      <c r="F456" s="6" t="n"/>
       <c r="G456" s="5" t="n"/>
-      <c r="H456" s="6" t="n"/>
+      <c r="H456" s="5" t="n"/>
+      <c r="I456" s="6" t="n"/>
     </row>
     <row r="457" outlineLevel="2">
       <c r="A457" s="4" t="n">
@@ -6488,9 +6962,10 @@
       <c r="C457" s="6" t="n"/>
       <c r="D457" s="6" t="n"/>
       <c r="E457" s="6" t="n"/>
-      <c r="F457" s="5" t="n"/>
+      <c r="F457" s="6" t="n"/>
       <c r="G457" s="5" t="n"/>
-      <c r="H457" s="6" t="n"/>
+      <c r="H457" s="5" t="n"/>
+      <c r="I457" s="6" t="n"/>
     </row>
     <row r="458" outlineLevel="1">
       <c r="A458" s="4" t="n">
@@ -6500,9 +6975,10 @@
       <c r="C458" s="6" t="n"/>
       <c r="D458" s="6" t="n"/>
       <c r="E458" s="6" t="n"/>
-      <c r="F458" s="5" t="n"/>
+      <c r="F458" s="6" t="n"/>
       <c r="G458" s="5" t="n"/>
-      <c r="H458" s="6" t="n"/>
+      <c r="H458" s="5" t="n"/>
+      <c r="I458" s="6" t="n"/>
     </row>
     <row r="459" outlineLevel="2">
       <c r="A459" s="4" t="n">
@@ -6512,9 +6988,10 @@
       <c r="C459" s="6" t="n"/>
       <c r="D459" s="6" t="n"/>
       <c r="E459" s="6" t="n"/>
-      <c r="F459" s="5" t="n"/>
+      <c r="F459" s="6" t="n"/>
       <c r="G459" s="5" t="n"/>
-      <c r="H459" s="6" t="n"/>
+      <c r="H459" s="5" t="n"/>
+      <c r="I459" s="6" t="n"/>
     </row>
     <row r="460" outlineLevel="2">
       <c r="A460" s="4" t="n">
@@ -6524,9 +7001,10 @@
       <c r="C460" s="6" t="n"/>
       <c r="D460" s="6" t="n"/>
       <c r="E460" s="6" t="n"/>
-      <c r="F460" s="5" t="n"/>
+      <c r="F460" s="6" t="n"/>
       <c r="G460" s="5" t="n"/>
-      <c r="H460" s="6" t="n"/>
+      <c r="H460" s="5" t="n"/>
+      <c r="I460" s="6" t="n"/>
     </row>
     <row r="461" outlineLevel="2">
       <c r="A461" s="4" t="n">
@@ -6536,9 +7014,10 @@
       <c r="C461" s="6" t="n"/>
       <c r="D461" s="6" t="n"/>
       <c r="E461" s="6" t="n"/>
-      <c r="F461" s="5" t="n"/>
+      <c r="F461" s="6" t="n"/>
       <c r="G461" s="5" t="n"/>
-      <c r="H461" s="6" t="n"/>
+      <c r="H461" s="5" t="n"/>
+      <c r="I461" s="6" t="n"/>
     </row>
     <row r="462" outlineLevel="1">
       <c r="A462" s="4" t="n">
@@ -6548,9 +7027,10 @@
       <c r="C462" s="6" t="n"/>
       <c r="D462" s="6" t="n"/>
       <c r="E462" s="6" t="n"/>
-      <c r="F462" s="5" t="n"/>
+      <c r="F462" s="6" t="n"/>
       <c r="G462" s="5" t="n"/>
-      <c r="H462" s="6" t="n"/>
+      <c r="H462" s="5" t="n"/>
+      <c r="I462" s="6" t="n"/>
     </row>
     <row r="463" outlineLevel="2">
       <c r="A463" s="4" t="n">
@@ -6560,9 +7040,10 @@
       <c r="C463" s="6" t="n"/>
       <c r="D463" s="6" t="n"/>
       <c r="E463" s="6" t="n"/>
-      <c r="F463" s="5" t="n"/>
+      <c r="F463" s="6" t="n"/>
       <c r="G463" s="5" t="n"/>
-      <c r="H463" s="6" t="n"/>
+      <c r="H463" s="5" t="n"/>
+      <c r="I463" s="6" t="n"/>
     </row>
     <row r="464" outlineLevel="2">
       <c r="A464" s="4" t="n">
@@ -6572,9 +7053,10 @@
       <c r="C464" s="6" t="n"/>
       <c r="D464" s="6" t="n"/>
       <c r="E464" s="6" t="n"/>
-      <c r="F464" s="5" t="n"/>
+      <c r="F464" s="6" t="n"/>
       <c r="G464" s="5" t="n"/>
-      <c r="H464" s="6" t="n"/>
+      <c r="H464" s="5" t="n"/>
+      <c r="I464" s="6" t="n"/>
     </row>
     <row r="465" outlineLevel="2">
       <c r="A465" s="4" t="n">
@@ -6584,9 +7066,10 @@
       <c r="C465" s="6" t="n"/>
       <c r="D465" s="6" t="n"/>
       <c r="E465" s="6" t="n"/>
-      <c r="F465" s="5" t="n"/>
+      <c r="F465" s="6" t="n"/>
       <c r="G465" s="5" t="n"/>
-      <c r="H465" s="6" t="n"/>
+      <c r="H465" s="5" t="n"/>
+      <c r="I465" s="6" t="n"/>
     </row>
     <row r="466" outlineLevel="1">
       <c r="A466" s="4" t="n">
@@ -6596,9 +7079,10 @@
       <c r="C466" s="6" t="n"/>
       <c r="D466" s="6" t="n"/>
       <c r="E466" s="6" t="n"/>
-      <c r="F466" s="5" t="n"/>
+      <c r="F466" s="6" t="n"/>
       <c r="G466" s="5" t="n"/>
-      <c r="H466" s="6" t="n"/>
+      <c r="H466" s="5" t="n"/>
+      <c r="I466" s="6" t="n"/>
     </row>
     <row r="467" outlineLevel="2">
       <c r="A467" s="4" t="n">
@@ -6608,9 +7092,10 @@
       <c r="C467" s="6" t="n"/>
       <c r="D467" s="6" t="n"/>
       <c r="E467" s="6" t="n"/>
-      <c r="F467" s="5" t="n"/>
+      <c r="F467" s="6" t="n"/>
       <c r="G467" s="5" t="n"/>
-      <c r="H467" s="6" t="n"/>
+      <c r="H467" s="5" t="n"/>
+      <c r="I467" s="6" t="n"/>
     </row>
     <row r="468" outlineLevel="2">
       <c r="A468" s="4" t="n">
@@ -6620,9 +7105,10 @@
       <c r="C468" s="6" t="n"/>
       <c r="D468" s="6" t="n"/>
       <c r="E468" s="6" t="n"/>
-      <c r="F468" s="5" t="n"/>
+      <c r="F468" s="6" t="n"/>
       <c r="G468" s="5" t="n"/>
-      <c r="H468" s="6" t="n"/>
+      <c r="H468" s="5" t="n"/>
+      <c r="I468" s="6" t="n"/>
     </row>
     <row r="469" outlineLevel="2">
       <c r="A469" s="4" t="n">
@@ -6632,9 +7118,10 @@
       <c r="C469" s="6" t="n"/>
       <c r="D469" s="6" t="n"/>
       <c r="E469" s="6" t="n"/>
-      <c r="F469" s="5" t="n"/>
+      <c r="F469" s="6" t="n"/>
       <c r="G469" s="5" t="n"/>
-      <c r="H469" s="6" t="n"/>
+      <c r="H469" s="5" t="n"/>
+      <c r="I469" s="6" t="n"/>
     </row>
     <row r="470">
       <c r="A470" s="7" t="n">
@@ -6650,10 +7137,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="F470" t="n">
+      <c r="G470" t="n">
         <v>0</v>
       </c>
-      <c r="G470">
+      <c r="H470">
         <f>$C$3</f>
         <v/>
       </c>
